--- a/evaluation_result_9cd.xlsx
+++ b/evaluation_result_9cd.xlsx
@@ -709,10 +709,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.4724409448818898</v>
+        <v>0.4923076923076923</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.6417112299465241</v>
+        <v>0.6597938144329898</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>24</v>
@@ -754,10 +754,10 @@
         <v>0.9210526315789473</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>0.356401384083045</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>0.5139354194882031</v>
+        <v>0.5136889641546711</v>
       </c>
       <c r="J7" s="11" t="n">
         <v>31</v>
@@ -799,10 +799,10 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.4383561643835616</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.58222533240028</v>
+        <v>0.5901201602136181</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>10</v>
@@ -844,10 +844,10 @@
         <v>0.75</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>0.3188405797101449</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>0.447457627118644</v>
+        <v>0.4615384615384615</v>
       </c>
       <c r="J9" s="11" t="n">
         <v>5</v>
@@ -886,25 +886,25 @@
         <v>142</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.923076923076923</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.2049469964664311</v>
+        <v>0.2027972027972028</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.3354216867469879</v>
+        <v>0.324194836305563</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.88</v>
+        <v>0.68</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="11">
@@ -931,25 +931,25 @@
         <v>96</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0.256544502617801</v>
+        <v>0.2680412371134021</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>0.3972728947853326</v>
+        <v>0.4015444015444015</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1</v>
+        <v>0.9583333333333335</v>
       </c>
     </row>
     <row r="12">
@@ -976,25 +976,25 @@
         <v>343</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0.2014598540145985</v>
+        <v>0.2005813953488372</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0.3233112065599375</v>
+        <v>0.3184903611186533</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6031746031746031</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0.9841269841269841</v>
+        <v>0.9523809523809522</v>
       </c>
     </row>
     <row r="13">
@@ -1021,25 +1021,25 @@
         <v>142</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.951219512195122</v>
+        <v>0.926829268292683</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>0.3498233215547703</v>
+        <v>0.3496503496503497</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>0.5115262321144675</v>
+        <v>0.5077498663816142</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>0.925</v>
+        <v>0.875</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="14">
@@ -1069,10 +1069,10 @@
         <v>0.9130434782608695</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0.2667332667332667</v>
+        <v>0.2669322709163346</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0.412856196156395</v>
+        <v>0.4130945390487375</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>92</v>
@@ -1109,25 +1109,25 @@
         <v>1505</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.8914712255511498</v>
+        <v>0.8620012916909719</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>0.3183941127161677</v>
+        <v>0.3241306984534919</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>0.462857536146308</v>
+        <v>0.4655794894154123</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>0.8051575931232091</v>
+        <v>0.7650429799426934</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>0.997134670487106</v>
+        <v>0.9828080229226361</v>
       </c>
     </row>
     <row r="16">
@@ -1147,34 +1147,34 @@
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>326 / 363 mốc</t>
+          <t>317 / 363 mốc</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>828 / 3001 vết</t>
+          <t>421 / 1514 vết</t>
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.8980716253443526</v>
+        <v>0.8732782369146006</v>
       </c>
       <c r="H16" s="17" t="n">
-        <v>0.2759080306564479</v>
+        <v>0.2780713342140027</v>
       </c>
       <c r="I16" s="17" t="n">
-        <v>0.4221285646146268</v>
+        <v>0.4218243539029744</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>0.8051575931232091</v>
+        <v>0.7650429799426934</v>
       </c>
       <c r="L16" s="16" t="n">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="M16" s="17" t="n">
-        <v>0.997134670487106</v>
+        <v>0.9828080229226361</v>
       </c>
     </row>
     <row r="17"/>
@@ -1245,30 +1245,30 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>0.5556343490517739</v>
+        <v>0.5053825162928249</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>0.5702479338842975</v>
+        <v>0.5206611570247934</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>207 / 363</t>
+          <t>189 / 363</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>0.1488967586333777</v>
+        <v>0.1489843403980958</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0.1279573475508164</v>
+        <v>0.1301188903566711</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0.2348573474094153</v>
+        <v>0.2301280392450571</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>0.3151862464183381</v>
+        <v>0.2808022922636103</v>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
     </row>
@@ -1279,30 +1279,30 @@
         </is>
       </c>
       <c r="B22" s="20" t="n">
-        <v>0.8914712255511498</v>
+        <v>0.8620012916909718</v>
       </c>
       <c r="C22" s="20" t="n">
-        <v>0.8980716253443526</v>
+        <v>0.8732782369146005</v>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>326 / 363</t>
+          <t>317 / 363</t>
         </is>
       </c>
       <c r="E22" s="20" t="n">
-        <v>0.3183941127161677</v>
+        <v>0.324130698453492</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>0.2759080306564479</v>
+        <v>0.2780713342140027</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.4692079042083264</v>
+        <v>0.4711129673006755</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="I22" s="20" t="n">
-        <v>0.8051575931232091</v>
+        <v>0.7650429799426933</v>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.4389627438150844</v>
+        <v>0.4323698549093903</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0.3795401532822392</v>
+        <v>0.3771466314398942</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0.6012507675847177</v>
+        <v>0.5950368965869876</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>319</v>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.5436383353277798</v>
+        <v>0.5463565192971105</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0.4705098300566478</v>
+        <v>0.4729194187582563</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.7003508780475863</v>
+        <v>0.7026024612080722</v>
       </c>
       <c r="H24" s="11" t="n">
         <v>340</v>
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="E25" s="8" t="n">
-        <v>0.6879609659275868</v>
+        <v>0.6898114698271535</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0.5998000666444518</v>
+        <v>0.6023778071334214</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0.8151384775056465</v>
+        <v>0.8164360133000074</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>349</v>
@@ -1434,13 +1434,13 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.7560009990866599</v>
+        <v>0.7551002182686358</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.6657780739753414</v>
+        <v>0.667107001321004</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.8610484840041377</v>
+        <v>0.8604639329525285</v>
       </c>
       <c r="H26" s="11" t="n">
         <v>349</v>
@@ -1613,10 +1613,10 @@
         <v>1.33</v>
       </c>
       <c r="K5" s="22" t="n">
-        <v>1.263</v>
+        <v>1.229</v>
       </c>
       <c r="L5" s="22" t="n">
-        <v>0.067</v>
+        <v>0.101</v>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
         <v>1.33</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>1.263</v>
+        <v>1.229</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>0.067</v>
+        <v>0.101</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         <v>4.72</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>5.051</v>
+        <v>5.085</v>
       </c>
       <c r="L6" s="24" t="n">
-        <v>0.331</v>
+        <v>0.365</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
         <v>4.72</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>5.051</v>
+        <v>5.085</v>
       </c>
       <c r="H7" s="22" t="n">
-        <v>0.331</v>
+        <v>0.365</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         <v>5.98</v>
       </c>
       <c r="K7" s="22" t="n">
-        <v>5.982</v>
+        <v>5.949</v>
       </c>
       <c r="L7" s="22" t="n">
-        <v>0.002</v>
+        <v>0.031</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         <v>5.98</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>5.982</v>
+        <v>5.949</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>0.002</v>
+        <v>0.031</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         <v>8.640000000000001</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>8.640000000000001</v>
+        <v>8.606999999999999</v>
       </c>
       <c r="L8" s="24" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
@@ -1819,10 +1819,10 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>8.640000000000001</v>
+        <v>8.606999999999999</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
         <v>11.7</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>11.83</v>
+        <v>11.864</v>
       </c>
       <c r="L9" s="22" t="n">
-        <v>0.13</v>
+        <v>0.164</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         <v>11.7</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>11.83</v>
+        <v>11.864</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>0.13</v>
+        <v>0.164</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -1888,10 +1888,10 @@
         <v>13.1</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>13.093</v>
+        <v>13.059</v>
       </c>
       <c r="L10" s="24" t="n">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         <v>13.1</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>13.093</v>
+        <v>13.059</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         <v>16.76</v>
       </c>
       <c r="K11" s="22" t="n">
-        <v>16.682</v>
+        <v>16.648</v>
       </c>
       <c r="L11" s="22" t="n">
-        <v>0.078</v>
+        <v>0.112</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
@@ -1984,10 +1984,10 @@
         <v>16.76</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>16.682</v>
+        <v>16.648</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>0.078</v>
+        <v>0.112</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         <v>20.68</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>20.67</v>
+        <v>20.637</v>
       </c>
       <c r="L12" s="24" t="n">
-        <v>0.01</v>
+        <v>0.043</v>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
         <v>20.68</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>20.67</v>
+        <v>20.637</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>0.01</v>
+        <v>0.043</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
         <v>22.01</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>21.799</v>
+        <v>21.766</v>
       </c>
       <c r="L13" s="22" t="n">
-        <v>0.211</v>
+        <v>0.244</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
@@ -2094,10 +2094,10 @@
         <v>22.01</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>21.799</v>
+        <v>21.766</v>
       </c>
       <c r="H14" s="24" t="n">
-        <v>0.211</v>
+        <v>0.244</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         <v>23.01</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>23.394</v>
+        <v>23.427</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>0.384</v>
+        <v>0.417</v>
       </c>
       <c r="M14" s="9" t="inlineStr">
         <is>
@@ -2149,10 +2149,10 @@
         <v>23.01</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>23.394</v>
+        <v>23.427</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>0.384</v>
+        <v>0.417</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -2163,10 +2163,10 @@
         <v>24.01</v>
       </c>
       <c r="K15" s="22" t="n">
-        <v>23.993</v>
+        <v>24.026</v>
       </c>
       <c r="L15" s="22" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
@@ -2204,10 +2204,10 @@
         <v>24.01</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>23.993</v>
+        <v>24.026</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         <v>26.6</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>26.585</v>
+        <v>26.552</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>0.015</v>
+        <v>0.048</v>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         <v>26.6</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>26.585</v>
+        <v>26.552</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>0.015</v>
+        <v>0.048</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
@@ -2273,10 +2273,10 @@
         <v>28.01</v>
       </c>
       <c r="K17" s="22" t="n">
-        <v>27.98</v>
+        <v>27.947</v>
       </c>
       <c r="L17" s="22" t="n">
-        <v>0.03</v>
+        <v>0.063</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
@@ -2314,10 +2314,10 @@
         <v>28.01</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>27.98</v>
+        <v>27.947</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>0.03</v>
+        <v>0.063</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -2328,10 +2328,10 @@
         <v>31.71</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>31.702</v>
+        <v>31.736</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>0.008</v>
+        <v>0.026</v>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
         <v>31.71</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>31.702</v>
+        <v>31.736</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>0.008</v>
+        <v>0.026</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -2383,10 +2383,10 @@
         <v>32.44</v>
       </c>
       <c r="K19" s="22" t="n">
-        <v>32.699</v>
+        <v>32.733</v>
       </c>
       <c r="L19" s="22" t="n">
-        <v>0.259</v>
+        <v>0.293</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
         <v>32.44</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>32.699</v>
+        <v>32.733</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>0.259</v>
+        <v>0.293</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -2438,10 +2438,10 @@
         <v>34.01</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>34.294</v>
+        <v>34.328</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>0.284</v>
+        <v>0.318</v>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
         <v>34.01</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>34.294</v>
+        <v>34.328</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>0.284</v>
+        <v>0.318</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
         <v>36.1</v>
       </c>
       <c r="K21" s="22" t="n">
-        <v>36.354</v>
+        <v>36.388</v>
       </c>
       <c r="L21" s="22" t="n">
-        <v>0.254</v>
+        <v>0.288</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         <v>36.1</v>
       </c>
       <c r="G22" s="24" t="n">
-        <v>36.354</v>
+        <v>36.388</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>0.254</v>
+        <v>0.288</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -2548,10 +2548,10 @@
         <v>41.01</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>41.273</v>
+        <v>41.306</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.263</v>
+        <v>0.296</v>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
@@ -2589,10 +2589,10 @@
         <v>41.01</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>41.273</v>
+        <v>41.306</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>0.263</v>
+        <v>0.296</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
@@ -2603,10 +2603,10 @@
         <v>42.48</v>
       </c>
       <c r="K23" s="22" t="n">
-        <v>42.469</v>
+        <v>42.436</v>
       </c>
       <c r="L23" s="22" t="n">
-        <v>0.011</v>
+        <v>0.044</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
         <v>42.48</v>
       </c>
       <c r="G24" s="24" t="n">
-        <v>42.469</v>
+        <v>42.436</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>0.011</v>
+        <v>0.044</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
         <v>46</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>45.991</v>
+        <v>46.025</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         <v>46</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>45.991</v>
+        <v>46.025</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
@@ -2713,10 +2713,10 @@
         <v>46.6</v>
       </c>
       <c r="K25" s="22" t="n">
-        <v>46.59</v>
+        <v>46.556</v>
       </c>
       <c r="L25" s="22" t="n">
-        <v>0.01</v>
+        <v>0.044</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         <v>46.6</v>
       </c>
       <c r="G26" s="24" t="n">
-        <v>46.59</v>
+        <v>46.556</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>0.01</v>
+        <v>0.044</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -2768,10 +2768,10 @@
         <v>47.86</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>47.719</v>
+        <v>47.686</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>0.141</v>
+        <v>0.174</v>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
         <v>47.86</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>47.719</v>
+        <v>47.686</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>0.141</v>
+        <v>0.174</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
@@ -2823,10 +2823,10 @@
         <v>51.01</v>
       </c>
       <c r="K27" s="22" t="n">
-        <v>51.109</v>
+        <v>51.142</v>
       </c>
       <c r="L27" s="22" t="n">
-        <v>0.099</v>
+        <v>0.132</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
@@ -2864,10 +2864,10 @@
         <v>51.01</v>
       </c>
       <c r="G28" s="24" t="n">
-        <v>51.109</v>
+        <v>51.142</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>0.099</v>
+        <v>0.132</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
@@ -2878,10 +2878,10 @@
         <v>53.01</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>53.036</v>
+        <v>53.07</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.026</v>
+        <v>0.06</v>
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="22" t="n">
-        <v>1.138</v>
+        <v>1.171</v>
       </c>
       <c r="H29" s="22" t="n">
-        <v>0.138</v>
+        <v>0.171</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
         <v>8</v>
       </c>
       <c r="K29" s="22" t="n">
-        <v>8.102</v>
+        <v>8.135999999999999</v>
       </c>
       <c r="L29" s="22" t="n">
-        <v>0.102</v>
+        <v>0.136</v>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
@@ -2974,10 +2974,10 @@
         <v>8</v>
       </c>
       <c r="G30" s="24" t="n">
-        <v>8.102</v>
+        <v>8.135999999999999</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>0.102</v>
+        <v>0.136</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
         <v>17</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>17.075</v>
+        <v>17.108</v>
       </c>
       <c r="L30" s="24" t="n">
-        <v>0.075</v>
+        <v>0.108</v>
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
@@ -3029,10 +3029,10 @@
         <v>17</v>
       </c>
       <c r="G31" s="22" t="n">
-        <v>17.075</v>
+        <v>17.108</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>0.075</v>
+        <v>0.108</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>18</v>
       </c>
       <c r="K31" s="22" t="n">
-        <v>17.745</v>
+        <v>17.712</v>
       </c>
       <c r="L31" s="22" t="n">
-        <v>0.255</v>
+        <v>0.288</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         <v>18</v>
       </c>
       <c r="G32" s="24" t="n">
-        <v>17.745</v>
+        <v>17.712</v>
       </c>
       <c r="H32" s="24" t="n">
-        <v>0.255</v>
+        <v>0.288</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -3098,10 +3098,10 @@
         <v>20</v>
       </c>
       <c r="K32" s="24" t="n">
-        <v>19.62</v>
+        <v>19.587</v>
       </c>
       <c r="L32" s="24" t="n">
-        <v>0.38</v>
+        <v>0.413</v>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
         <v>20</v>
       </c>
       <c r="G33" s="22" t="n">
-        <v>19.62</v>
+        <v>19.587</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>0.38</v>
+        <v>0.413</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
         <v>21</v>
       </c>
       <c r="K33" s="22" t="n">
-        <v>21.16</v>
+        <v>21.194</v>
       </c>
       <c r="L33" s="22" t="n">
-        <v>0.16</v>
+        <v>0.194</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
@@ -3194,10 +3194,10 @@
         <v>21</v>
       </c>
       <c r="G34" s="24" t="n">
-        <v>21.16</v>
+        <v>21.194</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>0.16</v>
+        <v>0.194</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -3208,10 +3208,10 @@
         <v>24</v>
       </c>
       <c r="K34" s="24" t="n">
-        <v>24.24</v>
+        <v>24.273</v>
       </c>
       <c r="L34" s="24" t="n">
-        <v>0.24</v>
+        <v>0.273</v>
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         <v>24</v>
       </c>
       <c r="G35" s="22" t="n">
-        <v>24.24</v>
+        <v>24.273</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>0.24</v>
+        <v>0.273</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
@@ -3263,10 +3263,10 @@
         <v>26</v>
       </c>
       <c r="K35" s="22" t="n">
-        <v>26.316</v>
+        <v>26.349</v>
       </c>
       <c r="L35" s="22" t="n">
-        <v>0.316</v>
+        <v>0.349</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
@@ -3304,10 +3304,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="24" t="n">
-        <v>26.316</v>
+        <v>26.349</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>0.316</v>
+        <v>0.349</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -3318,10 +3318,10 @@
         <v>27</v>
       </c>
       <c r="K36" s="24" t="n">
-        <v>26.383</v>
+        <v>26.349</v>
       </c>
       <c r="L36" s="24" t="n">
-        <v>0.617</v>
+        <v>0.651</v>
       </c>
       <c r="M36" s="9" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         <v>27</v>
       </c>
       <c r="G37" s="22" t="n">
-        <v>26.383</v>
+        <v>26.349</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>0.617</v>
+        <v>0.651</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
         <v>28</v>
       </c>
       <c r="K37" s="22" t="n">
-        <v>27.856</v>
+        <v>27.823</v>
       </c>
       <c r="L37" s="22" t="n">
-        <v>0.144</v>
+        <v>0.177</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>28</v>
       </c>
       <c r="G38" s="24" t="n">
-        <v>27.856</v>
+        <v>27.823</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>0.144</v>
+        <v>0.177</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
@@ -3428,10 +3428,10 @@
         <v>29</v>
       </c>
       <c r="K38" s="24" t="n">
-        <v>28.927</v>
+        <v>28.893</v>
       </c>
       <c r="L38" s="24" t="n">
-        <v>0.073</v>
+        <v>0.107</v>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
@@ -3469,10 +3469,10 @@
         <v>29</v>
       </c>
       <c r="G39" s="22" t="n">
-        <v>28.927</v>
+        <v>28.893</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>0.073</v>
+        <v>0.107</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
@@ -3483,10 +3483,10 @@
         <v>30</v>
       </c>
       <c r="K39" s="22" t="n">
-        <v>30.333</v>
+        <v>30.366</v>
       </c>
       <c r="L39" s="22" t="n">
-        <v>0.333</v>
+        <v>0.366</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
@@ -3524,10 +3524,10 @@
         <v>30</v>
       </c>
       <c r="G40" s="24" t="n">
-        <v>30.333</v>
+        <v>30.366</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>0.333</v>
+        <v>0.366</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -3538,10 +3538,10 @@
         <v>37</v>
       </c>
       <c r="K40" s="24" t="n">
-        <v>37.163</v>
+        <v>37.197</v>
       </c>
       <c r="L40" s="24" t="n">
-        <v>0.163</v>
+        <v>0.197</v>
       </c>
       <c r="M40" s="9" t="inlineStr">
         <is>
@@ -3579,10 +3579,10 @@
         <v>37</v>
       </c>
       <c r="G41" s="22" t="n">
-        <v>37.163</v>
+        <v>37.197</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>0.163</v>
+        <v>0.197</v>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
@@ -3593,10 +3593,10 @@
         <v>38</v>
       </c>
       <c r="K41" s="22" t="n">
-        <v>37.967</v>
+        <v>37.933</v>
       </c>
       <c r="L41" s="22" t="n">
-        <v>0.033</v>
+        <v>0.067</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         <v>38</v>
       </c>
       <c r="G42" s="24" t="n">
-        <v>37.967</v>
+        <v>37.933</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>0.033</v>
+        <v>0.067</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
         <v>42</v>
       </c>
       <c r="K42" s="24" t="n">
-        <v>42.52</v>
+        <v>42.553</v>
       </c>
       <c r="L42" s="24" t="n">
-        <v>0.52</v>
+        <v>0.553</v>
       </c>
       <c r="M42" s="9" t="inlineStr">
         <is>
@@ -3689,10 +3689,10 @@
         <v>42</v>
       </c>
       <c r="G43" s="22" t="n">
-        <v>42.52</v>
+        <v>42.553</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>0.52</v>
+        <v>0.553</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         <v>43</v>
       </c>
       <c r="K43" s="22" t="n">
-        <v>43.391</v>
+        <v>43.424</v>
       </c>
       <c r="L43" s="22" t="n">
-        <v>0.391</v>
+        <v>0.424</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         <v>43</v>
       </c>
       <c r="G44" s="24" t="n">
-        <v>43.391</v>
+        <v>43.424</v>
       </c>
       <c r="H44" s="24" t="n">
-        <v>0.391</v>
+        <v>0.424</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -3758,10 +3758,10 @@
         <v>45</v>
       </c>
       <c r="K44" s="24" t="n">
-        <v>45.065</v>
+        <v>45.099</v>
       </c>
       <c r="L44" s="24" t="n">
-        <v>0.065</v>
+        <v>0.099</v>
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         <v>45</v>
       </c>
       <c r="G45" s="22" t="n">
-        <v>45.065</v>
+        <v>45.099</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>0.065</v>
+        <v>0.099</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         <v>48</v>
       </c>
       <c r="K45" s="22" t="n">
-        <v>48.145</v>
+        <v>48.178</v>
       </c>
       <c r="L45" s="22" t="n">
-        <v>0.145</v>
+        <v>0.178</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
@@ -3854,10 +3854,10 @@
         <v>48</v>
       </c>
       <c r="G46" s="24" t="n">
-        <v>48.145</v>
+        <v>48.178</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>0.145</v>
+        <v>0.178</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -3868,10 +3868,10 @@
         <v>49</v>
       </c>
       <c r="K46" s="24" t="n">
-        <v>49.016</v>
+        <v>48.983</v>
       </c>
       <c r="L46" s="24" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
@@ -3909,10 +3909,10 @@
         <v>49</v>
       </c>
       <c r="G47" s="22" t="n">
-        <v>49.016</v>
+        <v>48.983</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         <v>52</v>
       </c>
       <c r="K47" s="22" t="n">
-        <v>52.297</v>
+        <v>52.331</v>
       </c>
       <c r="L47" s="22" t="n">
-        <v>0.297</v>
+        <v>0.331</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
@@ -3964,10 +3964,10 @@
         <v>52</v>
       </c>
       <c r="G48" s="24" t="n">
-        <v>52.297</v>
+        <v>52.331</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>0.297</v>
+        <v>0.331</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -3978,10 +3978,10 @@
         <v>53</v>
       </c>
       <c r="K48" s="24" t="n">
-        <v>53.167</v>
+        <v>53.201</v>
       </c>
       <c r="L48" s="24" t="n">
-        <v>0.167</v>
+        <v>0.201</v>
       </c>
       <c r="M48" s="9" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         <v>53</v>
       </c>
       <c r="G49" s="22" t="n">
-        <v>53.167</v>
+        <v>53.201</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>0.167</v>
+        <v>0.201</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -4033,10 +4033,10 @@
         <v>58</v>
       </c>
       <c r="K49" s="22" t="n">
-        <v>58.323</v>
+        <v>58.356</v>
       </c>
       <c r="L49" s="22" t="n">
-        <v>0.323</v>
+        <v>0.356</v>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
@@ -4074,10 +4074,10 @@
         <v>58</v>
       </c>
       <c r="G50" s="24" t="n">
-        <v>58.323</v>
+        <v>58.356</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>0.323</v>
+        <v>0.356</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -4088,10 +4088,10 @@
         <v>60</v>
       </c>
       <c r="K50" s="24" t="n">
-        <v>60.265</v>
+        <v>60.299</v>
       </c>
       <c r="L50" s="24" t="n">
-        <v>0.265</v>
+        <v>0.299</v>
       </c>
       <c r="M50" s="9" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
         <v>60</v>
       </c>
       <c r="G51" s="22" t="n">
-        <v>60.265</v>
+        <v>60.299</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>0.265</v>
+        <v>0.299</v>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
@@ -4143,10 +4143,10 @@
         <v>63</v>
       </c>
       <c r="K51" s="22" t="n">
-        <v>62.81</v>
+        <v>62.776</v>
       </c>
       <c r="L51" s="22" t="n">
-        <v>0.19</v>
+        <v>0.224</v>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
         <v>63</v>
       </c>
       <c r="G52" s="24" t="n">
-        <v>62.81</v>
+        <v>62.776</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>0.19</v>
+        <v>0.224</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>64</v>
       </c>
       <c r="K52" s="24" t="n">
-        <v>64.283</v>
+        <v>64.316</v>
       </c>
       <c r="L52" s="24" t="n">
-        <v>0.283</v>
+        <v>0.316</v>
       </c>
       <c r="M52" s="9" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         <v>64</v>
       </c>
       <c r="G53" s="22" t="n">
-        <v>64.283</v>
+        <v>64.316</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>0.283</v>
+        <v>0.316</v>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
@@ -4253,10 +4253,10 @@
         <v>85</v>
       </c>
       <c r="K53" s="22" t="n">
-        <v>84.907</v>
+        <v>84.874</v>
       </c>
       <c r="L53" s="22" t="n">
-        <v>0.093</v>
+        <v>0.126</v>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
@@ -4294,10 +4294,10 @@
         <v>85</v>
       </c>
       <c r="G54" s="24" t="n">
-        <v>84.907</v>
+        <v>84.874</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>0.093</v>
+        <v>0.126</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
@@ -4308,10 +4308,10 @@
         <v>90</v>
       </c>
       <c r="K54" s="24" t="n">
-        <v>89.86199999999999</v>
+        <v>89.828</v>
       </c>
       <c r="L54" s="24" t="n">
-        <v>0.138</v>
+        <v>0.172</v>
       </c>
       <c r="M54" s="9" t="inlineStr">
         <is>
@@ -4349,10 +4349,10 @@
         <v>90</v>
       </c>
       <c r="G55" s="22" t="n">
-        <v>89.86199999999999</v>
+        <v>89.828</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>0.138</v>
+        <v>0.172</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
@@ -4363,10 +4363,10 @@
         <v>91</v>
       </c>
       <c r="K55" s="22" t="n">
-        <v>90.732</v>
+        <v>90.69799999999999</v>
       </c>
       <c r="L55" s="22" t="n">
-        <v>0.268</v>
+        <v>0.302</v>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
@@ -4404,10 +4404,10 @@
         <v>91</v>
       </c>
       <c r="G56" s="24" t="n">
-        <v>90.732</v>
+        <v>90.69799999999999</v>
       </c>
       <c r="H56" s="24" t="n">
-        <v>0.268</v>
+        <v>0.302</v>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
@@ -4418,10 +4418,10 @@
         <v>95</v>
       </c>
       <c r="K56" s="24" t="n">
-        <v>95.018</v>
+        <v>94.98399999999999</v>
       </c>
       <c r="L56" s="24" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="M56" s="9" t="inlineStr">
         <is>
@@ -4459,10 +4459,10 @@
         <v>95</v>
       </c>
       <c r="G57" s="22" t="n">
-        <v>95.018</v>
+        <v>94.98399999999999</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>0.018</v>
+        <v>0.016</v>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
         <v>96</v>
       </c>
       <c r="K57" s="22" t="n">
-        <v>96.357</v>
+        <v>96.39100000000001</v>
       </c>
       <c r="L57" s="22" t="n">
-        <v>0.357</v>
+        <v>0.391</v>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
         <v>96</v>
       </c>
       <c r="G58" s="24" t="n">
-        <v>96.357</v>
+        <v>96.39100000000001</v>
       </c>
       <c r="H58" s="24" t="n">
-        <v>0.357</v>
+        <v>0.391</v>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
         <v>97</v>
       </c>
       <c r="K58" s="24" t="n">
-        <v>96.95999999999999</v>
+        <v>96.92700000000001</v>
       </c>
       <c r="L58" s="24" t="n">
-        <v>0.04</v>
+        <v>0.073</v>
       </c>
       <c r="M58" s="9" t="inlineStr">
         <is>
@@ -4569,10 +4569,10 @@
         <v>97</v>
       </c>
       <c r="G59" s="22" t="n">
-        <v>96.95999999999999</v>
+        <v>96.92700000000001</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>0.04</v>
+        <v>0.073</v>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
@@ -4583,10 +4583,10 @@
         <v>102</v>
       </c>
       <c r="K59" s="22" t="n">
-        <v>101.647</v>
+        <v>101.614</v>
       </c>
       <c r="L59" s="22" t="n">
-        <v>0.353</v>
+        <v>0.386</v>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
@@ -4624,10 +4624,10 @@
         <v>102</v>
       </c>
       <c r="G60" s="24" t="n">
-        <v>101.647</v>
+        <v>101.614</v>
       </c>
       <c r="H60" s="24" t="n">
-        <v>0.353</v>
+        <v>0.386</v>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
@@ -4638,10 +4638,10 @@
         <v>105</v>
       </c>
       <c r="K60" s="24" t="n">
-        <v>104.995</v>
+        <v>105.029</v>
       </c>
       <c r="L60" s="24" t="n">
-        <v>0.005</v>
+        <v>0.029</v>
       </c>
       <c r="M60" s="9" t="inlineStr">
         <is>
@@ -4679,10 +4679,10 @@
         <v>105</v>
       </c>
       <c r="G61" s="22" t="n">
-        <v>104.995</v>
+        <v>105.029</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>0.005</v>
+        <v>0.029</v>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
@@ -4693,10 +4693,10 @@
         <v>108</v>
       </c>
       <c r="K61" s="22" t="n">
-        <v>108.142</v>
+        <v>108.175</v>
       </c>
       <c r="L61" s="22" t="n">
-        <v>0.142</v>
+        <v>0.175</v>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
@@ -4734,10 +4734,10 @@
         <v>108</v>
       </c>
       <c r="G62" s="24" t="n">
-        <v>108.142</v>
+        <v>108.175</v>
       </c>
       <c r="H62" s="24" t="n">
-        <v>0.142</v>
+        <v>0.175</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
@@ -4748,10 +4748,10 @@
         <v>112</v>
       </c>
       <c r="K62" s="24" t="n">
-        <v>112.629</v>
+        <v>112.662</v>
       </c>
       <c r="L62" s="24" t="n">
-        <v>0.629</v>
+        <v>0.662</v>
       </c>
       <c r="M62" s="9" t="inlineStr">
         <is>
@@ -4789,10 +4789,10 @@
         <v>112</v>
       </c>
       <c r="G63" s="22" t="n">
-        <v>112.629</v>
+        <v>112.662</v>
       </c>
       <c r="H63" s="22" t="n">
-        <v>0.629</v>
+        <v>0.662</v>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
@@ -4803,10 +4803,10 @@
         <v>113</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>113.298</v>
+        <v>113.332</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>0.298</v>
+        <v>0.332</v>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
@@ -4844,10 +4844,10 @@
         <v>113</v>
       </c>
       <c r="G64" s="24" t="n">
-        <v>113.298</v>
+        <v>113.332</v>
       </c>
       <c r="H64" s="24" t="n">
-        <v>0.298</v>
+        <v>0.332</v>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
@@ -4858,10 +4858,10 @@
         <v>115</v>
       </c>
       <c r="K64" s="24" t="n">
-        <v>115.039</v>
+        <v>115.072</v>
       </c>
       <c r="L64" s="24" t="n">
-        <v>0.039</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="M64" s="9" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
         <v>115</v>
       </c>
       <c r="G65" s="22" t="n">
-        <v>115.039</v>
+        <v>115.072</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>0.039</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
@@ -4913,10 +4913,10 @@
         <v>121</v>
       </c>
       <c r="K65" s="22" t="n">
-        <v>121.066</v>
+        <v>121.1</v>
       </c>
       <c r="L65" s="22" t="n">
-        <v>0.066</v>
+        <v>0.1</v>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
@@ -4954,10 +4954,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="24" t="n">
-        <v>1.125</v>
+        <v>1.158</v>
       </c>
       <c r="H66" s="24" t="n">
-        <v>0.125</v>
+        <v>0.158</v>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
@@ -4968,10 +4968,10 @@
         <v>4</v>
       </c>
       <c r="K66" s="24" t="n">
-        <v>4.235</v>
+        <v>4.268</v>
       </c>
       <c r="L66" s="24" t="n">
-        <v>0.235</v>
+        <v>0.268</v>
       </c>
       <c r="M66" s="9" t="inlineStr">
         <is>
@@ -5009,10 +5009,10 @@
         <v>4</v>
       </c>
       <c r="G67" s="22" t="n">
-        <v>4.235</v>
+        <v>4.268</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>0.235</v>
+        <v>0.268</v>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
         <v>6</v>
       </c>
       <c r="K67" s="22" t="n">
-        <v>5.691</v>
+        <v>5.658</v>
       </c>
       <c r="L67" s="22" t="n">
-        <v>0.309</v>
+        <v>0.342</v>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         <v>6</v>
       </c>
       <c r="G68" s="24" t="n">
-        <v>5.691</v>
+        <v>5.658</v>
       </c>
       <c r="H68" s="24" t="n">
-        <v>0.309</v>
+        <v>0.342</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -5078,10 +5078,10 @@
         <v>8</v>
       </c>
       <c r="K68" s="24" t="n">
-        <v>7.742</v>
+        <v>7.709</v>
       </c>
       <c r="L68" s="24" t="n">
-        <v>0.258</v>
+        <v>0.291</v>
       </c>
       <c r="M68" s="9" t="inlineStr">
         <is>
@@ -5119,10 +5119,10 @@
         <v>8</v>
       </c>
       <c r="G69" s="22" t="n">
-        <v>7.742</v>
+        <v>7.709</v>
       </c>
       <c r="H69" s="22" t="n">
-        <v>0.258</v>
+        <v>0.291</v>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
         <v>12</v>
       </c>
       <c r="K69" s="22" t="n">
-        <v>11.779</v>
+        <v>11.745</v>
       </c>
       <c r="L69" s="22" t="n">
-        <v>0.221</v>
+        <v>0.255</v>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
@@ -5174,10 +5174,10 @@
         <v>12</v>
       </c>
       <c r="G70" s="24" t="n">
-        <v>11.779</v>
+        <v>11.745</v>
       </c>
       <c r="H70" s="24" t="n">
-        <v>0.221</v>
+        <v>0.255</v>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
@@ -5188,10 +5188,10 @@
         <v>13</v>
       </c>
       <c r="K70" s="24" t="n">
-        <v>13.565</v>
+        <v>13.598</v>
       </c>
       <c r="L70" s="24" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.598</v>
       </c>
       <c r="M70" s="9" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         <v>13</v>
       </c>
       <c r="G71" s="22" t="n">
-        <v>13.565</v>
+        <v>13.598</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.598</v>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
@@ -5243,10 +5243,10 @@
         <v>14</v>
       </c>
       <c r="K71" s="22" t="n">
-        <v>14.227</v>
+        <v>14.26</v>
       </c>
       <c r="L71" s="22" t="n">
-        <v>0.227</v>
+        <v>0.26</v>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         <v>14</v>
       </c>
       <c r="G72" s="24" t="n">
-        <v>14.227</v>
+        <v>14.26</v>
       </c>
       <c r="H72" s="24" t="n">
-        <v>0.227</v>
+        <v>0.26</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
@@ -5298,10 +5298,10 @@
         <v>20</v>
       </c>
       <c r="K72" s="24" t="n">
-        <v>19.852</v>
+        <v>19.819</v>
       </c>
       <c r="L72" s="24" t="n">
-        <v>0.148</v>
+        <v>0.181</v>
       </c>
       <c r="M72" s="9" t="inlineStr">
         <is>
@@ -5339,10 +5339,10 @@
         <v>20</v>
       </c>
       <c r="G73" s="22" t="n">
-        <v>19.852</v>
+        <v>19.819</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>0.148</v>
+        <v>0.181</v>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
@@ -5353,10 +5353,10 @@
         <v>23</v>
       </c>
       <c r="K73" s="22" t="n">
-        <v>22.498</v>
+        <v>22.465</v>
       </c>
       <c r="L73" s="22" t="n">
-        <v>0.502</v>
+        <v>0.535</v>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
@@ -5394,10 +5394,10 @@
         <v>23</v>
       </c>
       <c r="G74" s="24" t="n">
-        <v>22.498</v>
+        <v>22.465</v>
       </c>
       <c r="H74" s="24" t="n">
-        <v>0.502</v>
+        <v>0.535</v>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
         <v>25</v>
       </c>
       <c r="K74" s="24" t="n">
-        <v>25.41</v>
+        <v>25.443</v>
       </c>
       <c r="L74" s="24" t="n">
-        <v>0.41</v>
+        <v>0.443</v>
       </c>
       <c r="M74" s="9" t="inlineStr">
         <is>
@@ -5449,10 +5449,10 @@
         <v>25</v>
       </c>
       <c r="G75" s="22" t="n">
-        <v>25.41</v>
+        <v>25.443</v>
       </c>
       <c r="H75" s="22" t="n">
-        <v>0.41</v>
+        <v>0.443</v>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
@@ -5463,10 +5463,10 @@
         <v>28</v>
       </c>
       <c r="K75" s="22" t="n">
-        <v>27.726</v>
+        <v>27.693</v>
       </c>
       <c r="L75" s="22" t="n">
-        <v>0.274</v>
+        <v>0.307</v>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         <v>28</v>
       </c>
       <c r="G76" s="24" t="n">
-        <v>27.726</v>
+        <v>27.693</v>
       </c>
       <c r="H76" s="24" t="n">
-        <v>0.274</v>
+        <v>0.307</v>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
@@ -5518,10 +5518,10 @@
         <v>30</v>
       </c>
       <c r="K76" s="24" t="n">
-        <v>30.307</v>
+        <v>30.34</v>
       </c>
       <c r="L76" s="24" t="n">
-        <v>0.307</v>
+        <v>0.34</v>
       </c>
       <c r="M76" s="9" t="inlineStr">
         <is>
@@ -5559,10 +5559,10 @@
         <v>30</v>
       </c>
       <c r="G77" s="22" t="n">
-        <v>30.307</v>
+        <v>30.34</v>
       </c>
       <c r="H77" s="22" t="n">
-        <v>0.307</v>
+        <v>0.34</v>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
@@ -5573,10 +5573,10 @@
         <v>35</v>
       </c>
       <c r="K77" s="22" t="n">
-        <v>35.336</v>
+        <v>35.369</v>
       </c>
       <c r="L77" s="22" t="n">
-        <v>0.336</v>
+        <v>0.369</v>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
@@ -5614,10 +5614,10 @@
         <v>35</v>
       </c>
       <c r="G78" s="24" t="n">
-        <v>35.336</v>
+        <v>35.369</v>
       </c>
       <c r="H78" s="24" t="n">
-        <v>0.336</v>
+        <v>0.369</v>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
@@ -5628,10 +5628,10 @@
         <v>36</v>
       </c>
       <c r="K78" s="24" t="n">
-        <v>36.064</v>
+        <v>36.097</v>
       </c>
       <c r="L78" s="24" t="n">
-        <v>0.064</v>
+        <v>0.097</v>
       </c>
       <c r="M78" s="9" t="inlineStr">
         <is>
@@ -5669,10 +5669,10 @@
         <v>36</v>
       </c>
       <c r="G79" s="22" t="n">
-        <v>36.064</v>
+        <v>36.097</v>
       </c>
       <c r="H79" s="22" t="n">
-        <v>0.064</v>
+        <v>0.097</v>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="24" t="n">
-        <v>1</v>
+        <v>1.033</v>
       </c>
       <c r="H80" s="24" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
@@ -5738,10 +5738,10 @@
         <v>3</v>
       </c>
       <c r="K80" s="24" t="n">
-        <v>3.399</v>
+        <v>3.433</v>
       </c>
       <c r="L80" s="24" t="n">
-        <v>0.399</v>
+        <v>0.433</v>
       </c>
       <c r="M80" s="9" t="inlineStr">
         <is>
@@ -5779,10 +5779,10 @@
         <v>3</v>
       </c>
       <c r="G81" s="22" t="n">
-        <v>3.399</v>
+        <v>3.433</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>0.399</v>
+        <v>0.433</v>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
@@ -5793,10 +5793,10 @@
         <v>7</v>
       </c>
       <c r="K81" s="22" t="n">
-        <v>6.999</v>
+        <v>6.966</v>
       </c>
       <c r="L81" s="22" t="n">
-        <v>0.001</v>
+        <v>0.034</v>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
@@ -5834,10 +5834,10 @@
         <v>7</v>
       </c>
       <c r="G82" s="24" t="n">
-        <v>6.999</v>
+        <v>6.966</v>
       </c>
       <c r="H82" s="24" t="n">
-        <v>0.001</v>
+        <v>0.034</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
@@ -5848,10 +5848,10 @@
         <v>10</v>
       </c>
       <c r="K82" s="24" t="n">
-        <v>9.997999999999999</v>
+        <v>9.964</v>
       </c>
       <c r="L82" s="24" t="n">
-        <v>0.002</v>
+        <v>0.036</v>
       </c>
       <c r="M82" s="9" t="inlineStr">
         <is>
@@ -5889,10 +5889,10 @@
         <v>10</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>9.997999999999999</v>
+        <v>9.964</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0.002</v>
+        <v>0.036</v>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
@@ -5903,10 +5903,10 @@
         <v>13</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>13.797</v>
+        <v>13.831</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>0.797</v>
+        <v>0.831</v>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
@@ -5944,10 +5944,10 @@
         <v>13</v>
       </c>
       <c r="G84" s="24" t="n">
-        <v>13.797</v>
+        <v>13.831</v>
       </c>
       <c r="H84" s="24" t="n">
-        <v>0.797</v>
+        <v>0.831</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>15</v>
       </c>
       <c r="K84" s="24" t="n">
-        <v>15.264</v>
+        <v>15.297</v>
       </c>
       <c r="L84" s="24" t="n">
-        <v>0.264</v>
+        <v>0.297</v>
       </c>
       <c r="M84" s="9" t="inlineStr">
         <is>
@@ -5999,10 +5999,10 @@
         <v>15</v>
       </c>
       <c r="G85" s="22" t="n">
-        <v>15.264</v>
+        <v>15.297</v>
       </c>
       <c r="H85" s="22" t="n">
-        <v>0.264</v>
+        <v>0.297</v>
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
@@ -6013,10 +6013,10 @@
         <v>18</v>
       </c>
       <c r="K85" s="22" t="n">
-        <v>17.73</v>
+        <v>17.697</v>
       </c>
       <c r="L85" s="22" t="n">
-        <v>0.27</v>
+        <v>0.303</v>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
@@ -6054,10 +6054,10 @@
         <v>18</v>
       </c>
       <c r="G86" s="24" t="n">
-        <v>17.73</v>
+        <v>17.697</v>
       </c>
       <c r="H86" s="24" t="n">
-        <v>0.27</v>
+        <v>0.303</v>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         <v>20</v>
       </c>
       <c r="K86" s="24" t="n">
-        <v>20.596</v>
+        <v>20.629</v>
       </c>
       <c r="L86" s="24" t="n">
-        <v>0.596</v>
+        <v>0.629</v>
       </c>
       <c r="M86" s="9" t="inlineStr">
         <is>
@@ -6109,10 +6109,10 @@
         <v>20</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>20.596</v>
+        <v>20.629</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>0.596</v>
+        <v>0.629</v>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
@@ -6123,10 +6123,10 @@
         <v>24</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>24.062</v>
+        <v>24.095</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>0.062</v>
+        <v>0.095</v>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
@@ -6164,10 +6164,10 @@
         <v>24</v>
       </c>
       <c r="G88" s="24" t="n">
-        <v>24.062</v>
+        <v>24.095</v>
       </c>
       <c r="H88" s="24" t="n">
-        <v>0.062</v>
+        <v>0.095</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         <v>26</v>
       </c>
       <c r="K88" s="24" t="n">
-        <v>27.061</v>
+        <v>27.095</v>
       </c>
       <c r="L88" s="24" t="n">
-        <v>1.061</v>
+        <v>1.095</v>
       </c>
       <c r="M88" s="9" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>27.061</v>
+        <v>27.095</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>1.061</v>
+        <v>1.095</v>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
@@ -6233,10 +6233,10 @@
         <v>27</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>27.061</v>
+        <v>27.095</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>0.061</v>
+        <v>0.095</v>
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
@@ -6274,10 +6274,10 @@
         <v>27</v>
       </c>
       <c r="G90" s="24" t="n">
-        <v>27.061</v>
+        <v>27.095</v>
       </c>
       <c r="H90" s="24" t="n">
-        <v>0.061</v>
+        <v>0.095</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>29</v>
       </c>
       <c r="K90" s="24" t="n">
-        <v>28.994</v>
+        <v>29.027</v>
       </c>
       <c r="L90" s="24" t="n">
-        <v>0.006</v>
+        <v>0.027</v>
       </c>
       <c r="M90" s="9" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>8</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>7.443</v>
+        <v>7.409</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.591</v>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
@@ -6343,10 +6343,10 @@
         <v>9</v>
       </c>
       <c r="K91" s="22" t="n">
-        <v>8.877000000000001</v>
+        <v>8.843</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>0.123</v>
+        <v>0.157</v>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>9</v>
       </c>
       <c r="G92" s="24" t="n">
-        <v>8.877000000000001</v>
+        <v>8.843</v>
       </c>
       <c r="H92" s="24" t="n">
-        <v>0.123</v>
+        <v>0.157</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -6398,10 +6398,10 @@
         <v>10</v>
       </c>
       <c r="K92" s="24" t="n">
-        <v>9.628</v>
+        <v>9.593</v>
       </c>
       <c r="L92" s="24" t="n">
-        <v>0.372</v>
+        <v>0.407</v>
       </c>
       <c r="M92" s="9" t="inlineStr">
         <is>
@@ -6439,10 +6439,10 @@
         <v>10</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>9.628</v>
+        <v>9.593</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>0.372</v>
+        <v>0.407</v>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
@@ -6453,10 +6453,10 @@
         <v>16</v>
       </c>
       <c r="K93" s="22" t="n">
-        <v>15.978</v>
+        <v>15.944</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>0.022</v>
+        <v>0.056</v>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
@@ -6494,10 +6494,10 @@
         <v>16</v>
       </c>
       <c r="G94" s="24" t="n">
-        <v>15.978</v>
+        <v>15.944</v>
       </c>
       <c r="H94" s="24" t="n">
-        <v>0.022</v>
+        <v>0.056</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -6508,10 +6508,10 @@
         <v>17</v>
       </c>
       <c r="K94" s="24" t="n">
-        <v>17.002</v>
+        <v>17.036</v>
       </c>
       <c r="L94" s="24" t="n">
-        <v>0.002</v>
+        <v>0.036</v>
       </c>
       <c r="M94" s="9" t="inlineStr">
         <is>
@@ -6549,10 +6549,10 @@
         <v>17</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>17.002</v>
+        <v>17.036</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>0.002</v>
+        <v>0.036</v>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
@@ -6563,10 +6563,10 @@
         <v>18</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>18.026</v>
+        <v>17.992</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>0.026</v>
+        <v>0.008</v>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
@@ -6604,10 +6604,10 @@
         <v>18</v>
       </c>
       <c r="G96" s="24" t="n">
-        <v>18.026</v>
+        <v>17.992</v>
       </c>
       <c r="H96" s="24" t="n">
-        <v>0.026</v>
+        <v>0.008</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
         <v>25</v>
       </c>
       <c r="K96" s="24" t="n">
-        <v>24.923</v>
+        <v>24.889</v>
       </c>
       <c r="L96" s="24" t="n">
-        <v>0.077</v>
+        <v>0.111</v>
       </c>
       <c r="M96" s="9" t="inlineStr">
         <is>
@@ -6659,10 +6659,10 @@
         <v>25</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>24.923</v>
+        <v>24.889</v>
       </c>
       <c r="H97" s="22" t="n">
-        <v>0.077</v>
+        <v>0.111</v>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
@@ -6673,10 +6673,10 @@
         <v>37</v>
       </c>
       <c r="K97" s="22" t="n">
-        <v>36.804</v>
+        <v>36.77</v>
       </c>
       <c r="L97" s="22" t="n">
-        <v>0.196</v>
+        <v>0.23</v>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
@@ -6714,10 +6714,10 @@
         <v>37</v>
       </c>
       <c r="G98" s="24" t="n">
-        <v>36.804</v>
+        <v>36.77</v>
       </c>
       <c r="H98" s="24" t="n">
-        <v>0.196</v>
+        <v>0.23</v>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
@@ -6728,22 +6728,22 @@
         <v>39</v>
       </c>
       <c r="K98" s="24" t="n">
-        <v>39.467</v>
+        <v>39.501</v>
       </c>
       <c r="L98" s="24" t="n">
-        <v>0.467</v>
+        <v>0.501</v>
       </c>
       <c r="M98" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N98" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O98" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O98" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc Start</t>
         </is>
       </c>
     </row>
@@ -6769,24 +6769,24 @@
         <v>39</v>
       </c>
       <c r="G99" s="22" t="n">
-        <v>39.467</v>
+        <v>39.501</v>
       </c>
       <c r="H99" s="22" t="n">
-        <v>0.467</v>
+        <v>0.501</v>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="J99" s="22" t="n">
         <v>41</v>
       </c>
       <c r="K99" s="22" t="n">
-        <v>40.969</v>
+        <v>40.934</v>
       </c>
       <c r="L99" s="22" t="n">
-        <v>0.031</v>
+        <v>0.066</v>
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
@@ -6796,9 +6796,9 @@
       <c r="N99" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="O99" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O99" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc End</t>
         </is>
       </c>
     </row>
@@ -6824,10 +6824,10 @@
         <v>41</v>
       </c>
       <c r="G100" s="24" t="n">
-        <v>40.969</v>
+        <v>40.934</v>
       </c>
       <c r="H100" s="24" t="n">
-        <v>0.031</v>
+        <v>0.066</v>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
@@ -6838,10 +6838,10 @@
         <v>44</v>
       </c>
       <c r="K100" s="24" t="n">
-        <v>44.451</v>
+        <v>44.485</v>
       </c>
       <c r="L100" s="24" t="n">
-        <v>0.451</v>
+        <v>0.485</v>
       </c>
       <c r="M100" s="9" t="inlineStr">
         <is>
@@ -6879,10 +6879,10 @@
         <v>44</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>44.451</v>
+        <v>44.485</v>
       </c>
       <c r="H101" s="22" t="n">
-        <v>0.451</v>
+        <v>0.485</v>
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
@@ -6893,22 +6893,22 @@
         <v>45</v>
       </c>
       <c r="K101" s="22" t="n">
-        <v>45.475</v>
+        <v>45.51</v>
       </c>
       <c r="L101" s="22" t="n">
-        <v>0.475</v>
+        <v>0.51</v>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N101" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="O101" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O101" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc Start</t>
         </is>
       </c>
     </row>
@@ -6934,24 +6934,24 @@
         <v>45</v>
       </c>
       <c r="G102" s="24" t="n">
-        <v>45.475</v>
+        <v>45.51</v>
       </c>
       <c r="H102" s="24" t="n">
-        <v>0.475</v>
+        <v>0.51</v>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="J102" s="24" t="n">
         <v>47</v>
       </c>
       <c r="K102" s="24" t="n">
-        <v>46.431</v>
+        <v>46.397</v>
       </c>
       <c r="L102" s="24" t="n">
-        <v>0.569</v>
+        <v>0.603</v>
       </c>
       <c r="M102" s="9" t="inlineStr">
         <is>
@@ -6961,9 +6961,9 @@
       <c r="N102" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O102" s="25" t="inlineStr">
-        <is>
-          <t>Khớp mốc Start</t>
+      <c r="O102" s="26" t="inlineStr">
+        <is>
+          <t>Không khớp</t>
         </is>
       </c>
     </row>
@@ -6989,10 +6989,10 @@
         <v>47</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>46.431</v>
+        <v>46.397</v>
       </c>
       <c r="H103" s="22" t="n">
-        <v>0.569</v>
+        <v>0.603</v>
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
@@ -7003,10 +7003,10 @@
         <v>48</v>
       </c>
       <c r="K103" s="22" t="n">
-        <v>48.002</v>
+        <v>47.968</v>
       </c>
       <c r="L103" s="22" t="n">
-        <v>0.002</v>
+        <v>0.032</v>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
@@ -7044,10 +7044,10 @@
         <v>48</v>
       </c>
       <c r="G104" s="24" t="n">
-        <v>48.002</v>
+        <v>47.968</v>
       </c>
       <c r="H104" s="24" t="n">
-        <v>0.002</v>
+        <v>0.032</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -7058,10 +7058,10 @@
         <v>52</v>
       </c>
       <c r="K104" s="24" t="n">
-        <v>51.825</v>
+        <v>51.791</v>
       </c>
       <c r="L104" s="24" t="n">
-        <v>0.175</v>
+        <v>0.209</v>
       </c>
       <c r="M104" s="9" t="inlineStr">
         <is>
@@ -7099,10 +7099,10 @@
         <v>52</v>
       </c>
       <c r="G105" s="22" t="n">
-        <v>51.825</v>
+        <v>51.791</v>
       </c>
       <c r="H105" s="22" t="n">
-        <v>0.175</v>
+        <v>0.209</v>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
@@ -7113,10 +7113,10 @@
         <v>53</v>
       </c>
       <c r="K105" s="22" t="n">
-        <v>52.577</v>
+        <v>52.543</v>
       </c>
       <c r="L105" s="22" t="n">
-        <v>0.423</v>
+        <v>0.457</v>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
@@ -7154,10 +7154,10 @@
         <v>53</v>
       </c>
       <c r="G106" s="24" t="n">
-        <v>52.577</v>
+        <v>52.543</v>
       </c>
       <c r="H106" s="24" t="n">
-        <v>0.423</v>
+        <v>0.457</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
@@ -7168,10 +7168,10 @@
         <v>115</v>
       </c>
       <c r="K106" s="24" t="n">
-        <v>115.122</v>
+        <v>115.156</v>
       </c>
       <c r="L106" s="24" t="n">
-        <v>0.122</v>
+        <v>0.156</v>
       </c>
       <c r="M106" s="9" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         <v>115</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>115.122</v>
+        <v>115.156</v>
       </c>
       <c r="H107" s="22" t="n">
-        <v>0.122</v>
+        <v>0.156</v>
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
@@ -7223,10 +7223,10 @@
         <v>118</v>
       </c>
       <c r="K107" s="22" t="n">
-        <v>117.717</v>
+        <v>117.683</v>
       </c>
       <c r="L107" s="22" t="n">
-        <v>0.283</v>
+        <v>0.317</v>
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
@@ -7264,10 +7264,10 @@
         <v>118</v>
       </c>
       <c r="G108" s="24" t="n">
-        <v>117.717</v>
+        <v>117.683</v>
       </c>
       <c r="H108" s="24" t="n">
-        <v>0.283</v>
+        <v>0.317</v>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
@@ -7278,10 +7278,10 @@
         <v>119</v>
       </c>
       <c r="K108" s="24" t="n">
-        <v>118.536</v>
+        <v>118.502</v>
       </c>
       <c r="L108" s="24" t="n">
-        <v>0.464</v>
+        <v>0.498</v>
       </c>
       <c r="M108" s="9" t="inlineStr">
         <is>
@@ -7319,10 +7319,10 @@
         <v>119</v>
       </c>
       <c r="G109" s="22" t="n">
-        <v>118.536</v>
+        <v>118.502</v>
       </c>
       <c r="H109" s="22" t="n">
-        <v>0.464</v>
+        <v>0.498</v>
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
@@ -7333,10 +7333,10 @@
         <v>121</v>
       </c>
       <c r="K109" s="22" t="n">
-        <v>121.199</v>
+        <v>121.233</v>
       </c>
       <c r="L109" s="22" t="n">
-        <v>0.199</v>
+        <v>0.233</v>
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
@@ -7374,10 +7374,10 @@
         <v>121</v>
       </c>
       <c r="G110" s="24" t="n">
-        <v>121.199</v>
+        <v>121.233</v>
       </c>
       <c r="H110" s="24" t="n">
-        <v>0.199</v>
+        <v>0.233</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         <v>123</v>
       </c>
       <c r="K110" s="24" t="n">
-        <v>122.565</v>
+        <v>122.531</v>
       </c>
       <c r="L110" s="24" t="n">
-        <v>0.435</v>
+        <v>0.469</v>
       </c>
       <c r="M110" s="9" t="inlineStr">
         <is>
@@ -7429,10 +7429,10 @@
         <v>123</v>
       </c>
       <c r="G111" s="22" t="n">
-        <v>122.565</v>
+        <v>122.531</v>
       </c>
       <c r="H111" s="22" t="n">
-        <v>0.435</v>
+        <v>0.469</v>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
         <v>125</v>
       </c>
       <c r="K111" s="22" t="n">
-        <v>125.091</v>
+        <v>125.125</v>
       </c>
       <c r="L111" s="22" t="n">
-        <v>0.091</v>
+        <v>0.125</v>
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
@@ -7484,10 +7484,10 @@
         <v>125</v>
       </c>
       <c r="G112" s="24" t="n">
-        <v>125.091</v>
+        <v>125.125</v>
       </c>
       <c r="H112" s="24" t="n">
-        <v>0.091</v>
+        <v>0.125</v>
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
@@ -7498,10 +7498,10 @@
         <v>129</v>
       </c>
       <c r="K112" s="24" t="n">
-        <v>128.983</v>
+        <v>128.949</v>
       </c>
       <c r="L112" s="24" t="n">
-        <v>0.017</v>
+        <v>0.051</v>
       </c>
       <c r="M112" s="9" t="inlineStr">
         <is>
@@ -7539,10 +7539,10 @@
         <v>129</v>
       </c>
       <c r="G113" s="22" t="n">
-        <v>128.983</v>
+        <v>128.949</v>
       </c>
       <c r="H113" s="22" t="n">
-        <v>0.017</v>
+        <v>0.051</v>
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
@@ -7553,22 +7553,22 @@
         <v>130</v>
       </c>
       <c r="K113" s="22" t="n">
-        <v>130.485</v>
+        <v>130.519</v>
       </c>
       <c r="L113" s="22" t="n">
-        <v>0.485</v>
+        <v>0.519</v>
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N113" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="O113" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O113" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc Start</t>
         </is>
       </c>
     </row>
@@ -7594,24 +7594,24 @@
         <v>130</v>
       </c>
       <c r="G114" s="24" t="n">
-        <v>130.485</v>
+        <v>130.519</v>
       </c>
       <c r="H114" s="24" t="n">
-        <v>0.485</v>
+        <v>0.519</v>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="J114" s="24" t="n">
         <v>132</v>
       </c>
       <c r="K114" s="24" t="n">
-        <v>132.329</v>
+        <v>132.363</v>
       </c>
       <c r="L114" s="24" t="n">
-        <v>0.329</v>
+        <v>0.363</v>
       </c>
       <c r="M114" s="9" t="inlineStr">
         <is>
@@ -7621,9 +7621,9 @@
       <c r="N114" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O114" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O114" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc End</t>
         </is>
       </c>
     </row>
@@ -7649,10 +7649,10 @@
         <v>132</v>
       </c>
       <c r="G115" s="22" t="n">
-        <v>132.329</v>
+        <v>132.363</v>
       </c>
       <c r="H115" s="22" t="n">
-        <v>0.329</v>
+        <v>0.363</v>
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
@@ -7704,10 +7704,10 @@
         <v>1</v>
       </c>
       <c r="G116" s="24" t="n">
-        <v>0.981</v>
+        <v>1.016</v>
       </c>
       <c r="H116" s="24" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="I116" s="9" t="inlineStr">
         <is>
@@ -7718,10 +7718,10 @@
         <v>2</v>
       </c>
       <c r="K116" s="24" t="n">
-        <v>2.103</v>
+        <v>2.138</v>
       </c>
       <c r="L116" s="24" t="n">
-        <v>0.103</v>
+        <v>0.138</v>
       </c>
       <c r="M116" s="9" t="inlineStr">
         <is>
@@ -7759,10 +7759,10 @@
         <v>2</v>
       </c>
       <c r="G117" s="22" t="n">
-        <v>2.103</v>
+        <v>2.138</v>
       </c>
       <c r="H117" s="22" t="n">
-        <v>0.103</v>
+        <v>0.138</v>
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
@@ -7773,10 +7773,10 @@
         <v>9</v>
       </c>
       <c r="K117" s="22" t="n">
-        <v>9.252000000000001</v>
+        <v>9.287000000000001</v>
       </c>
       <c r="L117" s="22" t="n">
-        <v>0.252</v>
+        <v>0.287</v>
       </c>
       <c r="M117" s="5" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         <v>9</v>
       </c>
       <c r="G118" s="24" t="n">
-        <v>9.252000000000001</v>
+        <v>9.287000000000001</v>
       </c>
       <c r="H118" s="24" t="n">
-        <v>0.252</v>
+        <v>0.287</v>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
@@ -7828,10 +7828,10 @@
         <v>10</v>
       </c>
       <c r="K118" s="24" t="n">
-        <v>10.583</v>
+        <v>10.618</v>
       </c>
       <c r="L118" s="24" t="n">
-        <v>0.583</v>
+        <v>0.618</v>
       </c>
       <c r="M118" s="9" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
         <v>10</v>
       </c>
       <c r="G119" s="22" t="n">
-        <v>10.583</v>
+        <v>10.618</v>
       </c>
       <c r="H119" s="22" t="n">
-        <v>0.583</v>
+        <v>0.618</v>
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>15</v>
       </c>
       <c r="K119" s="22" t="n">
-        <v>15.279</v>
+        <v>15.314</v>
       </c>
       <c r="L119" s="22" t="n">
-        <v>0.279</v>
+        <v>0.314</v>
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>15</v>
       </c>
       <c r="G120" s="24" t="n">
-        <v>15.279</v>
+        <v>15.314</v>
       </c>
       <c r="H120" s="24" t="n">
-        <v>0.279</v>
+        <v>0.314</v>
       </c>
       <c r="I120" s="9" t="inlineStr">
         <is>
@@ -7938,10 +7938,10 @@
         <v>17</v>
       </c>
       <c r="K120" s="24" t="n">
-        <v>16.681</v>
+        <v>16.646</v>
       </c>
       <c r="L120" s="24" t="n">
-        <v>0.319</v>
+        <v>0.354</v>
       </c>
       <c r="M120" s="9" t="inlineStr">
         <is>
@@ -7979,10 +7979,10 @@
         <v>17</v>
       </c>
       <c r="G121" s="22" t="n">
-        <v>16.681</v>
+        <v>16.646</v>
       </c>
       <c r="H121" s="22" t="n">
-        <v>0.319</v>
+        <v>0.354</v>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
@@ -7993,10 +7993,10 @@
         <v>21</v>
       </c>
       <c r="K121" s="22" t="n">
-        <v>20.536</v>
+        <v>20.501</v>
       </c>
       <c r="L121" s="22" t="n">
-        <v>0.464</v>
+        <v>0.499</v>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
@@ -8034,10 +8034,10 @@
         <v>21</v>
       </c>
       <c r="G122" s="24" t="n">
-        <v>20.536</v>
+        <v>20.501</v>
       </c>
       <c r="H122" s="24" t="n">
-        <v>0.464</v>
+        <v>0.499</v>
       </c>
       <c r="I122" s="9" t="inlineStr">
         <is>
@@ -8048,10 +8048,10 @@
         <v>25</v>
       </c>
       <c r="K122" s="24" t="n">
-        <v>25.021</v>
+        <v>25.056</v>
       </c>
       <c r="L122" s="24" t="n">
-        <v>0.021</v>
+        <v>0.056</v>
       </c>
       <c r="M122" s="9" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         <v>25</v>
       </c>
       <c r="G123" s="22" t="n">
-        <v>25.021</v>
+        <v>25.056</v>
       </c>
       <c r="H123" s="22" t="n">
-        <v>0.021</v>
+        <v>0.056</v>
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
@@ -8103,10 +8103,10 @@
         <v>26</v>
       </c>
       <c r="K123" s="22" t="n">
-        <v>26.002</v>
+        <v>26.038</v>
       </c>
       <c r="L123" s="22" t="n">
-        <v>0.002</v>
+        <v>0.038</v>
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
@@ -8144,10 +8144,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="24" t="n">
-        <v>26.002</v>
+        <v>26.038</v>
       </c>
       <c r="H124" s="24" t="n">
-        <v>0.002</v>
+        <v>0.038</v>
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
@@ -8158,10 +8158,10 @@
         <v>27</v>
       </c>
       <c r="K124" s="24" t="n">
-        <v>27.755</v>
+        <v>27.79</v>
       </c>
       <c r="L124" s="24" t="n">
-        <v>0.755</v>
+        <v>0.79</v>
       </c>
       <c r="M124" s="9" t="inlineStr">
         <is>
@@ -8199,10 +8199,10 @@
         <v>27</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>27.755</v>
+        <v>27.79</v>
       </c>
       <c r="H125" s="22" t="n">
-        <v>0.755</v>
+        <v>0.79</v>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
@@ -8213,22 +8213,22 @@
         <v>30</v>
       </c>
       <c r="K125" s="22" t="n">
-        <v>29.507</v>
+        <v>29.472</v>
       </c>
       <c r="L125" s="22" t="n">
-        <v>0.493</v>
+        <v>0.528</v>
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N125" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="O125" s="25" t="inlineStr">
-        <is>
-          <t>Khớp mốc End</t>
+      <c r="O125" s="26" t="inlineStr">
+        <is>
+          <t>Không khớp</t>
         </is>
       </c>
     </row>
@@ -8254,24 +8254,24 @@
         <v>30</v>
       </c>
       <c r="G126" s="24" t="n">
-        <v>29.507</v>
+        <v>29.472</v>
       </c>
       <c r="H126" s="24" t="n">
-        <v>0.493</v>
+        <v>0.528</v>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="J126" s="24" t="n">
         <v>32</v>
       </c>
       <c r="K126" s="24" t="n">
-        <v>31.609</v>
+        <v>31.574</v>
       </c>
       <c r="L126" s="24" t="n">
-        <v>0.391</v>
+        <v>0.426</v>
       </c>
       <c r="M126" s="9" t="inlineStr">
         <is>
@@ -8281,9 +8281,9 @@
       <c r="N126" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O126" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O126" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc End</t>
         </is>
       </c>
     </row>
@@ -8309,10 +8309,10 @@
         <v>32</v>
       </c>
       <c r="G127" s="22" t="n">
-        <v>31.609</v>
+        <v>31.574</v>
       </c>
       <c r="H127" s="22" t="n">
-        <v>0.391</v>
+        <v>0.426</v>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
@@ -8323,10 +8323,10 @@
         <v>43</v>
       </c>
       <c r="K127" s="22" t="n">
-        <v>43.244</v>
+        <v>43.279</v>
       </c>
       <c r="L127" s="22" t="n">
-        <v>0.244</v>
+        <v>0.279</v>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
@@ -8364,10 +8364,10 @@
         <v>43</v>
       </c>
       <c r="G128" s="24" t="n">
-        <v>43.244</v>
+        <v>43.279</v>
       </c>
       <c r="H128" s="24" t="n">
-        <v>0.244</v>
+        <v>0.279</v>
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
@@ -8378,10 +8378,10 @@
         <v>47</v>
       </c>
       <c r="K128" s="24" t="n">
-        <v>47.449</v>
+        <v>47.484</v>
       </c>
       <c r="L128" s="24" t="n">
-        <v>0.449</v>
+        <v>0.484</v>
       </c>
       <c r="M128" s="9" t="inlineStr">
         <is>
@@ -8419,10 +8419,10 @@
         <v>47</v>
       </c>
       <c r="G129" s="22" t="n">
-        <v>47.449</v>
+        <v>47.484</v>
       </c>
       <c r="H129" s="22" t="n">
-        <v>0.449</v>
+        <v>0.484</v>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         <v>51</v>
       </c>
       <c r="K129" s="22" t="n">
-        <v>51.164</v>
+        <v>51.199</v>
       </c>
       <c r="L129" s="22" t="n">
-        <v>0.164</v>
+        <v>0.199</v>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
@@ -8474,10 +8474,10 @@
         <v>51</v>
       </c>
       <c r="G130" s="24" t="n">
-        <v>51.164</v>
+        <v>51.199</v>
       </c>
       <c r="H130" s="24" t="n">
-        <v>0.164</v>
+        <v>0.199</v>
       </c>
       <c r="I130" s="9" t="inlineStr">
         <is>
@@ -8488,22 +8488,22 @@
         <v>56</v>
       </c>
       <c r="K130" s="24" t="n">
-        <v>55.509</v>
+        <v>55.474</v>
       </c>
       <c r="L130" s="24" t="n">
-        <v>0.491</v>
+        <v>0.526</v>
       </c>
       <c r="M130" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N130" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="O130" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O130" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc Start</t>
         </is>
       </c>
     </row>
@@ -8529,24 +8529,24 @@
         <v>56</v>
       </c>
       <c r="G131" s="22" t="n">
-        <v>55.509</v>
+        <v>55.474</v>
       </c>
       <c r="H131" s="22" t="n">
-        <v>0.491</v>
+        <v>0.526</v>
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="J131" s="22" t="n">
         <v>59</v>
       </c>
       <c r="K131" s="22" t="n">
-        <v>59.084</v>
+        <v>59.119</v>
       </c>
       <c r="L131" s="22" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.119</v>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
@@ -8556,9 +8556,9 @@
       <c r="N131" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="O131" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O131" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc End</t>
         </is>
       </c>
     </row>
@@ -8584,10 +8584,10 @@
         <v>59</v>
       </c>
       <c r="G132" s="24" t="n">
-        <v>59.084</v>
+        <v>59.119</v>
       </c>
       <c r="H132" s="24" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.119</v>
       </c>
       <c r="I132" s="9" t="inlineStr">
         <is>
@@ -8598,10 +8598,10 @@
         <v>61</v>
       </c>
       <c r="K132" s="24" t="n">
-        <v>60.976</v>
+        <v>60.941</v>
       </c>
       <c r="L132" s="24" t="n">
-        <v>0.024</v>
+        <v>0.059</v>
       </c>
       <c r="M132" s="9" t="inlineStr">
         <is>
@@ -8639,10 +8639,10 @@
         <v>61</v>
       </c>
       <c r="G133" s="22" t="n">
-        <v>60.976</v>
+        <v>60.941</v>
       </c>
       <c r="H133" s="22" t="n">
-        <v>0.024</v>
+        <v>0.059</v>
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
@@ -8653,10 +8653,10 @@
         <v>73</v>
       </c>
       <c r="K133" s="22" t="n">
-        <v>73.03100000000001</v>
+        <v>72.996</v>
       </c>
       <c r="L133" s="22" t="n">
-        <v>0.031</v>
+        <v>0.004</v>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
@@ -8694,10 +8694,10 @@
         <v>73</v>
       </c>
       <c r="G134" s="24" t="n">
-        <v>73.03100000000001</v>
+        <v>72.996</v>
       </c>
       <c r="H134" s="24" t="n">
-        <v>0.031</v>
+        <v>0.004</v>
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
@@ -8708,10 +8708,10 @@
         <v>75</v>
       </c>
       <c r="K134" s="24" t="n">
-        <v>75.414</v>
+        <v>75.449</v>
       </c>
       <c r="L134" s="24" t="n">
-        <v>0.414</v>
+        <v>0.449</v>
       </c>
       <c r="M134" s="9" t="inlineStr">
         <is>
@@ -8749,10 +8749,10 @@
         <v>75</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>75.414</v>
+        <v>75.449</v>
       </c>
       <c r="H135" s="22" t="n">
-        <v>0.414</v>
+        <v>0.449</v>
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
@@ -8763,10 +8763,10 @@
         <v>77</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>76.886</v>
+        <v>76.851</v>
       </c>
       <c r="L135" s="22" t="n">
-        <v>0.114</v>
+        <v>0.149</v>
       </c>
       <c r="M135" s="5" t="inlineStr">
         <is>
@@ -8804,10 +8804,10 @@
         <v>77</v>
       </c>
       <c r="G136" s="24" t="n">
-        <v>76.886</v>
+        <v>76.851</v>
       </c>
       <c r="H136" s="24" t="n">
-        <v>0.114</v>
+        <v>0.149</v>
       </c>
       <c r="I136" s="9" t="inlineStr">
         <is>
@@ -8818,10 +8818,10 @@
         <v>78</v>
       </c>
       <c r="K136" s="24" t="n">
-        <v>78.077</v>
+        <v>78.11199999999999</v>
       </c>
       <c r="L136" s="24" t="n">
-        <v>0.077</v>
+        <v>0.112</v>
       </c>
       <c r="M136" s="9" t="inlineStr">
         <is>
@@ -8859,10 +8859,10 @@
         <v>78</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>78.077</v>
+        <v>78.11199999999999</v>
       </c>
       <c r="H137" s="22" t="n">
-        <v>0.077</v>
+        <v>0.112</v>
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
@@ -8873,10 +8873,10 @@
         <v>79</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>78.848</v>
+        <v>78.813</v>
       </c>
       <c r="L137" s="22" t="n">
-        <v>0.152</v>
+        <v>0.187</v>
       </c>
       <c r="M137" s="5" t="inlineStr">
         <is>
@@ -8914,10 +8914,10 @@
         <v>79</v>
       </c>
       <c r="G138" s="24" t="n">
-        <v>78.848</v>
+        <v>78.813</v>
       </c>
       <c r="H138" s="24" t="n">
-        <v>0.152</v>
+        <v>0.187</v>
       </c>
       <c r="I138" s="9" t="inlineStr">
         <is>
@@ -8928,10 +8928,10 @@
         <v>86</v>
       </c>
       <c r="K138" s="24" t="n">
-        <v>85.226</v>
+        <v>85.191</v>
       </c>
       <c r="L138" s="24" t="n">
-        <v>0.774</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="M138" s="9" t="inlineStr">
         <is>
@@ -8969,10 +8969,10 @@
         <v>86</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>85.226</v>
+        <v>85.191</v>
       </c>
       <c r="H139" s="22" t="n">
-        <v>0.774</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
         <v>115</v>
       </c>
       <c r="G140" s="24" t="n">
-        <v>115.657</v>
+        <v>115.692</v>
       </c>
       <c r="H140" s="24" t="n">
-        <v>0.657</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="I140" s="9" t="inlineStr">
         <is>
@@ -9042,10 +9042,10 @@
         <v>119</v>
       </c>
       <c r="K140" s="24" t="n">
-        <v>119.078</v>
+        <v>119.113</v>
       </c>
       <c r="L140" s="24" t="n">
-        <v>0.078</v>
+        <v>0.113</v>
       </c>
       <c r="M140" s="9" t="inlineStr">
         <is>
@@ -9087,10 +9087,10 @@
         <v>119</v>
       </c>
       <c r="G141" s="22" t="n">
-        <v>119.078</v>
+        <v>119.113</v>
       </c>
       <c r="H141" s="22" t="n">
-        <v>0.078</v>
+        <v>0.113</v>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
@@ -9101,10 +9101,10 @@
         <v>127</v>
       </c>
       <c r="K141" s="22" t="n">
-        <v>127.035</v>
+        <v>127.07</v>
       </c>
       <c r="L141" s="22" t="n">
-        <v>0.035</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M141" s="5" t="inlineStr">
         <is>
@@ -9146,10 +9146,10 @@
         <v>127</v>
       </c>
       <c r="G142" s="24" t="n">
-        <v>127.035</v>
+        <v>127.07</v>
       </c>
       <c r="H142" s="24" t="n">
-        <v>0.035</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I142" s="9" t="inlineStr">
         <is>
@@ -9160,10 +9160,10 @@
         <v>129</v>
       </c>
       <c r="K142" s="24" t="n">
-        <v>129.268</v>
+        <v>129.303</v>
       </c>
       <c r="L142" s="24" t="n">
-        <v>0.268</v>
+        <v>0.303</v>
       </c>
       <c r="M142" s="9" t="inlineStr">
         <is>
@@ -9205,10 +9205,10 @@
         <v>128</v>
       </c>
       <c r="G143" s="22" t="n">
-        <v>128.151</v>
+        <v>128.186</v>
       </c>
       <c r="H143" s="22" t="n">
-        <v>0.151</v>
+        <v>0.186</v>
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
@@ -9219,10 +9219,10 @@
         <v>132</v>
       </c>
       <c r="K143" s="22" t="n">
-        <v>132.27</v>
+        <v>132.305</v>
       </c>
       <c r="L143" s="22" t="n">
-        <v>0.27</v>
+        <v>0.305</v>
       </c>
       <c r="M143" s="5" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>132</v>
       </c>
       <c r="G144" s="24" t="n">
-        <v>132.27</v>
+        <v>132.305</v>
       </c>
       <c r="H144" s="24" t="n">
-        <v>0.27</v>
+        <v>0.305</v>
       </c>
       <c r="I144" s="9" t="inlineStr">
         <is>
@@ -9278,10 +9278,10 @@
         <v>135</v>
       </c>
       <c r="K144" s="24" t="n">
-        <v>135.131</v>
+        <v>135.166</v>
       </c>
       <c r="L144" s="24" t="n">
-        <v>0.131</v>
+        <v>0.166</v>
       </c>
       <c r="M144" s="9" t="inlineStr">
         <is>
@@ -9323,10 +9323,10 @@
         <v>135</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>135.131</v>
+        <v>135.166</v>
       </c>
       <c r="H145" s="22" t="n">
-        <v>0.131</v>
+        <v>0.166</v>
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
@@ -9337,10 +9337,10 @@
         <v>137</v>
       </c>
       <c r="K145" s="22" t="n">
-        <v>137.086</v>
+        <v>137.121</v>
       </c>
       <c r="L145" s="22" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="M145" s="5" t="inlineStr">
         <is>
@@ -9382,10 +9382,10 @@
         <v>137</v>
       </c>
       <c r="G146" s="24" t="n">
-        <v>137.086</v>
+        <v>137.121</v>
       </c>
       <c r="H146" s="24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="I146" s="9" t="inlineStr">
         <is>
@@ -9396,10 +9396,10 @@
         <v>139</v>
       </c>
       <c r="K146" s="24" t="n">
-        <v>139.11</v>
+        <v>139.145</v>
       </c>
       <c r="L146" s="24" t="n">
-        <v>0.11</v>
+        <v>0.145</v>
       </c>
       <c r="M146" s="9" t="inlineStr">
         <is>
@@ -9441,10 +9441,10 @@
         <v>139</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>139.11</v>
+        <v>139.145</v>
       </c>
       <c r="H147" s="22" t="n">
-        <v>0.11</v>
+        <v>0.145</v>
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
@@ -9455,10 +9455,10 @@
         <v>141</v>
       </c>
       <c r="K147" s="22" t="n">
-        <v>141.064</v>
+        <v>141.099</v>
       </c>
       <c r="L147" s="22" t="n">
-        <v>0.064</v>
+        <v>0.099</v>
       </c>
       <c r="M147" s="5" t="inlineStr">
         <is>
@@ -9500,10 +9500,10 @@
         <v>141</v>
       </c>
       <c r="G148" s="24" t="n">
-        <v>141.064</v>
+        <v>141.099</v>
       </c>
       <c r="H148" s="24" t="n">
-        <v>0.064</v>
+        <v>0.099</v>
       </c>
       <c r="I148" s="9" t="inlineStr">
         <is>
@@ -9514,10 +9514,10 @@
         <v>143</v>
       </c>
       <c r="K148" s="24" t="n">
-        <v>142.809</v>
+        <v>142.774</v>
       </c>
       <c r="L148" s="24" t="n">
-        <v>0.191</v>
+        <v>0.226</v>
       </c>
       <c r="M148" s="9" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         <v>143</v>
       </c>
       <c r="G149" s="22" t="n">
-        <v>142.809</v>
+        <v>142.774</v>
       </c>
       <c r="H149" s="22" t="n">
-        <v>0.191</v>
+        <v>0.226</v>
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
@@ -9573,10 +9573,10 @@
         <v>145</v>
       </c>
       <c r="K149" s="22" t="n">
-        <v>145.671</v>
+        <v>145.706</v>
       </c>
       <c r="L149" s="22" t="n">
-        <v>0.671</v>
+        <v>0.706</v>
       </c>
       <c r="M149" s="5" t="inlineStr">
         <is>
@@ -9618,10 +9618,10 @@
         <v>145</v>
       </c>
       <c r="G150" s="24" t="n">
-        <v>145.671</v>
+        <v>145.706</v>
       </c>
       <c r="H150" s="24" t="n">
-        <v>0.671</v>
+        <v>0.706</v>
       </c>
       <c r="I150" s="9" t="inlineStr">
         <is>
@@ -9632,22 +9632,22 @@
         <v>147</v>
       </c>
       <c r="K150" s="24" t="n">
-        <v>147.486</v>
+        <v>147.521</v>
       </c>
       <c r="L150" s="24" t="n">
-        <v>0.486</v>
+        <v>0.521</v>
       </c>
       <c r="M150" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N150" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O150" s="25" t="inlineStr">
-        <is>
-          <t>Khớp mốc End</t>
+      <c r="O150" s="26" t="inlineStr">
+        <is>
+          <t>Không khớp</t>
         </is>
       </c>
     </row>
@@ -9677,24 +9677,24 @@
         <v>147</v>
       </c>
       <c r="G151" s="22" t="n">
-        <v>147.486</v>
+        <v>147.521</v>
       </c>
       <c r="H151" s="22" t="n">
-        <v>0.486</v>
+        <v>0.521</v>
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="J151" s="22" t="n">
         <v>149</v>
       </c>
       <c r="K151" s="22" t="n">
-        <v>148.463</v>
+        <v>148.428</v>
       </c>
       <c r="L151" s="22" t="n">
-        <v>0.537</v>
+        <v>0.572</v>
       </c>
       <c r="M151" s="5" t="inlineStr">
         <is>
@@ -9704,9 +9704,9 @@
       <c r="N151" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="O151" s="25" t="inlineStr">
-        <is>
-          <t>Khớp mốc Start</t>
+      <c r="O151" s="26" t="inlineStr">
+        <is>
+          <t>Không khớp</t>
         </is>
       </c>
     </row>
@@ -9736,10 +9736,10 @@
         <v>149</v>
       </c>
       <c r="G152" s="24" t="n">
-        <v>148.463</v>
+        <v>148.428</v>
       </c>
       <c r="H152" s="24" t="n">
-        <v>0.537</v>
+        <v>0.572</v>
       </c>
       <c r="I152" s="9" t="inlineStr">
         <is>
@@ -9750,10 +9750,10 @@
         <v>152</v>
       </c>
       <c r="K152" s="24" t="n">
-        <v>152.302</v>
+        <v>152.337</v>
       </c>
       <c r="L152" s="24" t="n">
-        <v>0.302</v>
+        <v>0.337</v>
       </c>
       <c r="M152" s="9" t="inlineStr">
         <is>
@@ -9795,10 +9795,10 @@
         <v>152</v>
       </c>
       <c r="G153" s="22" t="n">
-        <v>152.302</v>
+        <v>152.337</v>
       </c>
       <c r="H153" s="22" t="n">
-        <v>0.302</v>
+        <v>0.337</v>
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
@@ -9809,10 +9809,10 @@
         <v>154</v>
       </c>
       <c r="K153" s="22" t="n">
-        <v>153.907</v>
+        <v>153.873</v>
       </c>
       <c r="L153" s="22" t="n">
-        <v>0.093</v>
+        <v>0.127</v>
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
@@ -9854,10 +9854,10 @@
         <v>154</v>
       </c>
       <c r="G154" s="24" t="n">
-        <v>153.907</v>
+        <v>153.873</v>
       </c>
       <c r="H154" s="24" t="n">
-        <v>0.093</v>
+        <v>0.127</v>
       </c>
       <c r="I154" s="9" t="inlineStr">
         <is>
@@ -9868,10 +9868,10 @@
         <v>156</v>
       </c>
       <c r="K154" s="24" t="n">
-        <v>155.652</v>
+        <v>155.618</v>
       </c>
       <c r="L154" s="24" t="n">
-        <v>0.348</v>
+        <v>0.382</v>
       </c>
       <c r="M154" s="9" t="inlineStr">
         <is>
@@ -9913,10 +9913,10 @@
         <v>157</v>
       </c>
       <c r="G155" s="22" t="n">
-        <v>157.188</v>
+        <v>157.223</v>
       </c>
       <c r="H155" s="22" t="n">
-        <v>0.188</v>
+        <v>0.223</v>
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
@@ -9927,10 +9927,10 @@
         <v>161</v>
       </c>
       <c r="K155" s="22" t="n">
-        <v>161.027</v>
+        <v>160.992</v>
       </c>
       <c r="L155" s="22" t="n">
-        <v>0.027</v>
+        <v>0.008</v>
       </c>
       <c r="M155" s="5" t="inlineStr">
         <is>
@@ -9972,10 +9972,10 @@
         <v>161</v>
       </c>
       <c r="G156" s="24" t="n">
-        <v>161.027</v>
+        <v>160.992</v>
       </c>
       <c r="H156" s="24" t="n">
-        <v>0.027</v>
+        <v>0.008</v>
       </c>
       <c r="I156" s="9" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>163</v>
       </c>
       <c r="K156" s="24" t="n">
-        <v>162.981</v>
+        <v>162.946</v>
       </c>
       <c r="L156" s="24" t="n">
-        <v>0.019</v>
+        <v>0.054</v>
       </c>
       <c r="M156" s="9" t="inlineStr">
         <is>
@@ -10031,10 +10031,10 @@
         <v>163</v>
       </c>
       <c r="G157" s="22" t="n">
-        <v>162.981</v>
+        <v>162.946</v>
       </c>
       <c r="H157" s="22" t="n">
-        <v>0.019</v>
+        <v>0.054</v>
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
@@ -10045,10 +10045,10 @@
         <v>165</v>
       </c>
       <c r="K157" s="22" t="n">
-        <v>164.587</v>
+        <v>164.552</v>
       </c>
       <c r="L157" s="22" t="n">
-        <v>0.413</v>
+        <v>0.448</v>
       </c>
       <c r="M157" s="5" t="inlineStr">
         <is>
@@ -10090,10 +10090,10 @@
         <v>165</v>
       </c>
       <c r="G158" s="24" t="n">
-        <v>164.587</v>
+        <v>164.552</v>
       </c>
       <c r="H158" s="24" t="n">
-        <v>0.413</v>
+        <v>0.448</v>
       </c>
       <c r="I158" s="9" t="inlineStr">
         <is>
@@ -10104,10 +10104,10 @@
         <v>167</v>
       </c>
       <c r="K158" s="24" t="n">
-        <v>166.89</v>
+        <v>166.855</v>
       </c>
       <c r="L158" s="24" t="n">
-        <v>0.11</v>
+        <v>0.145</v>
       </c>
       <c r="M158" s="9" t="inlineStr">
         <is>
@@ -10149,10 +10149,10 @@
         <v>167</v>
       </c>
       <c r="G159" s="22" t="n">
-        <v>166.89</v>
+        <v>166.855</v>
       </c>
       <c r="H159" s="22" t="n">
-        <v>0.11</v>
+        <v>0.145</v>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
@@ -10163,10 +10163,10 @@
         <v>171</v>
       </c>
       <c r="K159" s="22" t="n">
-        <v>170.589</v>
+        <v>170.555</v>
       </c>
       <c r="L159" s="22" t="n">
-        <v>0.411</v>
+        <v>0.445</v>
       </c>
       <c r="M159" s="5" t="inlineStr">
         <is>
@@ -10208,10 +10208,10 @@
         <v>171</v>
       </c>
       <c r="G160" s="24" t="n">
-        <v>170.589</v>
+        <v>170.555</v>
       </c>
       <c r="H160" s="24" t="n">
-        <v>0.411</v>
+        <v>0.445</v>
       </c>
       <c r="I160" s="9" t="inlineStr">
         <is>
@@ -10222,10 +10222,10 @@
         <v>173</v>
       </c>
       <c r="K160" s="24" t="n">
-        <v>171.846</v>
+        <v>171.811</v>
       </c>
       <c r="L160" s="24" t="n">
-        <v>1.154</v>
+        <v>1.189</v>
       </c>
       <c r="M160" s="9" t="inlineStr">
         <is>
@@ -10267,10 +10267,10 @@
         <v>173</v>
       </c>
       <c r="G161" s="22" t="n">
-        <v>171.846</v>
+        <v>171.811</v>
       </c>
       <c r="H161" s="22" t="n">
-        <v>1.154</v>
+        <v>1.189</v>
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
@@ -10281,10 +10281,10 @@
         <v>175</v>
       </c>
       <c r="K161" s="22" t="n">
-        <v>175.126</v>
+        <v>175.161</v>
       </c>
       <c r="L161" s="22" t="n">
-        <v>0.126</v>
+        <v>0.161</v>
       </c>
       <c r="M161" s="5" t="inlineStr">
         <is>
@@ -10326,10 +10326,10 @@
         <v>175</v>
       </c>
       <c r="G162" s="24" t="n">
-        <v>175.126</v>
+        <v>175.161</v>
       </c>
       <c r="H162" s="24" t="n">
-        <v>0.126</v>
+        <v>0.161</v>
       </c>
       <c r="I162" s="9" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         <v>180</v>
       </c>
       <c r="K162" s="24" t="n">
-        <v>180.291</v>
+        <v>180.326</v>
       </c>
       <c r="L162" s="24" t="n">
-        <v>0.291</v>
+        <v>0.326</v>
       </c>
       <c r="M162" s="9" t="inlineStr">
         <is>
@@ -10385,10 +10385,10 @@
         <v>180</v>
       </c>
       <c r="G163" s="22" t="n">
-        <v>180.291</v>
+        <v>180.326</v>
       </c>
       <c r="H163" s="22" t="n">
-        <v>0.291</v>
+        <v>0.326</v>
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
@@ -10399,10 +10399,10 @@
         <v>182</v>
       </c>
       <c r="K163" s="22" t="n">
-        <v>182.316</v>
+        <v>182.351</v>
       </c>
       <c r="L163" s="22" t="n">
-        <v>0.316</v>
+        <v>0.351</v>
       </c>
       <c r="M163" s="5" t="inlineStr">
         <is>
@@ -10444,10 +10444,10 @@
         <v>182</v>
       </c>
       <c r="G164" s="24" t="n">
-        <v>182.316</v>
+        <v>182.351</v>
       </c>
       <c r="H164" s="24" t="n">
-        <v>0.316</v>
+        <v>0.351</v>
       </c>
       <c r="I164" s="9" t="inlineStr">
         <is>
@@ -10458,10 +10458,10 @@
         <v>185</v>
       </c>
       <c r="K164" s="24" t="n">
-        <v>185.038</v>
+        <v>185.073</v>
       </c>
       <c r="L164" s="24" t="n">
-        <v>0.038</v>
+        <v>0.073</v>
       </c>
       <c r="M164" s="9" t="inlineStr">
         <is>
@@ -10503,10 +10503,10 @@
         <v>185</v>
       </c>
       <c r="G165" s="22" t="n">
-        <v>185.038</v>
+        <v>185.073</v>
       </c>
       <c r="H165" s="22" t="n">
-        <v>0.038</v>
+        <v>0.073</v>
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
@@ -10517,10 +10517,10 @@
         <v>190</v>
       </c>
       <c r="K165" s="22" t="n">
-        <v>190.273</v>
+        <v>190.308</v>
       </c>
       <c r="L165" s="22" t="n">
-        <v>0.273</v>
+        <v>0.308</v>
       </c>
       <c r="M165" s="5" t="inlineStr">
         <is>
@@ -10562,10 +10562,10 @@
         <v>190</v>
       </c>
       <c r="G166" s="24" t="n">
-        <v>190.273</v>
+        <v>190.308</v>
       </c>
       <c r="H166" s="24" t="n">
-        <v>0.273</v>
+        <v>0.308</v>
       </c>
       <c r="I166" s="9" t="inlineStr">
         <is>
@@ -10576,10 +10576,10 @@
         <v>193</v>
       </c>
       <c r="K166" s="24" t="n">
-        <v>193.065</v>
+        <v>193.1</v>
       </c>
       <c r="L166" s="24" t="n">
-        <v>0.065</v>
+        <v>0.1</v>
       </c>
       <c r="M166" s="9" t="inlineStr">
         <is>
@@ -10621,10 +10621,10 @@
         <v>193</v>
       </c>
       <c r="G167" s="22" t="n">
-        <v>193.065</v>
+        <v>193.1</v>
       </c>
       <c r="H167" s="22" t="n">
-        <v>0.065</v>
+        <v>0.1</v>
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
@@ -10635,10 +10635,10 @@
         <v>194</v>
       </c>
       <c r="K167" s="22" t="n">
-        <v>194.321</v>
+        <v>194.356</v>
       </c>
       <c r="L167" s="22" t="n">
-        <v>0.321</v>
+        <v>0.356</v>
       </c>
       <c r="M167" s="5" t="inlineStr">
         <is>
@@ -10680,10 +10680,10 @@
         <v>194</v>
       </c>
       <c r="G168" s="24" t="n">
-        <v>194.321</v>
+        <v>194.356</v>
       </c>
       <c r="H168" s="24" t="n">
-        <v>0.321</v>
+        <v>0.356</v>
       </c>
       <c r="I168" s="9" t="inlineStr">
         <is>
@@ -10694,10 +10694,10 @@
         <v>197</v>
       </c>
       <c r="K168" s="24" t="n">
-        <v>196.694</v>
+        <v>196.659</v>
       </c>
       <c r="L168" s="24" t="n">
-        <v>0.306</v>
+        <v>0.341</v>
       </c>
       <c r="M168" s="9" t="inlineStr">
         <is>
@@ -10739,10 +10739,10 @@
         <v>197</v>
       </c>
       <c r="G169" s="22" t="n">
-        <v>196.694</v>
+        <v>196.659</v>
       </c>
       <c r="H169" s="22" t="n">
-        <v>0.306</v>
+        <v>0.341</v>
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
@@ -10753,10 +10753,10 @@
         <v>207</v>
       </c>
       <c r="K169" s="22" t="n">
-        <v>208.002</v>
+        <v>208.037</v>
       </c>
       <c r="L169" s="22" t="n">
-        <v>1.002</v>
+        <v>1.037</v>
       </c>
       <c r="M169" s="5" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         <v>207</v>
       </c>
       <c r="G170" s="24" t="n">
-        <v>208.002</v>
+        <v>208.037</v>
       </c>
       <c r="H170" s="24" t="n">
-        <v>1.002</v>
+        <v>1.037</v>
       </c>
       <c r="I170" s="9" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         <v>212</v>
       </c>
       <c r="K170" s="24" t="n">
-        <v>212.05</v>
+        <v>212.085</v>
       </c>
       <c r="L170" s="24" t="n">
-        <v>0.05</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="M170" s="9" t="inlineStr">
         <is>
@@ -10857,10 +10857,10 @@
         <v>212</v>
       </c>
       <c r="G171" s="22" t="n">
-        <v>212.05</v>
+        <v>212.085</v>
       </c>
       <c r="H171" s="22" t="n">
-        <v>0.05</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
@@ -10871,22 +10871,22 @@
         <v>214</v>
       </c>
       <c r="K171" s="22" t="n">
-        <v>213.516</v>
+        <v>213.481</v>
       </c>
       <c r="L171" s="22" t="n">
-        <v>0.484</v>
+        <v>0.519</v>
       </c>
       <c r="M171" s="5" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N171" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="O171" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O171" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc Start</t>
         </is>
       </c>
     </row>
@@ -10916,24 +10916,24 @@
         <v>214</v>
       </c>
       <c r="G172" s="24" t="n">
-        <v>213.516</v>
+        <v>213.481</v>
       </c>
       <c r="H172" s="24" t="n">
-        <v>0.484</v>
+        <v>0.519</v>
       </c>
       <c r="I172" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="J172" s="24" t="n">
         <v>216</v>
       </c>
       <c r="K172" s="24" t="n">
-        <v>215.819</v>
+        <v>215.784</v>
       </c>
       <c r="L172" s="24" t="n">
-        <v>0.181</v>
+        <v>0.216</v>
       </c>
       <c r="M172" s="9" t="inlineStr">
         <is>
@@ -10943,9 +10943,9 @@
       <c r="N172" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O172" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O172" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc End</t>
         </is>
       </c>
     </row>
@@ -10975,10 +10975,10 @@
         <v>216</v>
       </c>
       <c r="G173" s="22" t="n">
-        <v>215.819</v>
+        <v>215.784</v>
       </c>
       <c r="H173" s="22" t="n">
-        <v>0.181</v>
+        <v>0.216</v>
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
@@ -10989,10 +10989,10 @@
         <v>226</v>
       </c>
       <c r="K173" s="22" t="n">
-        <v>226.359</v>
+        <v>226.394</v>
       </c>
       <c r="L173" s="22" t="n">
-        <v>0.359</v>
+        <v>0.394</v>
       </c>
       <c r="M173" s="5" t="inlineStr">
         <is>
@@ -11034,10 +11034,10 @@
         <v>226</v>
       </c>
       <c r="G174" s="24" t="n">
-        <v>226.359</v>
+        <v>226.394</v>
       </c>
       <c r="H174" s="24" t="n">
-        <v>0.359</v>
+        <v>0.394</v>
       </c>
       <c r="I174" s="9" t="inlineStr">
         <is>
@@ -11048,10 +11048,10 @@
         <v>235</v>
       </c>
       <c r="K174" s="24" t="n">
-        <v>235.503</v>
+        <v>235.537</v>
       </c>
       <c r="L174" s="24" t="n">
-        <v>0.503</v>
+        <v>0.537</v>
       </c>
       <c r="M174" s="9" t="inlineStr">
         <is>
@@ -11093,10 +11093,10 @@
         <v>235</v>
       </c>
       <c r="G175" s="22" t="n">
-        <v>235.503</v>
+        <v>235.537</v>
       </c>
       <c r="H175" s="22" t="n">
-        <v>0.503</v>
+        <v>0.537</v>
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
@@ -11107,10 +11107,10 @@
         <v>236</v>
       </c>
       <c r="K175" s="22" t="n">
-        <v>235.572</v>
+        <v>235.537</v>
       </c>
       <c r="L175" s="22" t="n">
-        <v>0.428</v>
+        <v>0.463</v>
       </c>
       <c r="M175" s="5" t="inlineStr">
         <is>
@@ -11152,10 +11152,10 @@
         <v>236</v>
       </c>
       <c r="G176" s="24" t="n">
-        <v>235.572</v>
+        <v>235.537</v>
       </c>
       <c r="H176" s="24" t="n">
-        <v>0.428</v>
+        <v>0.463</v>
       </c>
       <c r="I176" s="9" t="inlineStr">
         <is>
@@ -11166,10 +11166,10 @@
         <v>239</v>
       </c>
       <c r="K176" s="24" t="n">
-        <v>240.109</v>
+        <v>240.144</v>
       </c>
       <c r="L176" s="24" t="n">
-        <v>1.109</v>
+        <v>1.144</v>
       </c>
       <c r="M176" s="9" t="inlineStr">
         <is>
@@ -11211,10 +11211,10 @@
         <v>239</v>
       </c>
       <c r="G177" s="22" t="n">
-        <v>240.109</v>
+        <v>240.144</v>
       </c>
       <c r="H177" s="22" t="n">
-        <v>1.109</v>
+        <v>1.144</v>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
@@ -11225,10 +11225,10 @@
         <v>243</v>
       </c>
       <c r="K177" s="22" t="n">
-        <v>242.971</v>
+        <v>242.936</v>
       </c>
       <c r="L177" s="22" t="n">
-        <v>0.029</v>
+        <v>0.064</v>
       </c>
       <c r="M177" s="5" t="inlineStr">
         <is>
@@ -11270,10 +11270,10 @@
         <v>243</v>
       </c>
       <c r="G178" s="24" t="n">
-        <v>242.971</v>
+        <v>242.936</v>
       </c>
       <c r="H178" s="24" t="n">
-        <v>0.029</v>
+        <v>0.064</v>
       </c>
       <c r="I178" s="9" t="inlineStr">
         <is>
@@ -11284,10 +11284,10 @@
         <v>245</v>
       </c>
       <c r="K178" s="24" t="n">
-        <v>244.995</v>
+        <v>244.96</v>
       </c>
       <c r="L178" s="24" t="n">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="M178" s="9" t="inlineStr">
         <is>
@@ -11329,10 +11329,10 @@
         <v>245</v>
       </c>
       <c r="G179" s="22" t="n">
-        <v>244.995</v>
+        <v>244.96</v>
       </c>
       <c r="H179" s="22" t="n">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
@@ -11343,10 +11343,10 @@
         <v>249</v>
       </c>
       <c r="K179" s="22" t="n">
-        <v>248.904</v>
+        <v>248.869</v>
       </c>
       <c r="L179" s="22" t="n">
-        <v>0.096</v>
+        <v>0.131</v>
       </c>
       <c r="M179" s="5" t="inlineStr">
         <is>
@@ -11388,10 +11388,10 @@
         <v>249</v>
       </c>
       <c r="G180" s="24" t="n">
-        <v>248.904</v>
+        <v>248.869</v>
       </c>
       <c r="H180" s="24" t="n">
-        <v>0.096</v>
+        <v>0.131</v>
       </c>
       <c r="I180" s="9" t="inlineStr">
         <is>
@@ -11402,10 +11402,10 @@
         <v>251</v>
       </c>
       <c r="K180" s="24" t="n">
-        <v>250.998</v>
+        <v>250.963</v>
       </c>
       <c r="L180" s="24" t="n">
-        <v>0.002</v>
+        <v>0.037</v>
       </c>
       <c r="M180" s="9" t="inlineStr">
         <is>
@@ -11447,10 +11447,10 @@
         <v>251</v>
       </c>
       <c r="G181" s="22" t="n">
-        <v>250.998</v>
+        <v>250.963</v>
       </c>
       <c r="H181" s="22" t="n">
-        <v>0.002</v>
+        <v>0.037</v>
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
@@ -11461,10 +11461,10 @@
         <v>256</v>
       </c>
       <c r="K181" s="22" t="n">
-        <v>255.675</v>
+        <v>255.64</v>
       </c>
       <c r="L181" s="22" t="n">
-        <v>0.325</v>
+        <v>0.36</v>
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
@@ -11506,10 +11506,10 @@
         <v>256</v>
       </c>
       <c r="G182" s="24" t="n">
-        <v>255.675</v>
+        <v>255.64</v>
       </c>
       <c r="H182" s="24" t="n">
-        <v>0.325</v>
+        <v>0.36</v>
       </c>
       <c r="I182" s="9" t="inlineStr">
         <is>
@@ -11520,10 +11520,10 @@
         <v>259</v>
       </c>
       <c r="K182" s="24" t="n">
-        <v>258.816</v>
+        <v>258.781</v>
       </c>
       <c r="L182" s="24" t="n">
-        <v>0.184</v>
+        <v>0.219</v>
       </c>
       <c r="M182" s="9" t="inlineStr">
         <is>
@@ -11565,10 +11565,10 @@
         <v>259</v>
       </c>
       <c r="G183" s="22" t="n">
-        <v>258.816</v>
+        <v>258.781</v>
       </c>
       <c r="H183" s="22" t="n">
-        <v>0.184</v>
+        <v>0.219</v>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
@@ -11579,10 +11579,10 @@
         <v>261</v>
       </c>
       <c r="K183" s="22" t="n">
-        <v>260.91</v>
+        <v>260.875</v>
       </c>
       <c r="L183" s="22" t="n">
-        <v>0.09</v>
+        <v>0.125</v>
       </c>
       <c r="M183" s="5" t="inlineStr">
         <is>
@@ -11624,10 +11624,10 @@
         <v>261</v>
       </c>
       <c r="G184" s="24" t="n">
-        <v>260.91</v>
+        <v>260.875</v>
       </c>
       <c r="H184" s="24" t="n">
-        <v>0.09</v>
+        <v>0.125</v>
       </c>
       <c r="I184" s="9" t="inlineStr">
         <is>
@@ -11638,10 +11638,10 @@
         <v>263</v>
       </c>
       <c r="K184" s="24" t="n">
-        <v>263.143</v>
+        <v>263.178</v>
       </c>
       <c r="L184" s="24" t="n">
-        <v>0.143</v>
+        <v>0.178</v>
       </c>
       <c r="M184" s="9" t="inlineStr">
         <is>
@@ -11683,10 +11683,10 @@
         <v>263</v>
       </c>
       <c r="G185" s="22" t="n">
-        <v>263.143</v>
+        <v>263.178</v>
       </c>
       <c r="H185" s="22" t="n">
-        <v>0.143</v>
+        <v>0.178</v>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
@@ -11697,22 +11697,22 @@
         <v>266</v>
       </c>
       <c r="K185" s="22" t="n">
-        <v>265.516</v>
+        <v>265.481</v>
       </c>
       <c r="L185" s="22" t="n">
-        <v>0.484</v>
+        <v>0.519</v>
       </c>
       <c r="M185" s="5" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N185" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="O185" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O185" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc Start</t>
         </is>
       </c>
     </row>
@@ -11742,24 +11742,24 @@
         <v>266</v>
       </c>
       <c r="G186" s="24" t="n">
-        <v>265.516</v>
+        <v>265.481</v>
       </c>
       <c r="H186" s="24" t="n">
-        <v>0.484</v>
+        <v>0.519</v>
       </c>
       <c r="I186" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="J186" s="24" t="n">
         <v>268</v>
       </c>
       <c r="K186" s="24" t="n">
-        <v>267.541</v>
+        <v>267.506</v>
       </c>
       <c r="L186" s="24" t="n">
-        <v>0.459</v>
+        <v>0.494</v>
       </c>
       <c r="M186" s="9" t="inlineStr">
         <is>
@@ -11769,9 +11769,9 @@
       <c r="N186" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="O186" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O186" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc End</t>
         </is>
       </c>
     </row>
@@ -11801,10 +11801,10 @@
         <v>268</v>
       </c>
       <c r="G187" s="22" t="n">
-        <v>267.541</v>
+        <v>267.506</v>
       </c>
       <c r="H187" s="22" t="n">
-        <v>0.459</v>
+        <v>0.494</v>
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
@@ -11815,10 +11815,10 @@
         <v>269</v>
       </c>
       <c r="K187" s="22" t="n">
-        <v>269.216</v>
+        <v>269.251</v>
       </c>
       <c r="L187" s="22" t="n">
-        <v>0.216</v>
+        <v>0.251</v>
       </c>
       <c r="M187" s="5" t="inlineStr">
         <is>
@@ -11860,10 +11860,10 @@
         <v>269</v>
       </c>
       <c r="G188" s="24" t="n">
-        <v>269.216</v>
+        <v>269.251</v>
       </c>
       <c r="H188" s="24" t="n">
-        <v>0.216</v>
+        <v>0.251</v>
       </c>
       <c r="I188" s="9" t="inlineStr">
         <is>
@@ -11874,10 +11874,10 @@
         <v>271</v>
       </c>
       <c r="K188" s="24" t="n">
-        <v>271.31</v>
+        <v>271.345</v>
       </c>
       <c r="L188" s="24" t="n">
-        <v>0.31</v>
+        <v>0.345</v>
       </c>
       <c r="M188" s="9" t="inlineStr">
         <is>
@@ -11919,10 +11919,10 @@
         <v>271</v>
       </c>
       <c r="G189" s="22" t="n">
-        <v>271.31</v>
+        <v>271.345</v>
       </c>
       <c r="H189" s="22" t="n">
-        <v>0.31</v>
+        <v>0.345</v>
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
@@ -11933,10 +11933,10 @@
         <v>274</v>
       </c>
       <c r="K189" s="22" t="n">
-        <v>273.753</v>
+        <v>273.718</v>
       </c>
       <c r="L189" s="22" t="n">
-        <v>0.247</v>
+        <v>0.282</v>
       </c>
       <c r="M189" s="5" t="inlineStr">
         <is>
@@ -11978,10 +11978,10 @@
         <v>274</v>
       </c>
       <c r="G190" s="24" t="n">
-        <v>273.753</v>
+        <v>273.718</v>
       </c>
       <c r="H190" s="24" t="n">
-        <v>0.247</v>
+        <v>0.282</v>
       </c>
       <c r="I190" s="9" t="inlineStr">
         <is>
@@ -11992,10 +11992,10 @@
         <v>278</v>
       </c>
       <c r="K190" s="24" t="n">
-        <v>278.778</v>
+        <v>278.813</v>
       </c>
       <c r="L190" s="24" t="n">
-        <v>0.778</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="M190" s="9" t="inlineStr">
         <is>
@@ -12037,10 +12037,10 @@
         <v>278</v>
       </c>
       <c r="G191" s="22" t="n">
-        <v>278.778</v>
+        <v>278.813</v>
       </c>
       <c r="H191" s="22" t="n">
-        <v>0.778</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
@@ -12051,10 +12051,10 @@
         <v>280</v>
       </c>
       <c r="K191" s="22" t="n">
-        <v>280.244</v>
+        <v>280.279</v>
       </c>
       <c r="L191" s="22" t="n">
-        <v>0.244</v>
+        <v>0.279</v>
       </c>
       <c r="M191" s="5" t="inlineStr">
         <is>
@@ -12096,10 +12096,10 @@
         <v>280</v>
       </c>
       <c r="G192" s="24" t="n">
-        <v>280.244</v>
+        <v>280.279</v>
       </c>
       <c r="H192" s="24" t="n">
-        <v>0.244</v>
+        <v>0.279</v>
       </c>
       <c r="I192" s="9" t="inlineStr">
         <is>
@@ -12110,10 +12110,10 @@
         <v>283</v>
       </c>
       <c r="K192" s="24" t="n">
-        <v>282.478</v>
+        <v>282.443</v>
       </c>
       <c r="L192" s="24" t="n">
-        <v>0.522</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="M192" s="9" t="inlineStr">
         <is>
@@ -12155,10 +12155,10 @@
         <v>283</v>
       </c>
       <c r="G193" s="22" t="n">
-        <v>282.478</v>
+        <v>282.443</v>
       </c>
       <c r="H193" s="22" t="n">
-        <v>0.522</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
@@ -12169,10 +12169,10 @@
         <v>286</v>
       </c>
       <c r="K193" s="22" t="n">
-        <v>285.479</v>
+        <v>285.444</v>
       </c>
       <c r="L193" s="22" t="n">
-        <v>0.521</v>
+        <v>0.556</v>
       </c>
       <c r="M193" s="5" t="inlineStr">
         <is>
@@ -12214,10 +12214,10 @@
         <v>286</v>
       </c>
       <c r="G194" s="24" t="n">
-        <v>285.479</v>
+        <v>285.444</v>
       </c>
       <c r="H194" s="24" t="n">
-        <v>0.521</v>
+        <v>0.556</v>
       </c>
       <c r="I194" s="9" t="inlineStr">
         <is>
@@ -12228,10 +12228,10 @@
         <v>288</v>
       </c>
       <c r="K194" s="24" t="n">
-        <v>287.573</v>
+        <v>287.538</v>
       </c>
       <c r="L194" s="24" t="n">
-        <v>0.427</v>
+        <v>0.462</v>
       </c>
       <c r="M194" s="9" t="inlineStr">
         <is>
@@ -12273,10 +12273,10 @@
         <v>288</v>
       </c>
       <c r="G195" s="22" t="n">
-        <v>287.573</v>
+        <v>287.538</v>
       </c>
       <c r="H195" s="22" t="n">
-        <v>0.427</v>
+        <v>0.462</v>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
@@ -12287,10 +12287,10 @@
         <v>293</v>
       </c>
       <c r="K195" s="22" t="n">
-        <v>293.436</v>
+        <v>293.471</v>
       </c>
       <c r="L195" s="22" t="n">
-        <v>0.436</v>
+        <v>0.471</v>
       </c>
       <c r="M195" s="5" t="inlineStr">
         <is>
@@ -12332,10 +12332,10 @@
         <v>293</v>
       </c>
       <c r="G196" s="24" t="n">
-        <v>293.436</v>
+        <v>293.471</v>
       </c>
       <c r="H196" s="24" t="n">
-        <v>0.436</v>
+        <v>0.471</v>
       </c>
       <c r="I196" s="9" t="inlineStr">
         <is>
@@ -12346,10 +12346,10 @@
         <v>295</v>
       </c>
       <c r="K196" s="24" t="n">
-        <v>295.111</v>
+        <v>295.146</v>
       </c>
       <c r="L196" s="24" t="n">
-        <v>0.111</v>
+        <v>0.146</v>
       </c>
       <c r="M196" s="9" t="inlineStr">
         <is>
@@ -12391,10 +12391,10 @@
         <v>295</v>
       </c>
       <c r="G197" s="22" t="n">
-        <v>295.111</v>
+        <v>295.146</v>
       </c>
       <c r="H197" s="22" t="n">
-        <v>0.111</v>
+        <v>0.146</v>
       </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
@@ -12405,10 +12405,10 @@
         <v>298</v>
       </c>
       <c r="K197" s="22" t="n">
-        <v>297.554</v>
+        <v>297.519</v>
       </c>
       <c r="L197" s="22" t="n">
-        <v>0.446</v>
+        <v>0.481</v>
       </c>
       <c r="M197" s="5" t="inlineStr">
         <is>
@@ -12450,10 +12450,10 @@
         <v>298</v>
       </c>
       <c r="G198" s="24" t="n">
-        <v>297.554</v>
+        <v>297.519</v>
       </c>
       <c r="H198" s="24" t="n">
-        <v>0.446</v>
+        <v>0.481</v>
       </c>
       <c r="I198" s="9" t="inlineStr">
         <is>
@@ -12464,10 +12464,10 @@
         <v>305</v>
       </c>
       <c r="K198" s="24" t="n">
-        <v>304.883</v>
+        <v>304.848</v>
       </c>
       <c r="L198" s="24" t="n">
-        <v>0.117</v>
+        <v>0.152</v>
       </c>
       <c r="M198" s="9" t="inlineStr">
         <is>
@@ -12509,10 +12509,10 @@
         <v>305</v>
       </c>
       <c r="G199" s="22" t="n">
-        <v>304.883</v>
+        <v>304.848</v>
       </c>
       <c r="H199" s="22" t="n">
-        <v>0.117</v>
+        <v>0.152</v>
       </c>
       <c r="I199" s="5" t="inlineStr">
         <is>
@@ -12523,10 +12523,10 @@
         <v>306</v>
       </c>
       <c r="K199" s="22" t="n">
-        <v>306.698</v>
+        <v>306.733</v>
       </c>
       <c r="L199" s="22" t="n">
-        <v>0.698</v>
+        <v>0.733</v>
       </c>
       <c r="M199" s="5" t="inlineStr">
         <is>
@@ -12568,10 +12568,10 @@
         <v>306</v>
       </c>
       <c r="G200" s="24" t="n">
-        <v>306.698</v>
+        <v>306.733</v>
       </c>
       <c r="H200" s="24" t="n">
-        <v>0.698</v>
+        <v>0.733</v>
       </c>
       <c r="I200" s="9" t="inlineStr">
         <is>
@@ -12582,10 +12582,10 @@
         <v>314</v>
       </c>
       <c r="K200" s="24" t="n">
-        <v>314.236</v>
+        <v>314.271</v>
       </c>
       <c r="L200" s="24" t="n">
-        <v>0.236</v>
+        <v>0.271</v>
       </c>
       <c r="M200" s="9" t="inlineStr">
         <is>
@@ -12627,10 +12627,10 @@
         <v>314</v>
       </c>
       <c r="G201" s="22" t="n">
-        <v>314.236</v>
+        <v>314.271</v>
       </c>
       <c r="H201" s="22" t="n">
-        <v>0.236</v>
+        <v>0.271</v>
       </c>
       <c r="I201" s="5" t="inlineStr">
         <is>
@@ -12641,10 +12641,10 @@
         <v>321</v>
       </c>
       <c r="K201" s="22" t="n">
-        <v>321.007</v>
+        <v>320.972</v>
       </c>
       <c r="L201" s="22" t="n">
-        <v>0.007</v>
+        <v>0.028</v>
       </c>
       <c r="M201" s="5" t="inlineStr">
         <is>
@@ -12686,10 +12686,10 @@
         <v>321</v>
       </c>
       <c r="G202" s="24" t="n">
-        <v>321.007</v>
+        <v>320.972</v>
       </c>
       <c r="H202" s="24" t="n">
-        <v>0.007</v>
+        <v>0.028</v>
       </c>
       <c r="I202" s="9" t="inlineStr">
         <is>
@@ -12741,10 +12741,10 @@
         <v>1</v>
       </c>
       <c r="G203" s="22" t="n">
-        <v>1.804</v>
+        <v>1.837</v>
       </c>
       <c r="H203" s="22" t="n">
-        <v>0.804</v>
+        <v>0.837</v>
       </c>
       <c r="I203" s="5" t="inlineStr">
         <is>
@@ -12755,10 +12755,10 @@
         <v>2</v>
       </c>
       <c r="K203" s="22" t="n">
-        <v>1.871</v>
+        <v>1.837</v>
       </c>
       <c r="L203" s="22" t="n">
-        <v>0.129</v>
+        <v>0.163</v>
       </c>
       <c r="M203" s="5" t="inlineStr">
         <is>
@@ -12796,10 +12796,10 @@
         <v>2</v>
       </c>
       <c r="G204" s="24" t="n">
-        <v>1.871</v>
+        <v>1.837</v>
       </c>
       <c r="H204" s="24" t="n">
-        <v>0.129</v>
+        <v>0.163</v>
       </c>
       <c r="I204" s="9" t="inlineStr">
         <is>
@@ -12810,10 +12810,10 @@
         <v>7</v>
       </c>
       <c r="K204" s="24" t="n">
-        <v>6.948</v>
+        <v>6.915</v>
       </c>
       <c r="L204" s="24" t="n">
-        <v>0.052</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="M204" s="9" t="inlineStr">
         <is>
@@ -12851,10 +12851,10 @@
         <v>7</v>
       </c>
       <c r="G205" s="22" t="n">
-        <v>6.948</v>
+        <v>6.915</v>
       </c>
       <c r="H205" s="22" t="n">
-        <v>0.052</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I205" s="5" t="inlineStr">
         <is>
@@ -12865,10 +12865,10 @@
         <v>9</v>
       </c>
       <c r="K205" s="22" t="n">
-        <v>9.42</v>
+        <v>9.454000000000001</v>
       </c>
       <c r="L205" s="22" t="n">
-        <v>0.42</v>
+        <v>0.454</v>
       </c>
       <c r="M205" s="5" t="inlineStr">
         <is>
@@ -12906,10 +12906,10 @@
         <v>9</v>
       </c>
       <c r="G206" s="24" t="n">
-        <v>9.42</v>
+        <v>9.454000000000001</v>
       </c>
       <c r="H206" s="24" t="n">
-        <v>0.42</v>
+        <v>0.454</v>
       </c>
       <c r="I206" s="9" t="inlineStr">
         <is>
@@ -12920,10 +12920,10 @@
         <v>13</v>
       </c>
       <c r="K206" s="24" t="n">
-        <v>13.161</v>
+        <v>13.194</v>
       </c>
       <c r="L206" s="24" t="n">
-        <v>0.161</v>
+        <v>0.194</v>
       </c>
       <c r="M206" s="9" t="inlineStr">
         <is>
@@ -12961,10 +12961,10 @@
         <v>13</v>
       </c>
       <c r="G207" s="22" t="n">
-        <v>13.161</v>
+        <v>13.194</v>
       </c>
       <c r="H207" s="22" t="n">
-        <v>0.161</v>
+        <v>0.194</v>
       </c>
       <c r="I207" s="5" t="inlineStr">
         <is>
@@ -12975,10 +12975,10 @@
         <v>14</v>
       </c>
       <c r="K207" s="22" t="n">
-        <v>13.763</v>
+        <v>13.729</v>
       </c>
       <c r="L207" s="22" t="n">
-        <v>0.237</v>
+        <v>0.271</v>
       </c>
       <c r="M207" s="5" t="inlineStr">
         <is>
@@ -13016,10 +13016,10 @@
         <v>14</v>
       </c>
       <c r="G208" s="24" t="n">
-        <v>13.763</v>
+        <v>13.729</v>
       </c>
       <c r="H208" s="24" t="n">
-        <v>0.237</v>
+        <v>0.271</v>
       </c>
       <c r="I208" s="9" t="inlineStr">
         <is>
@@ -13030,10 +13030,10 @@
         <v>16</v>
       </c>
       <c r="K208" s="24" t="n">
-        <v>16.034</v>
+        <v>16.067</v>
       </c>
       <c r="L208" s="24" t="n">
-        <v>0.034</v>
+        <v>0.067</v>
       </c>
       <c r="M208" s="9" t="inlineStr">
         <is>
@@ -13071,10 +13071,10 @@
         <v>16</v>
       </c>
       <c r="G209" s="22" t="n">
-        <v>16.034</v>
+        <v>16.067</v>
       </c>
       <c r="H209" s="22" t="n">
-        <v>0.034</v>
+        <v>0.067</v>
       </c>
       <c r="I209" s="5" t="inlineStr">
         <is>
@@ -13085,10 +13085,10 @@
         <v>19</v>
       </c>
       <c r="K209" s="22" t="n">
-        <v>18.974</v>
+        <v>18.941</v>
       </c>
       <c r="L209" s="22" t="n">
-        <v>0.026</v>
+        <v>0.059</v>
       </c>
       <c r="M209" s="5" t="inlineStr">
         <is>
@@ -13126,10 +13126,10 @@
         <v>19</v>
       </c>
       <c r="G210" s="24" t="n">
-        <v>18.974</v>
+        <v>18.941</v>
       </c>
       <c r="H210" s="24" t="n">
-        <v>0.026</v>
+        <v>0.059</v>
       </c>
       <c r="I210" s="9" t="inlineStr">
         <is>
@@ -13140,10 +13140,10 @@
         <v>25</v>
       </c>
       <c r="K210" s="24" t="n">
-        <v>25.12</v>
+        <v>25.154</v>
       </c>
       <c r="L210" s="24" t="n">
-        <v>0.12</v>
+        <v>0.154</v>
       </c>
       <c r="M210" s="9" t="inlineStr">
         <is>
@@ -13181,10 +13181,10 @@
         <v>25</v>
       </c>
       <c r="G211" s="22" t="n">
-        <v>25.12</v>
+        <v>25.154</v>
       </c>
       <c r="H211" s="22" t="n">
-        <v>0.12</v>
+        <v>0.154</v>
       </c>
       <c r="I211" s="5" t="inlineStr">
         <is>
@@ -13195,10 +13195,10 @@
         <v>26</v>
       </c>
       <c r="K211" s="22" t="n">
-        <v>25.187</v>
+        <v>25.154</v>
       </c>
       <c r="L211" s="22" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.846</v>
       </c>
       <c r="M211" s="5" t="inlineStr">
         <is>
@@ -13236,10 +13236,10 @@
         <v>26</v>
       </c>
       <c r="G212" s="24" t="n">
-        <v>25.187</v>
+        <v>25.154</v>
       </c>
       <c r="H212" s="24" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.846</v>
       </c>
       <c r="I212" s="9" t="inlineStr">
         <is>
@@ -13250,10 +13250,10 @@
         <v>27</v>
       </c>
       <c r="K212" s="24" t="n">
-        <v>26.924</v>
+        <v>26.89</v>
       </c>
       <c r="L212" s="24" t="n">
-        <v>0.076</v>
+        <v>0.11</v>
       </c>
       <c r="M212" s="9" t="inlineStr">
         <is>
@@ -13291,10 +13291,10 @@
         <v>27</v>
       </c>
       <c r="G213" s="22" t="n">
-        <v>26.924</v>
+        <v>26.89</v>
       </c>
       <c r="H213" s="22" t="n">
-        <v>0.076</v>
+        <v>0.11</v>
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
@@ -13305,10 +13305,10 @@
         <v>29</v>
       </c>
       <c r="K213" s="22" t="n">
-        <v>28.728</v>
+        <v>28.695</v>
       </c>
       <c r="L213" s="22" t="n">
-        <v>0.272</v>
+        <v>0.305</v>
       </c>
       <c r="M213" s="5" t="inlineStr">
         <is>
@@ -13346,10 +13346,10 @@
         <v>29</v>
       </c>
       <c r="G214" s="24" t="n">
-        <v>28.728</v>
+        <v>28.695</v>
       </c>
       <c r="H214" s="24" t="n">
-        <v>0.272</v>
+        <v>0.305</v>
       </c>
       <c r="I214" s="9" t="inlineStr">
         <is>
@@ -13360,10 +13360,10 @@
         <v>30</v>
       </c>
       <c r="K214" s="24" t="n">
-        <v>29.93</v>
+        <v>29.897</v>
       </c>
       <c r="L214" s="24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="M214" s="9" t="inlineStr">
         <is>
@@ -13401,10 +13401,10 @@
         <v>30</v>
       </c>
       <c r="G215" s="22" t="n">
-        <v>29.93</v>
+        <v>29.897</v>
       </c>
       <c r="H215" s="22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="I215" s="5" t="inlineStr">
         <is>
@@ -13415,10 +13415,10 @@
         <v>32</v>
       </c>
       <c r="K215" s="22" t="n">
-        <v>31.868</v>
+        <v>31.834</v>
       </c>
       <c r="L215" s="22" t="n">
-        <v>0.132</v>
+        <v>0.166</v>
       </c>
       <c r="M215" s="5" t="inlineStr">
         <is>
@@ -13456,10 +13456,10 @@
         <v>32</v>
       </c>
       <c r="G216" s="24" t="n">
-        <v>31.868</v>
+        <v>31.834</v>
       </c>
       <c r="H216" s="24" t="n">
-        <v>0.132</v>
+        <v>0.166</v>
       </c>
       <c r="I216" s="9" t="inlineStr">
         <is>
@@ -13470,10 +13470,10 @@
         <v>34</v>
       </c>
       <c r="K216" s="24" t="n">
-        <v>34.006</v>
+        <v>33.972</v>
       </c>
       <c r="L216" s="24" t="n">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
       <c r="M216" s="9" t="inlineStr">
         <is>
@@ -13511,10 +13511,10 @@
         <v>34</v>
       </c>
       <c r="G217" s="22" t="n">
-        <v>34.006</v>
+        <v>33.972</v>
       </c>
       <c r="H217" s="22" t="n">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
@@ -13525,10 +13525,10 @@
         <v>36</v>
       </c>
       <c r="K217" s="22" t="n">
-        <v>36.144</v>
+        <v>36.177</v>
       </c>
       <c r="L217" s="22" t="n">
-        <v>0.144</v>
+        <v>0.177</v>
       </c>
       <c r="M217" s="5" t="inlineStr">
         <is>
@@ -13566,10 +13566,10 @@
         <v>36</v>
       </c>
       <c r="G218" s="24" t="n">
-        <v>36.144</v>
+        <v>36.177</v>
       </c>
       <c r="H218" s="24" t="n">
-        <v>0.144</v>
+        <v>0.177</v>
       </c>
       <c r="I218" s="9" t="inlineStr">
         <is>
@@ -13580,10 +13580,10 @@
         <v>40</v>
       </c>
       <c r="K218" s="24" t="n">
-        <v>40.019</v>
+        <v>40.052</v>
       </c>
       <c r="L218" s="24" t="n">
-        <v>0.019</v>
+        <v>0.052</v>
       </c>
       <c r="M218" s="9" t="inlineStr">
         <is>
@@ -13621,10 +13621,10 @@
         <v>40</v>
       </c>
       <c r="G219" s="22" t="n">
-        <v>40.019</v>
+        <v>40.052</v>
       </c>
       <c r="H219" s="22" t="n">
-        <v>0.019</v>
+        <v>0.052</v>
       </c>
       <c r="I219" s="5" t="inlineStr">
         <is>
@@ -13635,10 +13635,10 @@
         <v>42</v>
       </c>
       <c r="K219" s="22" t="n">
-        <v>41.756</v>
+        <v>41.722</v>
       </c>
       <c r="L219" s="22" t="n">
-        <v>0.244</v>
+        <v>0.278</v>
       </c>
       <c r="M219" s="5" t="inlineStr">
         <is>
@@ -13676,10 +13676,10 @@
         <v>42</v>
       </c>
       <c r="G220" s="24" t="n">
-        <v>41.756</v>
+        <v>41.722</v>
       </c>
       <c r="H220" s="24" t="n">
-        <v>0.244</v>
+        <v>0.278</v>
       </c>
       <c r="I220" s="9" t="inlineStr">
         <is>
@@ -13690,10 +13690,10 @@
         <v>46</v>
       </c>
       <c r="K220" s="24" t="n">
-        <v>45.831</v>
+        <v>45.797</v>
       </c>
       <c r="L220" s="24" t="n">
-        <v>0.169</v>
+        <v>0.203</v>
       </c>
       <c r="M220" s="9" t="inlineStr">
         <is>
@@ -13731,10 +13731,10 @@
         <v>46</v>
       </c>
       <c r="G221" s="22" t="n">
-        <v>45.831</v>
+        <v>45.797</v>
       </c>
       <c r="H221" s="22" t="n">
-        <v>0.169</v>
+        <v>0.203</v>
       </c>
       <c r="I221" s="5" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         <v>48</v>
       </c>
       <c r="K221" s="22" t="n">
-        <v>47.835</v>
+        <v>47.802</v>
       </c>
       <c r="L221" s="22" t="n">
-        <v>0.165</v>
+        <v>0.198</v>
       </c>
       <c r="M221" s="5" t="inlineStr">
         <is>
@@ -13786,10 +13786,10 @@
         <v>48</v>
       </c>
       <c r="G222" s="24" t="n">
-        <v>47.835</v>
+        <v>47.802</v>
       </c>
       <c r="H222" s="24" t="n">
-        <v>0.165</v>
+        <v>0.198</v>
       </c>
       <c r="I222" s="9" t="inlineStr">
         <is>
@@ -13800,10 +13800,10 @@
         <v>51</v>
       </c>
       <c r="K222" s="24" t="n">
-        <v>51.309</v>
+        <v>51.343</v>
       </c>
       <c r="L222" s="24" t="n">
-        <v>0.309</v>
+        <v>0.343</v>
       </c>
       <c r="M222" s="9" t="inlineStr">
         <is>
@@ -13841,10 +13841,10 @@
         <v>51</v>
       </c>
       <c r="G223" s="22" t="n">
-        <v>51.309</v>
+        <v>51.343</v>
       </c>
       <c r="H223" s="22" t="n">
-        <v>0.309</v>
+        <v>0.343</v>
       </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
@@ -13855,10 +13855,10 @@
         <v>54</v>
       </c>
       <c r="K223" s="22" t="n">
-        <v>53.581</v>
+        <v>53.547</v>
       </c>
       <c r="L223" s="22" t="n">
-        <v>0.419</v>
+        <v>0.453</v>
       </c>
       <c r="M223" s="5" t="inlineStr">
         <is>
@@ -13896,10 +13896,10 @@
         <v>54</v>
       </c>
       <c r="G224" s="24" t="n">
-        <v>53.581</v>
+        <v>53.547</v>
       </c>
       <c r="H224" s="24" t="n">
-        <v>0.419</v>
+        <v>0.453</v>
       </c>
       <c r="I224" s="9" t="inlineStr">
         <is>
@@ -13910,10 +13910,10 @@
         <v>57</v>
       </c>
       <c r="K224" s="24" t="n">
-        <v>56.988</v>
+        <v>57.022</v>
       </c>
       <c r="L224" s="24" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="M224" s="9" t="inlineStr">
         <is>
@@ -13951,10 +13951,10 @@
         <v>57</v>
       </c>
       <c r="G225" s="22" t="n">
-        <v>56.988</v>
+        <v>57.022</v>
       </c>
       <c r="H225" s="22" t="n">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="I225" s="5" t="inlineStr">
         <is>
@@ -13965,10 +13965,10 @@
         <v>59</v>
       </c>
       <c r="K225" s="22" t="n">
-        <v>58.725</v>
+        <v>58.692</v>
       </c>
       <c r="L225" s="22" t="n">
-        <v>0.275</v>
+        <v>0.308</v>
       </c>
       <c r="M225" s="5" t="inlineStr">
         <is>
@@ -14006,10 +14006,10 @@
         <v>59</v>
       </c>
       <c r="G226" s="24" t="n">
-        <v>58.725</v>
+        <v>58.692</v>
       </c>
       <c r="H226" s="24" t="n">
-        <v>0.275</v>
+        <v>0.308</v>
       </c>
       <c r="I226" s="9" t="inlineStr">
         <is>
@@ -14020,10 +14020,10 @@
         <v>63</v>
       </c>
       <c r="K226" s="24" t="n">
-        <v>63.001</v>
+        <v>63.034</v>
       </c>
       <c r="L226" s="24" t="n">
-        <v>0.001</v>
+        <v>0.034</v>
       </c>
       <c r="M226" s="9" t="inlineStr">
         <is>
@@ -14061,10 +14061,10 @@
         <v>63</v>
       </c>
       <c r="G227" s="22" t="n">
-        <v>63.001</v>
+        <v>63.034</v>
       </c>
       <c r="H227" s="22" t="n">
-        <v>0.001</v>
+        <v>0.034</v>
       </c>
       <c r="I227" s="5" t="inlineStr">
         <is>
@@ -14075,10 +14075,10 @@
         <v>65</v>
       </c>
       <c r="K227" s="22" t="n">
-        <v>64.871</v>
+        <v>64.83799999999999</v>
       </c>
       <c r="L227" s="22" t="n">
-        <v>0.129</v>
+        <v>0.162</v>
       </c>
       <c r="M227" s="5" t="inlineStr">
         <is>
@@ -14116,10 +14116,10 @@
         <v>65</v>
       </c>
       <c r="G228" s="24" t="n">
-        <v>64.871</v>
+        <v>64.83799999999999</v>
       </c>
       <c r="H228" s="24" t="n">
-        <v>0.129</v>
+        <v>0.162</v>
       </c>
       <c r="I228" s="9" t="inlineStr">
         <is>
@@ -14130,10 +14130,10 @@
         <v>66</v>
       </c>
       <c r="K228" s="24" t="n">
-        <v>66.208</v>
+        <v>66.241</v>
       </c>
       <c r="L228" s="24" t="n">
-        <v>0.208</v>
+        <v>0.241</v>
       </c>
       <c r="M228" s="9" t="inlineStr">
         <is>
@@ -14171,10 +14171,10 @@
         <v>66</v>
       </c>
       <c r="G229" s="22" t="n">
-        <v>66.208</v>
+        <v>66.241</v>
       </c>
       <c r="H229" s="22" t="n">
-        <v>0.208</v>
+        <v>0.241</v>
       </c>
       <c r="I229" s="5" t="inlineStr">
         <is>
@@ -14185,10 +14185,10 @@
         <v>73</v>
       </c>
       <c r="K229" s="22" t="n">
-        <v>73.15600000000001</v>
+        <v>73.19</v>
       </c>
       <c r="L229" s="22" t="n">
-        <v>0.156</v>
+        <v>0.19</v>
       </c>
       <c r="M229" s="5" t="inlineStr">
         <is>
@@ -14226,10 +14226,10 @@
         <v>73</v>
       </c>
       <c r="G230" s="24" t="n">
-        <v>73.15600000000001</v>
+        <v>73.19</v>
       </c>
       <c r="H230" s="24" t="n">
-        <v>0.156</v>
+        <v>0.19</v>
       </c>
       <c r="I230" s="9" t="inlineStr">
         <is>
@@ -14240,10 +14240,10 @@
         <v>76</v>
       </c>
       <c r="K230" s="24" t="n">
-        <v>76.29600000000001</v>
+        <v>76.32899999999999</v>
       </c>
       <c r="L230" s="24" t="n">
-        <v>0.296</v>
+        <v>0.329</v>
       </c>
       <c r="M230" s="9" t="inlineStr">
         <is>
@@ -14281,10 +14281,10 @@
         <v>76</v>
       </c>
       <c r="G231" s="22" t="n">
-        <v>76.29600000000001</v>
+        <v>76.32899999999999</v>
       </c>
       <c r="H231" s="22" t="n">
-        <v>0.296</v>
+        <v>0.329</v>
       </c>
       <c r="I231" s="5" t="inlineStr">
         <is>
@@ -14295,10 +14295,10 @@
         <v>78</v>
       </c>
       <c r="K231" s="22" t="n">
-        <v>78.233</v>
+        <v>78.267</v>
       </c>
       <c r="L231" s="22" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="M231" s="5" t="inlineStr">
         <is>
@@ -14336,10 +14336,10 @@
         <v>78</v>
       </c>
       <c r="G232" s="24" t="n">
-        <v>78.233</v>
+        <v>78.267</v>
       </c>
       <c r="H232" s="24" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="I232" s="9" t="inlineStr">
         <is>
@@ -14350,10 +14350,10 @@
         <v>80</v>
       </c>
       <c r="K232" s="24" t="n">
-        <v>79.636</v>
+        <v>79.602</v>
       </c>
       <c r="L232" s="24" t="n">
-        <v>0.364</v>
+        <v>0.398</v>
       </c>
       <c r="M232" s="9" t="inlineStr">
         <is>
@@ -14391,10 +14391,10 @@
         <v>80</v>
       </c>
       <c r="G233" s="22" t="n">
-        <v>79.636</v>
+        <v>79.602</v>
       </c>
       <c r="H233" s="22" t="n">
-        <v>0.364</v>
+        <v>0.398</v>
       </c>
       <c r="I233" s="5" t="inlineStr">
         <is>
@@ -14405,10 +14405,10 @@
         <v>83</v>
       </c>
       <c r="K233" s="22" t="n">
-        <v>83.31100000000001</v>
+        <v>83.345</v>
       </c>
       <c r="L233" s="22" t="n">
-        <v>0.311</v>
+        <v>0.345</v>
       </c>
       <c r="M233" s="5" t="inlineStr">
         <is>
@@ -14446,10 +14446,10 @@
         <v>83</v>
       </c>
       <c r="G234" s="24" t="n">
-        <v>83.31100000000001</v>
+        <v>83.345</v>
       </c>
       <c r="H234" s="24" t="n">
-        <v>0.311</v>
+        <v>0.345</v>
       </c>
       <c r="I234" s="9" t="inlineStr">
         <is>
@@ -14460,10 +14460,10 @@
         <v>86</v>
       </c>
       <c r="K234" s="24" t="n">
-        <v>85.649</v>
+        <v>85.61499999999999</v>
       </c>
       <c r="L234" s="24" t="n">
-        <v>0.351</v>
+        <v>0.385</v>
       </c>
       <c r="M234" s="9" t="inlineStr">
         <is>
@@ -14501,10 +14501,10 @@
         <v>86</v>
       </c>
       <c r="G235" s="22" t="n">
-        <v>85.649</v>
+        <v>85.61499999999999</v>
       </c>
       <c r="H235" s="22" t="n">
-        <v>0.351</v>
+        <v>0.385</v>
       </c>
       <c r="I235" s="5" t="inlineStr">
         <is>
@@ -14515,22 +14515,22 @@
         <v>87</v>
       </c>
       <c r="K235" s="22" t="n">
-        <v>86.518</v>
+        <v>86.48399999999999</v>
       </c>
       <c r="L235" s="22" t="n">
-        <v>0.482</v>
+        <v>0.516</v>
       </c>
       <c r="M235" s="5" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N235" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="O235" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O235" s="25" t="inlineStr">
+        <is>
+          <t>Khớp mốc Start</t>
         </is>
       </c>
     </row>
@@ -14556,36 +14556,36 @@
         <v>87</v>
       </c>
       <c r="G236" s="24" t="n">
-        <v>86.518</v>
+        <v>86.48399999999999</v>
       </c>
       <c r="H236" s="24" t="n">
-        <v>0.482</v>
+        <v>0.516</v>
       </c>
       <c r="I236" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="J236" s="24" t="n">
         <v>87</v>
       </c>
       <c r="K236" s="24" t="n">
-        <v>86.518</v>
+        <v>86.48399999999999</v>
       </c>
       <c r="L236" s="24" t="n">
-        <v>0.482</v>
+        <v>0.516</v>
       </c>
       <c r="M236" s="9" t="inlineStr">
         <is>
-          <t>ĐẠT</t>
+          <t>LỆCH</t>
         </is>
       </c>
       <c r="N236" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="O236" s="23" t="inlineStr">
-        <is>
-          <t>Khớp CẢ 2 đầu</t>
+      <c r="O236" s="26" t="inlineStr">
+        <is>
+          <t>Không khớp</t>
         </is>
       </c>
     </row>
@@ -14611,10 +14611,10 @@
         <v>88</v>
       </c>
       <c r="G237" s="22" t="n">
-        <v>88.255</v>
+        <v>88.288</v>
       </c>
       <c r="H237" s="22" t="n">
-        <v>0.255</v>
+        <v>0.288</v>
       </c>
       <c r="I237" s="5" t="inlineStr">
         <is>
@@ -14625,10 +14625,10 @@
         <v>92</v>
       </c>
       <c r="K237" s="22" t="n">
-        <v>92.129</v>
+        <v>92.16200000000001</v>
       </c>
       <c r="L237" s="22" t="n">
-        <v>0.129</v>
+        <v>0.162</v>
       </c>
       <c r="M237" s="5" t="inlineStr">
         <is>
@@ -14666,10 +14666,10 @@
         <v>92</v>
       </c>
       <c r="G238" s="24" t="n">
-        <v>92.129</v>
+        <v>92.16200000000001</v>
       </c>
       <c r="H238" s="24" t="n">
-        <v>0.129</v>
+        <v>0.162</v>
       </c>
       <c r="I238" s="9" t="inlineStr">
         <is>
@@ -14680,10 +14680,10 @@
         <v>101</v>
       </c>
       <c r="K238" s="24" t="n">
-        <v>101.282</v>
+        <v>101.316</v>
       </c>
       <c r="L238" s="24" t="n">
-        <v>0.282</v>
+        <v>0.316</v>
       </c>
       <c r="M238" s="9" t="inlineStr">
         <is>
@@ -14721,10 +14721,10 @@
         <v>101</v>
       </c>
       <c r="G239" s="22" t="n">
-        <v>101.282</v>
+        <v>101.316</v>
       </c>
       <c r="H239" s="22" t="n">
-        <v>0.282</v>
+        <v>0.316</v>
       </c>
       <c r="I239" s="5" t="inlineStr">
         <is>
@@ -14735,10 +14735,10 @@
         <v>112</v>
       </c>
       <c r="K239" s="22" t="n">
-        <v>111.571</v>
+        <v>111.537</v>
       </c>
       <c r="L239" s="22" t="n">
-        <v>0.429</v>
+        <v>0.463</v>
       </c>
       <c r="M239" s="5" t="inlineStr">
         <is>
@@ -14776,10 +14776,10 @@
         <v>112</v>
       </c>
       <c r="G240" s="24" t="n">
-        <v>111.571</v>
+        <v>111.537</v>
       </c>
       <c r="H240" s="24" t="n">
-        <v>0.429</v>
+        <v>0.463</v>
       </c>
       <c r="I240" s="9" t="inlineStr">
         <is>
@@ -14790,10 +14790,10 @@
         <v>114</v>
       </c>
       <c r="K240" s="24" t="n">
-        <v>113.909</v>
+        <v>113.876</v>
       </c>
       <c r="L240" s="24" t="n">
-        <v>0.091</v>
+        <v>0.124</v>
       </c>
       <c r="M240" s="9" t="inlineStr">
         <is>
@@ -14831,10 +14831,10 @@
         <v>114</v>
       </c>
       <c r="G241" s="22" t="n">
-        <v>113.909</v>
+        <v>113.876</v>
       </c>
       <c r="H241" s="22" t="n">
-        <v>0.091</v>
+        <v>0.124</v>
       </c>
       <c r="I241" s="5" t="inlineStr">
         <is>
@@ -14845,10 +14845,10 @@
         <v>117</v>
       </c>
       <c r="K241" s="22" t="n">
-        <v>116.715</v>
+        <v>116.681</v>
       </c>
       <c r="L241" s="22" t="n">
-        <v>0.285</v>
+        <v>0.319</v>
       </c>
       <c r="M241" s="5" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         <v>117</v>
       </c>
       <c r="G242" s="24" t="n">
-        <v>116.715</v>
+        <v>116.681</v>
       </c>
       <c r="H242" s="24" t="n">
-        <v>0.285</v>
+        <v>0.319</v>
       </c>
       <c r="I242" s="9" t="inlineStr">
         <is>
@@ -14945,10 +14945,10 @@
         <v>1</v>
       </c>
       <c r="G243" s="22" t="n">
-        <v>1.018</v>
+        <v>1.052</v>
       </c>
       <c r="H243" s="22" t="n">
-        <v>0.018</v>
+        <v>0.052</v>
       </c>
       <c r="I243" s="5" t="inlineStr">
         <is>
@@ -14959,10 +14959,10 @@
         <v>4</v>
       </c>
       <c r="K243" s="22" t="n">
-        <v>4.207</v>
+        <v>4.241</v>
       </c>
       <c r="L243" s="22" t="n">
-        <v>0.207</v>
+        <v>0.241</v>
       </c>
       <c r="M243" s="5" t="inlineStr">
         <is>
@@ -15004,10 +15004,10 @@
         <v>4</v>
       </c>
       <c r="G244" s="24" t="n">
-        <v>4.207</v>
+        <v>4.241</v>
       </c>
       <c r="H244" s="24" t="n">
-        <v>0.207</v>
+        <v>0.241</v>
       </c>
       <c r="I244" s="9" t="inlineStr">
         <is>
@@ -15018,10 +15018,10 @@
         <v>7</v>
       </c>
       <c r="K244" s="24" t="n">
-        <v>6.786</v>
+        <v>6.752</v>
       </c>
       <c r="L244" s="24" t="n">
-        <v>0.214</v>
+        <v>0.248</v>
       </c>
       <c r="M244" s="9" t="inlineStr">
         <is>
@@ -15063,10 +15063,10 @@
         <v>7</v>
       </c>
       <c r="G245" s="22" t="n">
-        <v>6.786</v>
+        <v>6.752</v>
       </c>
       <c r="H245" s="22" t="n">
-        <v>0.214</v>
+        <v>0.248</v>
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
@@ -15077,10 +15077,10 @@
         <v>9</v>
       </c>
       <c r="K245" s="22" t="n">
-        <v>8.888999999999999</v>
+        <v>8.855</v>
       </c>
       <c r="L245" s="22" t="n">
-        <v>0.111</v>
+        <v>0.145</v>
       </c>
       <c r="M245" s="5" t="inlineStr">
         <is>
@@ -15122,10 +15122,10 @@
         <v>9</v>
       </c>
       <c r="G246" s="24" t="n">
-        <v>8.888999999999999</v>
+        <v>8.855</v>
       </c>
       <c r="H246" s="24" t="n">
-        <v>0.111</v>
+        <v>0.145</v>
       </c>
       <c r="I246" s="9" t="inlineStr">
         <is>
@@ -15136,10 +15136,10 @@
         <v>14</v>
       </c>
       <c r="K246" s="24" t="n">
-        <v>14.114</v>
+        <v>14.148</v>
       </c>
       <c r="L246" s="24" t="n">
-        <v>0.114</v>
+        <v>0.148</v>
       </c>
       <c r="M246" s="9" t="inlineStr">
         <is>
@@ -15181,10 +15181,10 @@
         <v>14</v>
       </c>
       <c r="G247" s="22" t="n">
-        <v>14.114</v>
+        <v>14.148</v>
       </c>
       <c r="H247" s="22" t="n">
-        <v>0.114</v>
+        <v>0.148</v>
       </c>
       <c r="I247" s="5" t="inlineStr">
         <is>
@@ -15195,10 +15195,10 @@
         <v>17</v>
       </c>
       <c r="K247" s="22" t="n">
-        <v>17.235</v>
+        <v>17.269</v>
       </c>
       <c r="L247" s="22" t="n">
-        <v>0.235</v>
+        <v>0.269</v>
       </c>
       <c r="M247" s="5" t="inlineStr">
         <is>
@@ -15240,10 +15240,10 @@
         <v>17</v>
       </c>
       <c r="G248" s="24" t="n">
-        <v>17.235</v>
+        <v>17.269</v>
       </c>
       <c r="H248" s="24" t="n">
-        <v>0.235</v>
+        <v>0.269</v>
       </c>
       <c r="I248" s="9" t="inlineStr">
         <is>
@@ -15254,10 +15254,10 @@
         <v>18</v>
       </c>
       <c r="K248" s="24" t="n">
-        <v>18.457</v>
+        <v>18.491</v>
       </c>
       <c r="L248" s="24" t="n">
-        <v>0.457</v>
+        <v>0.491</v>
       </c>
       <c r="M248" s="9" t="inlineStr">
         <is>
@@ -15299,10 +15299,10 @@
         <v>18</v>
       </c>
       <c r="G249" s="22" t="n">
-        <v>18.457</v>
+        <v>18.491</v>
       </c>
       <c r="H249" s="22" t="n">
-        <v>0.457</v>
+        <v>0.491</v>
       </c>
       <c r="I249" s="5" t="inlineStr">
         <is>
@@ -15313,10 +15313,10 @@
         <v>23</v>
       </c>
       <c r="K249" s="22" t="n">
-        <v>23.343</v>
+        <v>23.377</v>
       </c>
       <c r="L249" s="22" t="n">
-        <v>0.343</v>
+        <v>0.377</v>
       </c>
       <c r="M249" s="5" t="inlineStr">
         <is>
@@ -15358,10 +15358,10 @@
         <v>23</v>
       </c>
       <c r="G250" s="24" t="n">
-        <v>23.343</v>
+        <v>23.377</v>
       </c>
       <c r="H250" s="24" t="n">
-        <v>0.343</v>
+        <v>0.377</v>
       </c>
       <c r="I250" s="9" t="inlineStr">
         <is>
@@ -15372,10 +15372,10 @@
         <v>27</v>
       </c>
       <c r="K250" s="24" t="n">
-        <v>27.007</v>
+        <v>26.973</v>
       </c>
       <c r="L250" s="24" t="n">
-        <v>0.007</v>
+        <v>0.027</v>
       </c>
       <c r="M250" s="9" t="inlineStr">
         <is>
@@ -15417,10 +15417,10 @@
         <v>27</v>
       </c>
       <c r="G251" s="22" t="n">
-        <v>27.007</v>
+        <v>26.973</v>
       </c>
       <c r="H251" s="22" t="n">
-        <v>0.007</v>
+        <v>0.027</v>
       </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
@@ -15431,10 +15431,10 @@
         <v>30</v>
       </c>
       <c r="K251" s="22" t="n">
-        <v>29.585</v>
+        <v>29.551</v>
       </c>
       <c r="L251" s="22" t="n">
-        <v>0.415</v>
+        <v>0.449</v>
       </c>
       <c r="M251" s="5" t="inlineStr">
         <is>
@@ -15476,10 +15476,10 @@
         <v>30</v>
       </c>
       <c r="G252" s="24" t="n">
-        <v>29.585</v>
+        <v>29.551</v>
       </c>
       <c r="H252" s="24" t="n">
-        <v>0.415</v>
+        <v>0.449</v>
       </c>
       <c r="I252" s="9" t="inlineStr">
         <is>
@@ -15490,10 +15490,10 @@
         <v>34</v>
       </c>
       <c r="K252" s="24" t="n">
-        <v>33.589</v>
+        <v>33.555</v>
       </c>
       <c r="L252" s="24" t="n">
-        <v>0.411</v>
+        <v>0.445</v>
       </c>
       <c r="M252" s="9" t="inlineStr">
         <is>
@@ -15535,10 +15535,10 @@
         <v>34</v>
       </c>
       <c r="G253" s="22" t="n">
-        <v>33.589</v>
+        <v>33.555</v>
       </c>
       <c r="H253" s="22" t="n">
-        <v>0.411</v>
+        <v>0.445</v>
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
@@ -15549,10 +15549,10 @@
         <v>36</v>
       </c>
       <c r="K253" s="22" t="n">
-        <v>36.303</v>
+        <v>36.337</v>
       </c>
       <c r="L253" s="22" t="n">
-        <v>0.303</v>
+        <v>0.337</v>
       </c>
       <c r="M253" s="5" t="inlineStr">
         <is>
@@ -15594,10 +15594,10 @@
         <v>36</v>
       </c>
       <c r="G254" s="24" t="n">
-        <v>36.303</v>
+        <v>36.337</v>
       </c>
       <c r="H254" s="24" t="n">
-        <v>0.303</v>
+        <v>0.337</v>
       </c>
       <c r="I254" s="9" t="inlineStr">
         <is>
@@ -15608,10 +15608,10 @@
         <v>39</v>
       </c>
       <c r="K254" s="24" t="n">
-        <v>38.882</v>
+        <v>38.848</v>
       </c>
       <c r="L254" s="24" t="n">
-        <v>0.118</v>
+        <v>0.152</v>
       </c>
       <c r="M254" s="9" t="inlineStr">
         <is>
@@ -15653,10 +15653,10 @@
         <v>40</v>
       </c>
       <c r="G255" s="22" t="n">
-        <v>40.307</v>
+        <v>40.341</v>
       </c>
       <c r="H255" s="22" t="n">
-        <v>0.307</v>
+        <v>0.341</v>
       </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
@@ -15667,10 +15667,10 @@
         <v>42</v>
       </c>
       <c r="K255" s="22" t="n">
-        <v>41.935</v>
+        <v>41.901</v>
       </c>
       <c r="L255" s="22" t="n">
-        <v>0.065</v>
+        <v>0.099</v>
       </c>
       <c r="M255" s="5" t="inlineStr">
         <is>
@@ -15712,10 +15712,10 @@
         <v>42</v>
       </c>
       <c r="G256" s="24" t="n">
-        <v>41.935</v>
+        <v>41.901</v>
       </c>
       <c r="H256" s="24" t="n">
-        <v>0.065</v>
+        <v>0.099</v>
       </c>
       <c r="I256" s="9" t="inlineStr">
         <is>
@@ -15726,10 +15726,10 @@
         <v>46</v>
       </c>
       <c r="K256" s="24" t="n">
-        <v>46.21</v>
+        <v>46.244</v>
       </c>
       <c r="L256" s="24" t="n">
-        <v>0.21</v>
+        <v>0.244</v>
       </c>
       <c r="M256" s="9" t="inlineStr">
         <is>
@@ -15771,10 +15771,10 @@
         <v>45</v>
       </c>
       <c r="G257" s="22" t="n">
-        <v>44.989</v>
+        <v>44.955</v>
       </c>
       <c r="H257" s="22" t="n">
-        <v>0.011</v>
+        <v>0.045</v>
       </c>
       <c r="I257" s="5" t="inlineStr">
         <is>
@@ -15785,10 +15785,10 @@
         <v>47</v>
       </c>
       <c r="K257" s="22" t="n">
-        <v>47.024</v>
+        <v>46.99</v>
       </c>
       <c r="L257" s="22" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="M257" s="5" t="inlineStr">
         <is>
@@ -15830,10 +15830,10 @@
         <v>47</v>
       </c>
       <c r="G258" s="24" t="n">
-        <v>47.024</v>
+        <v>46.99</v>
       </c>
       <c r="H258" s="24" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="I258" s="9" t="inlineStr">
         <is>
@@ -15844,10 +15844,10 @@
         <v>49</v>
       </c>
       <c r="K258" s="24" t="n">
-        <v>49.196</v>
+        <v>49.23</v>
       </c>
       <c r="L258" s="24" t="n">
-        <v>0.196</v>
+        <v>0.23</v>
       </c>
       <c r="M258" s="9" t="inlineStr">
         <is>
@@ -15889,10 +15889,10 @@
         <v>49</v>
       </c>
       <c r="G259" s="22" t="n">
-        <v>49.196</v>
+        <v>49.23</v>
       </c>
       <c r="H259" s="22" t="n">
-        <v>0.196</v>
+        <v>0.23</v>
       </c>
       <c r="I259" s="5" t="inlineStr">
         <is>
@@ -15903,10 +15903,10 @@
         <v>52</v>
       </c>
       <c r="K259" s="22" t="n">
-        <v>51.978</v>
+        <v>52.012</v>
       </c>
       <c r="L259" s="22" t="n">
-        <v>0.022</v>
+        <v>0.012</v>
       </c>
       <c r="M259" s="5" t="inlineStr">
         <is>
@@ -15948,10 +15948,10 @@
         <v>52</v>
       </c>
       <c r="G260" s="24" t="n">
-        <v>51.978</v>
+        <v>52.012</v>
       </c>
       <c r="H260" s="24" t="n">
-        <v>0.022</v>
+        <v>0.012</v>
       </c>
       <c r="I260" s="9" t="inlineStr">
         <is>
@@ -15962,10 +15962,10 @@
         <v>54</v>
       </c>
       <c r="K260" s="24" t="n">
-        <v>54.353</v>
+        <v>54.387</v>
       </c>
       <c r="L260" s="24" t="n">
-        <v>0.353</v>
+        <v>0.387</v>
       </c>
       <c r="M260" s="9" t="inlineStr">
         <is>
@@ -16007,10 +16007,10 @@
         <v>54</v>
       </c>
       <c r="G261" s="22" t="n">
-        <v>54.353</v>
+        <v>54.387</v>
       </c>
       <c r="H261" s="22" t="n">
-        <v>0.353</v>
+        <v>0.387</v>
       </c>
       <c r="I261" s="5" t="inlineStr">
         <is>
@@ -16021,10 +16021,10 @@
         <v>56</v>
       </c>
       <c r="K261" s="22" t="n">
-        <v>56.185</v>
+        <v>56.219</v>
       </c>
       <c r="L261" s="22" t="n">
-        <v>0.185</v>
+        <v>0.219</v>
       </c>
       <c r="M261" s="5" t="inlineStr">
         <is>
@@ -16066,10 +16066,10 @@
         <v>56</v>
       </c>
       <c r="G262" s="24" t="n">
-        <v>56.185</v>
+        <v>56.219</v>
       </c>
       <c r="H262" s="24" t="n">
-        <v>0.185</v>
+        <v>0.219</v>
       </c>
       <c r="I262" s="9" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>58</v>
       </c>
       <c r="K262" s="24" t="n">
-        <v>58.356</v>
+        <v>58.39</v>
       </c>
       <c r="L262" s="24" t="n">
-        <v>0.356</v>
+        <v>0.39</v>
       </c>
       <c r="M262" s="9" t="inlineStr">
         <is>
@@ -16125,10 +16125,10 @@
         <v>58</v>
       </c>
       <c r="G263" s="22" t="n">
-        <v>58.356</v>
+        <v>58.39</v>
       </c>
       <c r="H263" s="22" t="n">
-        <v>0.356</v>
+        <v>0.39</v>
       </c>
       <c r="I263" s="5" t="inlineStr">
         <is>
@@ -16139,10 +16139,10 @@
         <v>60</v>
       </c>
       <c r="K263" s="22" t="n">
-        <v>59.985</v>
+        <v>60.019</v>
       </c>
       <c r="L263" s="22" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="M263" s="5" t="inlineStr">
         <is>
@@ -16184,10 +16184,10 @@
         <v>60</v>
       </c>
       <c r="G264" s="24" t="n">
-        <v>59.985</v>
+        <v>60.019</v>
       </c>
       <c r="H264" s="24" t="n">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="I264" s="9" t="inlineStr">
         <is>
@@ -16198,10 +16198,10 @@
         <v>63</v>
       </c>
       <c r="K264" s="24" t="n">
-        <v>63.106</v>
+        <v>63.14</v>
       </c>
       <c r="L264" s="24" t="n">
-        <v>0.106</v>
+        <v>0.14</v>
       </c>
       <c r="M264" s="9" t="inlineStr">
         <is>
@@ -16243,10 +16243,10 @@
         <v>63</v>
       </c>
       <c r="G265" s="22" t="n">
-        <v>63.106</v>
+        <v>63.14</v>
       </c>
       <c r="H265" s="22" t="n">
-        <v>0.106</v>
+        <v>0.14</v>
       </c>
       <c r="I265" s="5" t="inlineStr">
         <is>
@@ -16257,10 +16257,10 @@
         <v>65</v>
       </c>
       <c r="K265" s="22" t="n">
-        <v>65.006</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="L265" s="22" t="n">
-        <v>0.006</v>
+        <v>0.04</v>
       </c>
       <c r="M265" s="5" t="inlineStr">
         <is>
@@ -16302,10 +16302,10 @@
         <v>65</v>
       </c>
       <c r="G266" s="24" t="n">
-        <v>65.006</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="H266" s="24" t="n">
-        <v>0.006</v>
+        <v>0.04</v>
       </c>
       <c r="I266" s="9" t="inlineStr">
         <is>
@@ -16316,10 +16316,10 @@
         <v>69</v>
       </c>
       <c r="K266" s="24" t="n">
-        <v>68.60299999999999</v>
+        <v>68.569</v>
       </c>
       <c r="L266" s="24" t="n">
-        <v>0.397</v>
+        <v>0.431</v>
       </c>
       <c r="M266" s="9" t="inlineStr">
         <is>
@@ -16361,10 +16361,10 @@
         <v>69</v>
       </c>
       <c r="G267" s="22" t="n">
-        <v>68.60299999999999</v>
+        <v>68.569</v>
       </c>
       <c r="H267" s="22" t="n">
-        <v>0.397</v>
+        <v>0.431</v>
       </c>
       <c r="I267" s="5" t="inlineStr">
         <is>
@@ -16375,10 +16375,10 @@
         <v>71</v>
       </c>
       <c r="K267" s="22" t="n">
-        <v>70.842</v>
+        <v>70.80800000000001</v>
       </c>
       <c r="L267" s="22" t="n">
-        <v>0.158</v>
+        <v>0.192</v>
       </c>
       <c r="M267" s="5" t="inlineStr">
         <is>
@@ -16420,10 +16420,10 @@
         <v>71</v>
       </c>
       <c r="G268" s="24" t="n">
-        <v>70.842</v>
+        <v>70.80800000000001</v>
       </c>
       <c r="H268" s="24" t="n">
-        <v>0.158</v>
+        <v>0.192</v>
       </c>
       <c r="I268" s="9" t="inlineStr">
         <is>
@@ -16434,10 +16434,10 @@
         <v>72</v>
       </c>
       <c r="K268" s="24" t="n">
-        <v>71.86</v>
+        <v>71.82599999999999</v>
       </c>
       <c r="L268" s="24" t="n">
-        <v>0.14</v>
+        <v>0.174</v>
       </c>
       <c r="M268" s="9" t="inlineStr">
         <is>
@@ -16479,10 +16479,10 @@
         <v>72</v>
       </c>
       <c r="G269" s="22" t="n">
-        <v>71.86</v>
+        <v>71.82599999999999</v>
       </c>
       <c r="H269" s="22" t="n">
-        <v>0.14</v>
+        <v>0.174</v>
       </c>
       <c r="I269" s="5" t="inlineStr">
         <is>
@@ -16493,10 +16493,10 @@
         <v>74</v>
       </c>
       <c r="K269" s="22" t="n">
-        <v>74.37</v>
+        <v>74.404</v>
       </c>
       <c r="L269" s="22" t="n">
-        <v>0.37</v>
+        <v>0.404</v>
       </c>
       <c r="M269" s="5" t="inlineStr">
         <is>
@@ -16538,10 +16538,10 @@
         <v>74</v>
       </c>
       <c r="G270" s="24" t="n">
-        <v>74.37</v>
+        <v>74.404</v>
       </c>
       <c r="H270" s="24" t="n">
-        <v>0.37</v>
+        <v>0.404</v>
       </c>
       <c r="I270" s="9" t="inlineStr">
         <is>
@@ -16552,10 +16552,10 @@
         <v>78</v>
       </c>
       <c r="K270" s="24" t="n">
-        <v>78.306</v>
+        <v>78.34</v>
       </c>
       <c r="L270" s="24" t="n">
-        <v>0.306</v>
+        <v>0.34</v>
       </c>
       <c r="M270" s="9" t="inlineStr">
         <is>
@@ -16597,10 +16597,10 @@
         <v>78</v>
       </c>
       <c r="G271" s="22" t="n">
-        <v>78.306</v>
+        <v>78.34</v>
       </c>
       <c r="H271" s="22" t="n">
-        <v>0.306</v>
+        <v>0.34</v>
       </c>
       <c r="I271" s="5" t="inlineStr">
         <is>
@@ -16611,10 +16611,10 @@
         <v>84</v>
       </c>
       <c r="K271" s="22" t="n">
-        <v>83.938</v>
+        <v>83.904</v>
       </c>
       <c r="L271" s="22" t="n">
-        <v>0.062</v>
+        <v>0.096</v>
       </c>
       <c r="M271" s="5" t="inlineStr">
         <is>
@@ -16656,10 +16656,10 @@
         <v>84</v>
       </c>
       <c r="G272" s="24" t="n">
-        <v>83.938</v>
+        <v>83.904</v>
       </c>
       <c r="H272" s="24" t="n">
-        <v>0.062</v>
+        <v>0.096</v>
       </c>
       <c r="I272" s="9" t="inlineStr">
         <is>
@@ -16670,10 +16670,10 @@
         <v>86</v>
       </c>
       <c r="K272" s="24" t="n">
-        <v>85.702</v>
+        <v>85.66800000000001</v>
       </c>
       <c r="L272" s="24" t="n">
-        <v>0.298</v>
+        <v>0.332</v>
       </c>
       <c r="M272" s="9" t="inlineStr">
         <is>
@@ -16715,10 +16715,10 @@
         <v>86</v>
       </c>
       <c r="G273" s="22" t="n">
-        <v>85.702</v>
+        <v>85.66800000000001</v>
       </c>
       <c r="H273" s="22" t="n">
-        <v>0.298</v>
+        <v>0.332</v>
       </c>
       <c r="I273" s="5" t="inlineStr">
         <is>
@@ -16729,10 +16729,10 @@
         <v>89</v>
       </c>
       <c r="K273" s="22" t="n">
-        <v>89.163</v>
+        <v>89.197</v>
       </c>
       <c r="L273" s="22" t="n">
-        <v>0.163</v>
+        <v>0.197</v>
       </c>
       <c r="M273" s="5" t="inlineStr">
         <is>
@@ -16774,10 +16774,10 @@
         <v>89</v>
       </c>
       <c r="G274" s="24" t="n">
-        <v>89.163</v>
+        <v>89.197</v>
       </c>
       <c r="H274" s="24" t="n">
-        <v>0.163</v>
+        <v>0.197</v>
       </c>
       <c r="I274" s="9" t="inlineStr">
         <is>
@@ -16788,10 +16788,10 @@
         <v>91</v>
       </c>
       <c r="K274" s="24" t="n">
-        <v>90.995</v>
+        <v>90.961</v>
       </c>
       <c r="L274" s="24" t="n">
-        <v>0.005</v>
+        <v>0.039</v>
       </c>
       <c r="M274" s="9" t="inlineStr">
         <is>
@@ -16833,10 +16833,10 @@
         <v>91</v>
       </c>
       <c r="G275" s="22" t="n">
-        <v>90.995</v>
+        <v>90.961</v>
       </c>
       <c r="H275" s="22" t="n">
-        <v>0.005</v>
+        <v>0.039</v>
       </c>
       <c r="I275" s="5" t="inlineStr">
         <is>
@@ -16847,10 +16847,10 @@
         <v>94</v>
       </c>
       <c r="K275" s="22" t="n">
-        <v>94.117</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="L275" s="22" t="n">
-        <v>0.117</v>
+        <v>0.15</v>
       </c>
       <c r="M275" s="5" t="inlineStr">
         <is>
@@ -16892,10 +16892,10 @@
         <v>94</v>
       </c>
       <c r="G276" s="24" t="n">
-        <v>94.117</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="H276" s="24" t="n">
-        <v>0.117</v>
+        <v>0.15</v>
       </c>
       <c r="I276" s="9" t="inlineStr">
         <is>
@@ -16906,10 +16906,10 @@
         <v>96</v>
       </c>
       <c r="K276" s="24" t="n">
-        <v>96.152</v>
+        <v>96.18600000000001</v>
       </c>
       <c r="L276" s="24" t="n">
-        <v>0.152</v>
+        <v>0.186</v>
       </c>
       <c r="M276" s="9" t="inlineStr">
         <is>
@@ -16951,10 +16951,10 @@
         <v>96</v>
       </c>
       <c r="G277" s="22" t="n">
-        <v>96.152</v>
+        <v>96.18600000000001</v>
       </c>
       <c r="H277" s="22" t="n">
-        <v>0.152</v>
+        <v>0.186</v>
       </c>
       <c r="I277" s="5" t="inlineStr">
         <is>
@@ -16965,10 +16965,10 @@
         <v>104</v>
       </c>
       <c r="K277" s="22" t="n">
-        <v>103.956</v>
+        <v>103.922</v>
       </c>
       <c r="L277" s="22" t="n">
-        <v>0.044</v>
+        <v>0.078</v>
       </c>
       <c r="M277" s="5" t="inlineStr">
         <is>
@@ -17010,10 +17010,10 @@
         <v>104</v>
       </c>
       <c r="G278" s="24" t="n">
-        <v>103.956</v>
+        <v>103.922</v>
       </c>
       <c r="H278" s="24" t="n">
-        <v>0.044</v>
+        <v>0.078</v>
       </c>
       <c r="I278" s="9" t="inlineStr">
         <is>
@@ -17024,10 +17024,10 @@
         <v>106</v>
       </c>
       <c r="K278" s="24" t="n">
-        <v>105.991</v>
+        <v>105.958</v>
       </c>
       <c r="L278" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="M278" s="9" t="inlineStr">
         <is>
@@ -17069,10 +17069,10 @@
         <v>106</v>
       </c>
       <c r="G279" s="22" t="n">
-        <v>105.991</v>
+        <v>105.958</v>
       </c>
       <c r="H279" s="22" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="I279" s="5" t="inlineStr">
         <is>
@@ -17083,10 +17083,10 @@
         <v>108</v>
       </c>
       <c r="K279" s="22" t="n">
-        <v>107.145</v>
+        <v>107.111</v>
       </c>
       <c r="L279" s="22" t="n">
-        <v>0.855</v>
+        <v>0.889</v>
       </c>
       <c r="M279" s="5" t="inlineStr">
         <is>
@@ -17128,10 +17128,10 @@
         <v>108</v>
       </c>
       <c r="G280" s="24" t="n">
-        <v>107.145</v>
+        <v>107.111</v>
       </c>
       <c r="H280" s="24" t="n">
-        <v>0.855</v>
+        <v>0.889</v>
       </c>
       <c r="I280" s="9" t="inlineStr">
         <is>
@@ -17142,10 +17142,10 @@
         <v>109</v>
       </c>
       <c r="K280" s="24" t="n">
-        <v>109.316</v>
+        <v>109.35</v>
       </c>
       <c r="L280" s="24" t="n">
-        <v>0.316</v>
+        <v>0.35</v>
       </c>
       <c r="M280" s="9" t="inlineStr">
         <is>
@@ -17187,10 +17187,10 @@
         <v>109</v>
       </c>
       <c r="G281" s="22" t="n">
-        <v>109.316</v>
+        <v>109.35</v>
       </c>
       <c r="H281" s="22" t="n">
-        <v>0.316</v>
+        <v>0.35</v>
       </c>
       <c r="I281" s="5" t="inlineStr">
         <is>
@@ -17201,10 +17201,10 @@
         <v>110</v>
       </c>
       <c r="K281" s="22" t="n">
-        <v>110.334</v>
+        <v>110.368</v>
       </c>
       <c r="L281" s="22" t="n">
-        <v>0.334</v>
+        <v>0.368</v>
       </c>
       <c r="M281" s="5" t="inlineStr">
         <is>
@@ -17246,10 +17246,10 @@
         <v>110</v>
       </c>
       <c r="G282" s="24" t="n">
-        <v>110.334</v>
+        <v>110.368</v>
       </c>
       <c r="H282" s="24" t="n">
-        <v>0.334</v>
+        <v>0.368</v>
       </c>
       <c r="I282" s="9" t="inlineStr">
         <is>
@@ -17260,10 +17260,10 @@
         <v>116</v>
       </c>
       <c r="K282" s="24" t="n">
-        <v>115.695</v>
+        <v>115.661</v>
       </c>
       <c r="L282" s="24" t="n">
-        <v>0.305</v>
+        <v>0.339</v>
       </c>
       <c r="M282" s="9" t="inlineStr">
         <is>
@@ -17305,10 +17305,10 @@
         <v>116</v>
       </c>
       <c r="G283" s="22" t="n">
-        <v>115.695</v>
+        <v>115.661</v>
       </c>
       <c r="H283" s="22" t="n">
-        <v>0.305</v>
+        <v>0.339</v>
       </c>
       <c r="I283" s="5" t="inlineStr">
         <is>
@@ -17319,10 +17319,10 @@
         <v>120</v>
       </c>
       <c r="K283" s="22" t="n">
-        <v>120.92</v>
+        <v>120.954</v>
       </c>
       <c r="L283" s="22" t="n">
-        <v>0.92</v>
+        <v>0.954</v>
       </c>
       <c r="M283" s="5" t="inlineStr">
         <is>
@@ -17364,10 +17364,10 @@
         <v>120</v>
       </c>
       <c r="G284" s="24" t="n">
-        <v>120.92</v>
+        <v>120.954</v>
       </c>
       <c r="H284" s="24" t="n">
-        <v>0.92</v>
+        <v>0.954</v>
       </c>
       <c r="I284" s="9" t="inlineStr">
         <is>
@@ -17378,10 +17378,10 @@
         <v>126</v>
       </c>
       <c r="K284" s="24" t="n">
-        <v>126.416</v>
+        <v>126.45</v>
       </c>
       <c r="L284" s="24" t="n">
-        <v>0.416</v>
+        <v>0.45</v>
       </c>
       <c r="M284" s="9" t="inlineStr">
         <is>
@@ -17423,10 +17423,10 @@
         <v>127</v>
       </c>
       <c r="G285" s="22" t="n">
-        <v>126.484</v>
+        <v>126.45</v>
       </c>
       <c r="H285" s="22" t="n">
-        <v>0.516</v>
+        <v>0.55</v>
       </c>
       <c r="I285" s="5" t="inlineStr">
         <is>
@@ -17437,10 +17437,10 @@
         <v>183</v>
       </c>
       <c r="K285" s="22" t="n">
-        <v>183.008</v>
+        <v>183.042</v>
       </c>
       <c r="L285" s="22" t="n">
-        <v>0.008</v>
+        <v>0.042</v>
       </c>
       <c r="M285" s="5" t="inlineStr">
         <is>
@@ -17482,10 +17482,10 @@
         <v>183</v>
       </c>
       <c r="G286" s="24" t="n">
-        <v>183.008</v>
+        <v>183.042</v>
       </c>
       <c r="H286" s="24" t="n">
-        <v>0.008</v>
+        <v>0.042</v>
       </c>
       <c r="I286" s="9" t="inlineStr">
         <is>
@@ -17496,10 +17496,10 @@
         <v>203</v>
       </c>
       <c r="K286" s="24" t="n">
-        <v>202.89</v>
+        <v>202.856</v>
       </c>
       <c r="L286" s="24" t="n">
-        <v>0.11</v>
+        <v>0.144</v>
       </c>
       <c r="M286" s="9" t="inlineStr">
         <is>
@@ -17541,10 +17541,10 @@
         <v>203</v>
       </c>
       <c r="G287" s="22" t="n">
-        <v>202.89</v>
+        <v>202.856</v>
       </c>
       <c r="H287" s="22" t="n">
-        <v>0.11</v>
+        <v>0.144</v>
       </c>
       <c r="I287" s="5" t="inlineStr">
         <is>
@@ -17555,10 +17555,10 @@
         <v>238</v>
       </c>
       <c r="K287" s="22" t="n">
-        <v>238.175</v>
+        <v>238.209</v>
       </c>
       <c r="L287" s="22" t="n">
-        <v>0.175</v>
+        <v>0.209</v>
       </c>
       <c r="M287" s="5" t="inlineStr">
         <is>
@@ -17600,10 +17600,10 @@
         <v>238</v>
       </c>
       <c r="G288" s="24" t="n">
-        <v>238.175</v>
+        <v>238.209</v>
       </c>
       <c r="H288" s="24" t="n">
-        <v>0.175</v>
+        <v>0.209</v>
       </c>
       <c r="I288" s="9" t="inlineStr">
         <is>
@@ -17614,10 +17614,10 @@
         <v>244</v>
       </c>
       <c r="K288" s="24" t="n">
-        <v>244.418</v>
+        <v>244.452</v>
       </c>
       <c r="L288" s="24" t="n">
-        <v>0.418</v>
+        <v>0.452</v>
       </c>
       <c r="M288" s="9" t="inlineStr">
         <is>
@@ -17659,10 +17659,10 @@
         <v>244</v>
       </c>
       <c r="G289" s="22" t="n">
-        <v>244.418</v>
+        <v>244.452</v>
       </c>
       <c r="H289" s="22" t="n">
-        <v>0.418</v>
+        <v>0.452</v>
       </c>
       <c r="I289" s="5" t="inlineStr">
         <is>
@@ -17673,10 +17673,10 @@
         <v>246</v>
       </c>
       <c r="K289" s="22" t="n">
-        <v>246.25</v>
+        <v>246.284</v>
       </c>
       <c r="L289" s="22" t="n">
-        <v>0.25</v>
+        <v>0.284</v>
       </c>
       <c r="M289" s="5" t="inlineStr">
         <is>
@@ -17718,10 +17718,10 @@
         <v>246</v>
       </c>
       <c r="G290" s="24" t="n">
-        <v>246.25</v>
+        <v>246.284</v>
       </c>
       <c r="H290" s="24" t="n">
-        <v>0.25</v>
+        <v>0.284</v>
       </c>
       <c r="I290" s="9" t="inlineStr">
         <is>
@@ -17732,10 +17732,10 @@
         <v>250</v>
       </c>
       <c r="K290" s="24" t="n">
-        <v>249.711</v>
+        <v>249.677</v>
       </c>
       <c r="L290" s="24" t="n">
-        <v>0.289</v>
+        <v>0.323</v>
       </c>
       <c r="M290" s="9" t="inlineStr">
         <is>
@@ -17777,10 +17777,10 @@
         <v>250</v>
       </c>
       <c r="G291" s="22" t="n">
-        <v>249.711</v>
+        <v>249.677</v>
       </c>
       <c r="H291" s="22" t="n">
-        <v>0.289</v>
+        <v>0.323</v>
       </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
@@ -17791,10 +17791,10 @@
         <v>252</v>
       </c>
       <c r="K291" s="22" t="n">
-        <v>252.154</v>
+        <v>252.188</v>
       </c>
       <c r="L291" s="22" t="n">
-        <v>0.154</v>
+        <v>0.188</v>
       </c>
       <c r="M291" s="5" t="inlineStr">
         <is>
@@ -17836,10 +17836,10 @@
         <v>252</v>
       </c>
       <c r="G292" s="24" t="n">
-        <v>252.154</v>
+        <v>252.188</v>
       </c>
       <c r="H292" s="24" t="n">
-        <v>0.154</v>
+        <v>0.188</v>
       </c>
       <c r="I292" s="9" t="inlineStr">
         <is>
@@ -17850,10 +17850,10 @@
         <v>254</v>
       </c>
       <c r="K292" s="24" t="n">
-        <v>254.054</v>
+        <v>254.088</v>
       </c>
       <c r="L292" s="24" t="n">
-        <v>0.054</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="M292" s="9" t="inlineStr">
         <is>
@@ -17895,10 +17895,10 @@
         <v>254</v>
       </c>
       <c r="G293" s="22" t="n">
-        <v>254.054</v>
+        <v>254.088</v>
       </c>
       <c r="H293" s="22" t="n">
-        <v>0.054</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
@@ -17909,10 +17909,10 @@
         <v>255</v>
       </c>
       <c r="K293" s="22" t="n">
-        <v>255.207</v>
+        <v>255.241</v>
       </c>
       <c r="L293" s="22" t="n">
-        <v>0.207</v>
+        <v>0.241</v>
       </c>
       <c r="M293" s="5" t="inlineStr">
         <is>
@@ -17954,10 +17954,10 @@
         <v>255</v>
       </c>
       <c r="G294" s="24" t="n">
-        <v>255.207</v>
+        <v>255.241</v>
       </c>
       <c r="H294" s="24" t="n">
-        <v>0.207</v>
+        <v>0.241</v>
       </c>
       <c r="I294" s="9" t="inlineStr">
         <is>
@@ -17968,10 +17968,10 @@
         <v>256</v>
       </c>
       <c r="K294" s="24" t="n">
-        <v>255.954</v>
+        <v>255.92</v>
       </c>
       <c r="L294" s="24" t="n">
-        <v>0.046</v>
+        <v>0.08</v>
       </c>
       <c r="M294" s="9" t="inlineStr">
         <is>
@@ -18013,10 +18013,10 @@
         <v>256</v>
       </c>
       <c r="G295" s="22" t="n">
-        <v>255.954</v>
+        <v>255.92</v>
       </c>
       <c r="H295" s="22" t="n">
-        <v>0.046</v>
+        <v>0.08</v>
       </c>
       <c r="I295" s="5" t="inlineStr">
         <is>
@@ -18027,10 +18027,10 @@
         <v>258</v>
       </c>
       <c r="K295" s="22" t="n">
-        <v>257.582</v>
+        <v>257.548</v>
       </c>
       <c r="L295" s="22" t="n">
-        <v>0.418</v>
+        <v>0.452</v>
       </c>
       <c r="M295" s="5" t="inlineStr">
         <is>
@@ -18072,10 +18072,10 @@
         <v>258</v>
       </c>
       <c r="G296" s="24" t="n">
-        <v>257.582</v>
+        <v>257.548</v>
       </c>
       <c r="H296" s="24" t="n">
-        <v>0.418</v>
+        <v>0.452</v>
       </c>
       <c r="I296" s="9" t="inlineStr">
         <is>
@@ -18086,10 +18086,10 @@
         <v>260</v>
       </c>
       <c r="K296" s="24" t="n">
-        <v>259.618</v>
+        <v>259.584</v>
       </c>
       <c r="L296" s="24" t="n">
-        <v>0.382</v>
+        <v>0.416</v>
       </c>
       <c r="M296" s="9" t="inlineStr">
         <is>
@@ -18131,10 +18131,10 @@
         <v>260</v>
       </c>
       <c r="G297" s="22" t="n">
-        <v>259.618</v>
+        <v>259.584</v>
       </c>
       <c r="H297" s="22" t="n">
-        <v>0.382</v>
+        <v>0.416</v>
       </c>
       <c r="I297" s="5" t="inlineStr">
         <is>
@@ -18145,10 +18145,10 @@
         <v>262</v>
       </c>
       <c r="K297" s="22" t="n">
-        <v>261.789</v>
+        <v>261.755</v>
       </c>
       <c r="L297" s="22" t="n">
-        <v>0.211</v>
+        <v>0.245</v>
       </c>
       <c r="M297" s="5" t="inlineStr">
         <is>
@@ -18190,10 +18190,10 @@
         <v>262</v>
       </c>
       <c r="G298" s="24" t="n">
-        <v>261.789</v>
+        <v>261.755</v>
       </c>
       <c r="H298" s="24" t="n">
-        <v>0.211</v>
+        <v>0.245</v>
       </c>
       <c r="I298" s="9" t="inlineStr">
         <is>
@@ -18204,10 +18204,10 @@
         <v>263</v>
       </c>
       <c r="K298" s="24" t="n">
-        <v>262.943</v>
+        <v>262.909</v>
       </c>
       <c r="L298" s="24" t="n">
-        <v>0.057</v>
+        <v>0.091</v>
       </c>
       <c r="M298" s="9" t="inlineStr">
         <is>
@@ -18249,10 +18249,10 @@
         <v>263</v>
       </c>
       <c r="G299" s="22" t="n">
-        <v>262.943</v>
+        <v>262.909</v>
       </c>
       <c r="H299" s="22" t="n">
-        <v>0.057</v>
+        <v>0.091</v>
       </c>
       <c r="I299" s="5" t="inlineStr">
         <is>
@@ -18263,10 +18263,10 @@
         <v>267</v>
       </c>
       <c r="K299" s="22" t="n">
-        <v>267.082</v>
+        <v>267.116</v>
       </c>
       <c r="L299" s="22" t="n">
-        <v>0.082</v>
+        <v>0.116</v>
       </c>
       <c r="M299" s="5" t="inlineStr">
         <is>
@@ -18308,10 +18308,10 @@
         <v>267</v>
       </c>
       <c r="G300" s="24" t="n">
-        <v>267.082</v>
+        <v>267.116</v>
       </c>
       <c r="H300" s="24" t="n">
-        <v>0.082</v>
+        <v>0.116</v>
       </c>
       <c r="I300" s="9" t="inlineStr">
         <is>
@@ -18322,10 +18322,10 @@
         <v>269</v>
       </c>
       <c r="K300" s="24" t="n">
-        <v>269.253</v>
+        <v>269.287</v>
       </c>
       <c r="L300" s="24" t="n">
-        <v>0.253</v>
+        <v>0.287</v>
       </c>
       <c r="M300" s="9" t="inlineStr">
         <is>
@@ -18367,10 +18367,10 @@
         <v>269</v>
       </c>
       <c r="G301" s="22" t="n">
-        <v>269.253</v>
+        <v>269.287</v>
       </c>
       <c r="H301" s="22" t="n">
-        <v>0.253</v>
+        <v>0.287</v>
       </c>
       <c r="I301" s="5" t="inlineStr">
         <is>
@@ -18381,10 +18381,10 @@
         <v>271</v>
       </c>
       <c r="K301" s="22" t="n">
-        <v>271.086</v>
+        <v>271.12</v>
       </c>
       <c r="L301" s="22" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="M301" s="5" t="inlineStr">
         <is>
@@ -18426,10 +18426,10 @@
         <v>271</v>
       </c>
       <c r="G302" s="24" t="n">
-        <v>271.086</v>
+        <v>271.12</v>
       </c>
       <c r="H302" s="24" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="I302" s="9" t="inlineStr">
         <is>
@@ -18440,10 +18440,10 @@
         <v>274</v>
       </c>
       <c r="K302" s="24" t="n">
-        <v>273.868</v>
+        <v>273.834</v>
       </c>
       <c r="L302" s="24" t="n">
-        <v>0.132</v>
+        <v>0.166</v>
       </c>
       <c r="M302" s="9" t="inlineStr">
         <is>
@@ -18485,10 +18485,10 @@
         <v>274</v>
       </c>
       <c r="G303" s="22" t="n">
-        <v>273.868</v>
+        <v>273.834</v>
       </c>
       <c r="H303" s="22" t="n">
-        <v>0.132</v>
+        <v>0.166</v>
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
@@ -18499,10 +18499,10 @@
         <v>277</v>
       </c>
       <c r="K303" s="22" t="n">
-        <v>276.989</v>
+        <v>276.955</v>
       </c>
       <c r="L303" s="22" t="n">
-        <v>0.011</v>
+        <v>0.045</v>
       </c>
       <c r="M303" s="5" t="inlineStr">
         <is>
@@ -18544,10 +18544,10 @@
         <v>277</v>
       </c>
       <c r="G304" s="24" t="n">
-        <v>276.989</v>
+        <v>276.955</v>
       </c>
       <c r="H304" s="24" t="n">
-        <v>0.011</v>
+        <v>0.045</v>
       </c>
       <c r="I304" s="9" t="inlineStr">
         <is>
@@ -18558,10 +18558,10 @@
         <v>279</v>
       </c>
       <c r="K304" s="24" t="n">
-        <v>278.685</v>
+        <v>278.651</v>
       </c>
       <c r="L304" s="24" t="n">
-        <v>0.315</v>
+        <v>0.349</v>
       </c>
       <c r="M304" s="9" t="inlineStr">
         <is>
@@ -18603,10 +18603,10 @@
         <v>279</v>
       </c>
       <c r="G305" s="22" t="n">
-        <v>278.685</v>
+        <v>278.651</v>
       </c>
       <c r="H305" s="22" t="n">
-        <v>0.315</v>
+        <v>0.349</v>
       </c>
       <c r="I305" s="5" t="inlineStr">
         <is>
@@ -18617,10 +18617,10 @@
         <v>283</v>
       </c>
       <c r="K305" s="22" t="n">
-        <v>283.096</v>
+        <v>283.13</v>
       </c>
       <c r="L305" s="22" t="n">
-        <v>0.096</v>
+        <v>0.13</v>
       </c>
       <c r="M305" s="5" t="inlineStr">
         <is>
@@ -18662,10 +18662,10 @@
         <v>283</v>
       </c>
       <c r="G306" s="24" t="n">
-        <v>283.096</v>
+        <v>283.13</v>
       </c>
       <c r="H306" s="24" t="n">
-        <v>0.096</v>
+        <v>0.13</v>
       </c>
       <c r="I306" s="9" t="inlineStr">
         <is>
@@ -18676,10 +18676,10 @@
         <v>289</v>
       </c>
       <c r="K306" s="24" t="n">
-        <v>289.135</v>
+        <v>289.169</v>
       </c>
       <c r="L306" s="24" t="n">
-        <v>0.135</v>
+        <v>0.169</v>
       </c>
       <c r="M306" s="9" t="inlineStr">
         <is>
@@ -18721,10 +18721,10 @@
         <v>289</v>
       </c>
       <c r="G307" s="22" t="n">
-        <v>289.135</v>
+        <v>289.169</v>
       </c>
       <c r="H307" s="22" t="n">
-        <v>0.135</v>
+        <v>0.169</v>
       </c>
       <c r="I307" s="5" t="inlineStr">
         <is>
@@ -18735,10 +18735,10 @@
         <v>290</v>
       </c>
       <c r="K307" s="22" t="n">
-        <v>290.764</v>
+        <v>290.798</v>
       </c>
       <c r="L307" s="22" t="n">
-        <v>0.764</v>
+        <v>0.798</v>
       </c>
       <c r="M307" s="5" t="inlineStr">
         <is>
@@ -18780,10 +18780,10 @@
         <v>290</v>
       </c>
       <c r="G308" s="24" t="n">
-        <v>290.764</v>
+        <v>290.798</v>
       </c>
       <c r="H308" s="24" t="n">
-        <v>0.764</v>
+        <v>0.798</v>
       </c>
       <c r="I308" s="9" t="inlineStr">
         <is>
@@ -18794,10 +18794,10 @@
         <v>293</v>
       </c>
       <c r="K308" s="24" t="n">
-        <v>292.935</v>
+        <v>292.901</v>
       </c>
       <c r="L308" s="24" t="n">
-        <v>0.065</v>
+        <v>0.099</v>
       </c>
       <c r="M308" s="9" t="inlineStr">
         <is>
@@ -18839,10 +18839,10 @@
         <v>293</v>
       </c>
       <c r="G309" s="22" t="n">
-        <v>292.935</v>
+        <v>292.901</v>
       </c>
       <c r="H309" s="22" t="n">
-        <v>0.065</v>
+        <v>0.099</v>
       </c>
       <c r="I309" s="5" t="inlineStr">
         <is>
@@ -18853,10 +18853,10 @@
         <v>295</v>
       </c>
       <c r="K309" s="22" t="n">
-        <v>294.632</v>
+        <v>294.598</v>
       </c>
       <c r="L309" s="22" t="n">
-        <v>0.368</v>
+        <v>0.402</v>
       </c>
       <c r="M309" s="5" t="inlineStr">
         <is>
@@ -18898,10 +18898,10 @@
         <v>295</v>
       </c>
       <c r="G310" s="24" t="n">
-        <v>294.632</v>
+        <v>294.598</v>
       </c>
       <c r="H310" s="24" t="n">
-        <v>0.368</v>
+        <v>0.402</v>
       </c>
       <c r="I310" s="9" t="inlineStr">
         <is>
@@ -18912,10 +18912,10 @@
         <v>301</v>
       </c>
       <c r="K310" s="24" t="n">
-        <v>301.214</v>
+        <v>301.248</v>
       </c>
       <c r="L310" s="24" t="n">
-        <v>0.214</v>
+        <v>0.248</v>
       </c>
       <c r="M310" s="9" t="inlineStr">
         <is>
@@ -18957,10 +18957,10 @@
         <v>301</v>
       </c>
       <c r="G311" s="22" t="n">
-        <v>301.214</v>
+        <v>301.248</v>
       </c>
       <c r="H311" s="22" t="n">
-        <v>0.214</v>
+        <v>0.248</v>
       </c>
       <c r="I311" s="5" t="inlineStr">
         <is>
@@ -18971,10 +18971,10 @@
         <v>304</v>
       </c>
       <c r="K311" s="22" t="n">
-        <v>303.86</v>
+        <v>303.826</v>
       </c>
       <c r="L311" s="22" t="n">
-        <v>0.14</v>
+        <v>0.174</v>
       </c>
       <c r="M311" s="5" t="inlineStr">
         <is>
@@ -19016,10 +19016,10 @@
         <v>304</v>
       </c>
       <c r="G312" s="24" t="n">
-        <v>303.86</v>
+        <v>303.826</v>
       </c>
       <c r="H312" s="24" t="n">
-        <v>0.14</v>
+        <v>0.174</v>
       </c>
       <c r="I312" s="9" t="inlineStr">
         <is>
@@ -19030,10 +19030,10 @@
         <v>308</v>
       </c>
       <c r="K312" s="24" t="n">
-        <v>308.271</v>
+        <v>308.305</v>
       </c>
       <c r="L312" s="24" t="n">
-        <v>0.271</v>
+        <v>0.305</v>
       </c>
       <c r="M312" s="9" t="inlineStr">
         <is>
@@ -19075,10 +19075,10 @@
         <v>308</v>
       </c>
       <c r="G313" s="22" t="n">
-        <v>308.271</v>
+        <v>308.305</v>
       </c>
       <c r="H313" s="22" t="n">
-        <v>0.271</v>
+        <v>0.305</v>
       </c>
       <c r="I313" s="5" t="inlineStr">
         <is>
@@ -19089,10 +19089,10 @@
         <v>311</v>
       </c>
       <c r="K313" s="22" t="n">
-        <v>310.917</v>
+        <v>310.883</v>
       </c>
       <c r="L313" s="22" t="n">
-        <v>0.083</v>
+        <v>0.117</v>
       </c>
       <c r="M313" s="5" t="inlineStr">
         <is>
@@ -19134,10 +19134,10 @@
         <v>311</v>
       </c>
       <c r="G314" s="24" t="n">
-        <v>310.917</v>
+        <v>310.883</v>
       </c>
       <c r="H314" s="24" t="n">
-        <v>0.083</v>
+        <v>0.117</v>
       </c>
       <c r="I314" s="9" t="inlineStr">
         <is>
@@ -19148,10 +19148,10 @@
         <v>312</v>
       </c>
       <c r="K314" s="24" t="n">
-        <v>312.274</v>
+        <v>312.308</v>
       </c>
       <c r="L314" s="24" t="n">
-        <v>0.274</v>
+        <v>0.308</v>
       </c>
       <c r="M314" s="9" t="inlineStr">
         <is>
@@ -19193,10 +19193,10 @@
         <v>312</v>
       </c>
       <c r="G315" s="22" t="n">
-        <v>312.274</v>
+        <v>312.308</v>
       </c>
       <c r="H315" s="22" t="n">
-        <v>0.274</v>
+        <v>0.308</v>
       </c>
       <c r="I315" s="5" t="inlineStr">
         <is>
@@ -19207,10 +19207,10 @@
         <v>314</v>
       </c>
       <c r="K315" s="22" t="n">
-        <v>313.767</v>
+        <v>313.733</v>
       </c>
       <c r="L315" s="22" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="M315" s="5" t="inlineStr">
         <is>
@@ -19252,10 +19252,10 @@
         <v>314</v>
       </c>
       <c r="G316" s="24" t="n">
-        <v>313.767</v>
+        <v>313.733</v>
       </c>
       <c r="H316" s="24" t="n">
-        <v>0.233</v>
+        <v>0.267</v>
       </c>
       <c r="I316" s="9" t="inlineStr">
         <is>
@@ -19266,10 +19266,10 @@
         <v>317</v>
       </c>
       <c r="K316" s="24" t="n">
-        <v>317.024</v>
+        <v>316.99</v>
       </c>
       <c r="L316" s="24" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="M316" s="9" t="inlineStr">
         <is>
@@ -19311,10 +19311,10 @@
         <v>317</v>
       </c>
       <c r="G317" s="22" t="n">
-        <v>317.024</v>
+        <v>316.99</v>
       </c>
       <c r="H317" s="22" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="I317" s="5" t="inlineStr">
         <is>
@@ -19325,10 +19325,10 @@
         <v>319</v>
       </c>
       <c r="K317" s="22" t="n">
-        <v>319.196</v>
+        <v>319.23</v>
       </c>
       <c r="L317" s="22" t="n">
-        <v>0.196</v>
+        <v>0.23</v>
       </c>
       <c r="M317" s="5" t="inlineStr">
         <is>
@@ -19370,10 +19370,10 @@
         <v>319</v>
       </c>
       <c r="G318" s="24" t="n">
-        <v>319.196</v>
+        <v>319.23</v>
       </c>
       <c r="H318" s="24" t="n">
-        <v>0.196</v>
+        <v>0.23</v>
       </c>
       <c r="I318" s="9" t="inlineStr">
         <is>
@@ -19384,10 +19384,10 @@
         <v>321</v>
       </c>
       <c r="K318" s="24" t="n">
-        <v>321.231</v>
+        <v>321.265</v>
       </c>
       <c r="L318" s="24" t="n">
-        <v>0.231</v>
+        <v>0.265</v>
       </c>
       <c r="M318" s="9" t="inlineStr">
         <is>
@@ -19429,10 +19429,10 @@
         <v>321</v>
       </c>
       <c r="G319" s="22" t="n">
-        <v>321.231</v>
+        <v>321.265</v>
       </c>
       <c r="H319" s="22" t="n">
-        <v>0.231</v>
+        <v>0.265</v>
       </c>
       <c r="I319" s="5" t="inlineStr">
         <is>
@@ -19443,10 +19443,10 @@
         <v>323</v>
       </c>
       <c r="K319" s="22" t="n">
-        <v>323.267</v>
+        <v>323.301</v>
       </c>
       <c r="L319" s="22" t="n">
-        <v>0.267</v>
+        <v>0.301</v>
       </c>
       <c r="M319" s="5" t="inlineStr">
         <is>
@@ -19488,10 +19488,10 @@
         <v>323</v>
       </c>
       <c r="G320" s="24" t="n">
-        <v>323.267</v>
+        <v>323.301</v>
       </c>
       <c r="H320" s="24" t="n">
-        <v>0.267</v>
+        <v>0.301</v>
       </c>
       <c r="I320" s="9" t="inlineStr">
         <is>
@@ -19502,10 +19502,10 @@
         <v>325</v>
       </c>
       <c r="K320" s="24" t="n">
-        <v>325.235</v>
+        <v>325.269</v>
       </c>
       <c r="L320" s="24" t="n">
-        <v>0.235</v>
+        <v>0.269</v>
       </c>
       <c r="M320" s="9" t="inlineStr">
         <is>
@@ -19547,10 +19547,10 @@
         <v>325</v>
       </c>
       <c r="G321" s="22" t="n">
-        <v>325.235</v>
+        <v>325.269</v>
       </c>
       <c r="H321" s="22" t="n">
-        <v>0.235</v>
+        <v>0.269</v>
       </c>
       <c r="I321" s="5" t="inlineStr">
         <is>
@@ -19561,10 +19561,10 @@
         <v>327</v>
       </c>
       <c r="K321" s="22" t="n">
-        <v>327.678</v>
+        <v>327.712</v>
       </c>
       <c r="L321" s="22" t="n">
-        <v>0.678</v>
+        <v>0.712</v>
       </c>
       <c r="M321" s="5" t="inlineStr">
         <is>
@@ -19606,10 +19606,10 @@
         <v>327</v>
       </c>
       <c r="G322" s="24" t="n">
-        <v>327.678</v>
+        <v>327.712</v>
       </c>
       <c r="H322" s="24" t="n">
-        <v>0.678</v>
+        <v>0.712</v>
       </c>
       <c r="I322" s="9" t="inlineStr">
         <is>
@@ -19620,10 +19620,10 @@
         <v>333</v>
       </c>
       <c r="K322" s="24" t="n">
-        <v>332.903</v>
+        <v>332.869</v>
       </c>
       <c r="L322" s="24" t="n">
-        <v>0.097</v>
+        <v>0.131</v>
       </c>
       <c r="M322" s="9" t="inlineStr">
         <is>
@@ -19665,10 +19665,10 @@
         <v>333</v>
       </c>
       <c r="G323" s="22" t="n">
-        <v>332.903</v>
+        <v>332.869</v>
       </c>
       <c r="H323" s="22" t="n">
-        <v>0.097</v>
+        <v>0.131</v>
       </c>
       <c r="I323" s="5" t="inlineStr">
         <is>
@@ -19679,10 +19679,10 @@
         <v>337</v>
       </c>
       <c r="K323" s="22" t="n">
-        <v>337.178</v>
+        <v>337.212</v>
       </c>
       <c r="L323" s="22" t="n">
-        <v>0.178</v>
+        <v>0.212</v>
       </c>
       <c r="M323" s="5" t="inlineStr">
         <is>
@@ -19724,10 +19724,10 @@
         <v>337</v>
       </c>
       <c r="G324" s="24" t="n">
-        <v>337.178</v>
+        <v>337.212</v>
       </c>
       <c r="H324" s="24" t="n">
-        <v>0.178</v>
+        <v>0.212</v>
       </c>
       <c r="I324" s="9" t="inlineStr">
         <is>
@@ -19738,10 +19738,10 @@
         <v>339</v>
       </c>
       <c r="K324" s="24" t="n">
-        <v>339.01</v>
+        <v>339.043</v>
       </c>
       <c r="L324" s="24" t="n">
-        <v>0.01</v>
+        <v>0.043</v>
       </c>
       <c r="M324" s="9" t="inlineStr">
         <is>
@@ -19783,10 +19783,10 @@
         <v>339</v>
       </c>
       <c r="G325" s="22" t="n">
-        <v>339.01</v>
+        <v>339.043</v>
       </c>
       <c r="H325" s="22" t="n">
-        <v>0.01</v>
+        <v>0.043</v>
       </c>
       <c r="I325" s="5" t="inlineStr">
         <is>
@@ -19797,10 +19797,10 @@
         <v>344</v>
       </c>
       <c r="K325" s="22" t="n">
-        <v>344.167</v>
+        <v>344.201</v>
       </c>
       <c r="L325" s="22" t="n">
-        <v>0.167</v>
+        <v>0.201</v>
       </c>
       <c r="M325" s="5" t="inlineStr">
         <is>
@@ -19842,10 +19842,10 @@
         <v>344</v>
       </c>
       <c r="G326" s="24" t="n">
-        <v>344.167</v>
+        <v>344.201</v>
       </c>
       <c r="H326" s="24" t="n">
-        <v>0.167</v>
+        <v>0.201</v>
       </c>
       <c r="I326" s="9" t="inlineStr">
         <is>
@@ -19856,10 +19856,10 @@
         <v>347</v>
       </c>
       <c r="K326" s="24" t="n">
-        <v>347.56</v>
+        <v>347.594</v>
       </c>
       <c r="L326" s="24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.594</v>
       </c>
       <c r="M326" s="9" t="inlineStr">
         <is>
@@ -19901,10 +19901,10 @@
         <v>347</v>
       </c>
       <c r="G327" s="22" t="n">
-        <v>347.56</v>
+        <v>347.594</v>
       </c>
       <c r="H327" s="22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.594</v>
       </c>
       <c r="I327" s="5" t="inlineStr">
         <is>
@@ -19915,10 +19915,10 @@
         <v>353</v>
       </c>
       <c r="K327" s="22" t="n">
-        <v>353.259</v>
+        <v>353.293</v>
       </c>
       <c r="L327" s="22" t="n">
-        <v>0.259</v>
+        <v>0.293</v>
       </c>
       <c r="M327" s="5" t="inlineStr">
         <is>
@@ -19960,10 +19960,10 @@
         <v>353</v>
       </c>
       <c r="G328" s="24" t="n">
-        <v>353.259</v>
+        <v>353.293</v>
       </c>
       <c r="H328" s="24" t="n">
-        <v>0.259</v>
+        <v>0.293</v>
       </c>
       <c r="I328" s="9" t="inlineStr">
         <is>
@@ -19974,10 +19974,10 @@
         <v>355</v>
       </c>
       <c r="K328" s="24" t="n">
-        <v>355.024</v>
+        <v>355.058</v>
       </c>
       <c r="L328" s="24" t="n">
-        <v>0.024</v>
+        <v>0.058</v>
       </c>
       <c r="M328" s="9" t="inlineStr">
         <is>
@@ -20019,10 +20019,10 @@
         <v>355</v>
       </c>
       <c r="G329" s="22" t="n">
-        <v>355.024</v>
+        <v>355.058</v>
       </c>
       <c r="H329" s="22" t="n">
-        <v>0.024</v>
+        <v>0.058</v>
       </c>
       <c r="I329" s="5" t="inlineStr">
         <is>
@@ -20033,10 +20033,10 @@
         <v>360</v>
       </c>
       <c r="K329" s="22" t="n">
-        <v>360.045</v>
+        <v>360.079</v>
       </c>
       <c r="L329" s="22" t="n">
-        <v>0.045</v>
+        <v>0.079</v>
       </c>
       <c r="M329" s="5" t="inlineStr">
         <is>
@@ -20078,10 +20078,10 @@
         <v>360</v>
       </c>
       <c r="G330" s="24" t="n">
-        <v>360.045</v>
+        <v>360.079</v>
       </c>
       <c r="H330" s="24" t="n">
-        <v>0.045</v>
+        <v>0.079</v>
       </c>
       <c r="I330" s="9" t="inlineStr">
         <is>
@@ -20092,10 +20092,10 @@
         <v>363</v>
       </c>
       <c r="K330" s="24" t="n">
-        <v>363.031</v>
+        <v>362.997</v>
       </c>
       <c r="L330" s="24" t="n">
-        <v>0.031</v>
+        <v>0.003</v>
       </c>
       <c r="M330" s="9" t="inlineStr">
         <is>
@@ -20137,10 +20137,10 @@
         <v>363</v>
       </c>
       <c r="G331" s="22" t="n">
-        <v>363.031</v>
+        <v>362.997</v>
       </c>
       <c r="H331" s="22" t="n">
-        <v>0.031</v>
+        <v>0.003</v>
       </c>
       <c r="I331" s="5" t="inlineStr">
         <is>
@@ -20151,10 +20151,10 @@
         <v>365</v>
       </c>
       <c r="K331" s="22" t="n">
-        <v>364.727</v>
+        <v>364.693</v>
       </c>
       <c r="L331" s="22" t="n">
-        <v>0.273</v>
+        <v>0.307</v>
       </c>
       <c r="M331" s="5" t="inlineStr">
         <is>
@@ -20196,10 +20196,10 @@
         <v>365</v>
       </c>
       <c r="G332" s="24" t="n">
-        <v>364.727</v>
+        <v>364.693</v>
       </c>
       <c r="H332" s="24" t="n">
-        <v>0.273</v>
+        <v>0.307</v>
       </c>
       <c r="I332" s="9" t="inlineStr">
         <is>
@@ -20210,10 +20210,10 @@
         <v>367</v>
       </c>
       <c r="K332" s="24" t="n">
-        <v>367.645</v>
+        <v>367.679</v>
       </c>
       <c r="L332" s="24" t="n">
-        <v>0.645</v>
+        <v>0.679</v>
       </c>
       <c r="M332" s="9" t="inlineStr">
         <is>
@@ -20255,10 +20255,10 @@
         <v>367</v>
       </c>
       <c r="G333" s="22" t="n">
-        <v>367.645</v>
+        <v>367.679</v>
       </c>
       <c r="H333" s="22" t="n">
-        <v>0.645</v>
+        <v>0.679</v>
       </c>
       <c r="I333" s="5" t="inlineStr">
         <is>
@@ -20269,10 +20269,10 @@
         <v>368</v>
       </c>
       <c r="K333" s="22" t="n">
-        <v>367.713</v>
+        <v>367.679</v>
       </c>
       <c r="L333" s="22" t="n">
-        <v>0.287</v>
+        <v>0.321</v>
       </c>
       <c r="M333" s="5" t="inlineStr">
         <is>
@@ -20314,10 +20314,10 @@
         <v>368</v>
       </c>
       <c r="G334" s="24" t="n">
-        <v>367.713</v>
+        <v>367.679</v>
       </c>
       <c r="H334" s="24" t="n">
-        <v>0.287</v>
+        <v>0.321</v>
       </c>
       <c r="I334" s="9" t="inlineStr">
         <is>
@@ -20328,10 +20328,10 @@
         <v>371</v>
       </c>
       <c r="K334" s="24" t="n">
-        <v>370.563</v>
+        <v>370.529</v>
       </c>
       <c r="L334" s="24" t="n">
-        <v>0.437</v>
+        <v>0.471</v>
       </c>
       <c r="M334" s="9" t="inlineStr">
         <is>
@@ -20373,10 +20373,10 @@
         <v>371</v>
       </c>
       <c r="G335" s="22" t="n">
-        <v>370.563</v>
+        <v>370.529</v>
       </c>
       <c r="H335" s="22" t="n">
-        <v>0.437</v>
+        <v>0.471</v>
       </c>
       <c r="I335" s="5" t="inlineStr">
         <is>
@@ -20387,10 +20387,10 @@
         <v>387</v>
       </c>
       <c r="K335" s="22" t="n">
-        <v>387.052</v>
+        <v>387.086</v>
       </c>
       <c r="L335" s="22" t="n">
-        <v>0.052</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="M335" s="5" t="inlineStr">
         <is>
@@ -20432,10 +20432,10 @@
         <v>387</v>
       </c>
       <c r="G336" s="24" t="n">
-        <v>387.052</v>
+        <v>387.086</v>
       </c>
       <c r="H336" s="24" t="n">
-        <v>0.052</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I336" s="9" t="inlineStr">
         <is>
@@ -20446,10 +20446,10 @@
         <v>398</v>
       </c>
       <c r="K336" s="24" t="n">
-        <v>398.316</v>
+        <v>398.35</v>
       </c>
       <c r="L336" s="24" t="n">
-        <v>0.316</v>
+        <v>0.35</v>
       </c>
       <c r="M336" s="9" t="inlineStr">
         <is>
@@ -20491,10 +20491,10 @@
         <v>398</v>
       </c>
       <c r="G337" s="22" t="n">
-        <v>398.316</v>
+        <v>398.35</v>
       </c>
       <c r="H337" s="22" t="n">
-        <v>0.316</v>
+        <v>0.35</v>
       </c>
       <c r="I337" s="5" t="inlineStr">
         <is>
@@ -20505,10 +20505,10 @@
         <v>400</v>
       </c>
       <c r="K337" s="22" t="n">
-        <v>399.877</v>
+        <v>399.843</v>
       </c>
       <c r="L337" s="22" t="n">
-        <v>0.123</v>
+        <v>0.157</v>
       </c>
       <c r="M337" s="5" t="inlineStr">
         <is>
@@ -20550,10 +20550,10 @@
         <v>400</v>
       </c>
       <c r="G338" s="24" t="n">
-        <v>399.877</v>
+        <v>399.843</v>
       </c>
       <c r="H338" s="24" t="n">
-        <v>0.123</v>
+        <v>0.157</v>
       </c>
       <c r="I338" s="9" t="inlineStr">
         <is>
@@ -20564,10 +20564,10 @@
         <v>403</v>
       </c>
       <c r="K338" s="24" t="n">
-        <v>402.93</v>
+        <v>402.896</v>
       </c>
       <c r="L338" s="24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="M338" s="9" t="inlineStr">
         <is>
@@ -20609,10 +20609,10 @@
         <v>403</v>
       </c>
       <c r="G339" s="22" t="n">
-        <v>402.93</v>
+        <v>402.896</v>
       </c>
       <c r="H339" s="22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="I339" s="5" t="inlineStr">
         <is>
@@ -20623,10 +20623,10 @@
         <v>407</v>
       </c>
       <c r="K339" s="22" t="n">
-        <v>406.594</v>
+        <v>406.56</v>
       </c>
       <c r="L339" s="22" t="n">
-        <v>0.406</v>
+        <v>0.44</v>
       </c>
       <c r="M339" s="5" t="inlineStr">
         <is>
@@ -20668,10 +20668,10 @@
         <v>407</v>
       </c>
       <c r="G340" s="24" t="n">
-        <v>406.594</v>
+        <v>406.56</v>
       </c>
       <c r="H340" s="24" t="n">
-        <v>0.406</v>
+        <v>0.44</v>
       </c>
       <c r="I340" s="9" t="inlineStr">
         <is>
@@ -20682,10 +20682,10 @@
         <v>409</v>
       </c>
       <c r="K340" s="24" t="n">
-        <v>408.969</v>
+        <v>409.003</v>
       </c>
       <c r="L340" s="24" t="n">
-        <v>0.031</v>
+        <v>0.003</v>
       </c>
       <c r="M340" s="9" t="inlineStr">
         <is>
@@ -20727,10 +20727,10 @@
         <v>409</v>
       </c>
       <c r="G341" s="22" t="n">
-        <v>408.969</v>
+        <v>409.003</v>
       </c>
       <c r="H341" s="22" t="n">
-        <v>0.031</v>
+        <v>0.003</v>
       </c>
       <c r="I341" s="5" t="inlineStr">
         <is>
@@ -20741,10 +20741,10 @@
         <v>410</v>
       </c>
       <c r="K341" s="22" t="n">
-        <v>409.037</v>
+        <v>409.003</v>
       </c>
       <c r="L341" s="22" t="n">
-        <v>0.963</v>
+        <v>0.997</v>
       </c>
       <c r="M341" s="5" t="inlineStr">
         <is>
@@ -20786,10 +20786,10 @@
         <v>410</v>
       </c>
       <c r="G342" s="24" t="n">
-        <v>409.037</v>
+        <v>409.003</v>
       </c>
       <c r="H342" s="24" t="n">
-        <v>0.963</v>
+        <v>0.997</v>
       </c>
       <c r="I342" s="9" t="inlineStr">
         <is>
@@ -20800,10 +20800,10 @@
         <v>412</v>
       </c>
       <c r="K342" s="24" t="n">
-        <v>411.887</v>
+        <v>411.853</v>
       </c>
       <c r="L342" s="24" t="n">
-        <v>0.113</v>
+        <v>0.147</v>
       </c>
       <c r="M342" s="9" t="inlineStr">
         <is>
@@ -20845,10 +20845,10 @@
         <v>412</v>
       </c>
       <c r="G343" s="22" t="n">
-        <v>411.887</v>
+        <v>411.853</v>
       </c>
       <c r="H343" s="22" t="n">
-        <v>0.113</v>
+        <v>0.147</v>
       </c>
       <c r="I343" s="5" t="inlineStr">
         <is>
@@ -20859,10 +20859,10 @@
         <v>413</v>
       </c>
       <c r="K343" s="22" t="n">
-        <v>413.041</v>
+        <v>413.075</v>
       </c>
       <c r="L343" s="22" t="n">
-        <v>0.041</v>
+        <v>0.075</v>
       </c>
       <c r="M343" s="5" t="inlineStr">
         <is>
@@ -20904,10 +20904,10 @@
         <v>413</v>
       </c>
       <c r="G344" s="24" t="n">
-        <v>413.041</v>
+        <v>413.075</v>
       </c>
       <c r="H344" s="24" t="n">
-        <v>0.041</v>
+        <v>0.075</v>
       </c>
       <c r="I344" s="9" t="inlineStr">
         <is>
@@ -20918,10 +20918,10 @@
         <v>414</v>
       </c>
       <c r="K344" s="24" t="n">
-        <v>414.33</v>
+        <v>414.364</v>
       </c>
       <c r="L344" s="24" t="n">
-        <v>0.33</v>
+        <v>0.364</v>
       </c>
       <c r="M344" s="9" t="inlineStr">
         <is>
@@ -20963,10 +20963,10 @@
         <v>414</v>
       </c>
       <c r="G345" s="22" t="n">
-        <v>414.33</v>
+        <v>414.364</v>
       </c>
       <c r="H345" s="22" t="n">
-        <v>0.33</v>
+        <v>0.364</v>
       </c>
       <c r="I345" s="5" t="inlineStr">
         <is>
@@ -20977,10 +20977,10 @@
         <v>416</v>
       </c>
       <c r="K345" s="22" t="n">
-        <v>415.076</v>
+        <v>415.043</v>
       </c>
       <c r="L345" s="22" t="n">
-        <v>0.924</v>
+        <v>0.957</v>
       </c>
       <c r="M345" s="5" t="inlineStr">
         <is>
@@ -21022,10 +21022,10 @@
         <v>416</v>
       </c>
       <c r="G346" s="24" t="n">
-        <v>415.076</v>
+        <v>415.043</v>
       </c>
       <c r="H346" s="24" t="n">
-        <v>0.924</v>
+        <v>0.957</v>
       </c>
       <c r="I346" s="9" t="inlineStr">
         <is>
@@ -21036,10 +21036,10 @@
         <v>419</v>
       </c>
       <c r="K346" s="24" t="n">
-        <v>419.148</v>
+        <v>419.182</v>
       </c>
       <c r="L346" s="24" t="n">
-        <v>0.148</v>
+        <v>0.182</v>
       </c>
       <c r="M346" s="9" t="inlineStr">
         <is>
@@ -21081,10 +21081,10 @@
         <v>419</v>
       </c>
       <c r="G347" s="22" t="n">
-        <v>419.148</v>
+        <v>419.182</v>
       </c>
       <c r="H347" s="22" t="n">
-        <v>0.148</v>
+        <v>0.182</v>
       </c>
       <c r="I347" s="5" t="inlineStr">
         <is>
@@ -21095,10 +21095,10 @@
         <v>420</v>
       </c>
       <c r="K347" s="22" t="n">
-        <v>419.759</v>
+        <v>419.725</v>
       </c>
       <c r="L347" s="22" t="n">
-        <v>0.241</v>
+        <v>0.275</v>
       </c>
       <c r="M347" s="5" t="inlineStr">
         <is>
@@ -21140,10 +21140,10 @@
         <v>420</v>
       </c>
       <c r="G348" s="24" t="n">
-        <v>419.759</v>
+        <v>419.725</v>
       </c>
       <c r="H348" s="24" t="n">
-        <v>0.241</v>
+        <v>0.275</v>
       </c>
       <c r="I348" s="9" t="inlineStr">
         <is>
@@ -21154,10 +21154,10 @@
         <v>422</v>
       </c>
       <c r="K348" s="24" t="n">
-        <v>422.337</v>
+        <v>422.371</v>
       </c>
       <c r="L348" s="24" t="n">
-        <v>0.337</v>
+        <v>0.371</v>
       </c>
       <c r="M348" s="9" t="inlineStr">
         <is>
@@ -21199,10 +21199,10 @@
         <v>422</v>
       </c>
       <c r="G349" s="22" t="n">
-        <v>422.337</v>
+        <v>422.371</v>
       </c>
       <c r="H349" s="22" t="n">
-        <v>0.337</v>
+        <v>0.371</v>
       </c>
       <c r="I349" s="5" t="inlineStr">
         <is>
@@ -21213,10 +21213,10 @@
         <v>425</v>
       </c>
       <c r="K349" s="22" t="n">
-        <v>424.712</v>
+        <v>424.678</v>
       </c>
       <c r="L349" s="22" t="n">
-        <v>0.288</v>
+        <v>0.322</v>
       </c>
       <c r="M349" s="5" t="inlineStr">
         <is>
@@ -21258,10 +21258,10 @@
         <v>425</v>
       </c>
       <c r="G350" s="24" t="n">
-        <v>424.712</v>
+        <v>424.678</v>
       </c>
       <c r="H350" s="24" t="n">
-        <v>0.288</v>
+        <v>0.322</v>
       </c>
       <c r="I350" s="9" t="inlineStr">
         <is>
@@ -21272,10 +21272,10 @@
         <v>444</v>
       </c>
       <c r="K350" s="24" t="n">
-        <v>443.44</v>
+        <v>443.406</v>
       </c>
       <c r="L350" s="24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.594</v>
       </c>
       <c r="M350" s="9" t="inlineStr">
         <is>
@@ -21317,10 +21317,10 @@
         <v>444</v>
       </c>
       <c r="G351" s="22" t="n">
-        <v>443.44</v>
+        <v>443.406</v>
       </c>
       <c r="H351" s="22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.594</v>
       </c>
       <c r="I351" s="5" t="inlineStr">
         <is>
@@ -21331,10 +21331,10 @@
         <v>449</v>
       </c>
       <c r="K351" s="22" t="n">
-        <v>448.801</v>
+        <v>448.767</v>
       </c>
       <c r="L351" s="22" t="n">
-        <v>0.199</v>
+        <v>0.233</v>
       </c>
       <c r="M351" s="5" t="inlineStr">
         <is>
@@ -21376,10 +21376,10 @@
         <v>449</v>
       </c>
       <c r="G352" s="24" t="n">
-        <v>448.801</v>
+        <v>448.767</v>
       </c>
       <c r="H352" s="24" t="n">
-        <v>0.199</v>
+        <v>0.233</v>
       </c>
       <c r="I352" s="9" t="inlineStr">
         <is>
@@ -21390,10 +21390,10 @@
         <v>452</v>
       </c>
       <c r="K352" s="24" t="n">
-        <v>451.922</v>
+        <v>451.889</v>
       </c>
       <c r="L352" s="24" t="n">
-        <v>0.078</v>
+        <v>0.111</v>
       </c>
       <c r="M352" s="9" t="inlineStr">
         <is>
@@ -21435,10 +21435,10 @@
         <v>452</v>
       </c>
       <c r="G353" s="22" t="n">
-        <v>451.922</v>
+        <v>451.889</v>
       </c>
       <c r="H353" s="22" t="n">
-        <v>0.078</v>
+        <v>0.111</v>
       </c>
       <c r="I353" s="5" t="inlineStr">
         <is>
